--- a/Översikt KALMAR.xlsx
+++ b/Översikt KALMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45209</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>44876</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45952</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>45345</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>46066</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>44876</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>46058</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>44979</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>44601</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>45947</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>44489</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>44876</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>44476</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>45915</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>44876</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>45324</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>46107</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>45664</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>45561</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>46085</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>44522</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>44951</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>44984</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>45463</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>44970</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         <v>45953</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>44993</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>44979</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>44853</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         <v>45254</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>44489</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>45684</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>44595</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         <v>44475</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
         <v>44489</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>44785</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>44784</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4913,7 +4913,7 @@
         <v>44575</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>44785</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
         <v>45118</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>45943</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         <v>45044</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         <v>44951</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>45114</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>45363</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>44616</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>44595</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
         <v>45903</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         <v>45954</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>44517</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>44970</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>45575</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>45243</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>45722</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6778,7 +6778,7 @@
         <v>44994</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         <v>44994</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
         <v>44802</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         <v>46055</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7206,7 +7206,7 @@
         <v>45874</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         <v>44796</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         <v>45924</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7524,7 +7524,7 @@
         <v>45190</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         <v>46049</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         <v>45105</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>46119</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         <v>46119</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>46245</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>45314</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>44517</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8380,7 +8380,7 @@
         <v>45275</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         <v>44827</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8601,7 +8601,7 @@
         <v>45966</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>46279</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8817,7 +8817,7 @@
         <v>45475</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         <v>45448</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9029,7 +9029,7 @@
         <v>44623</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>44740</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         <v>44895</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         <v>44466</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         <v>44575</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>45264</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9671,7 +9671,7 @@
         <v>45163</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9780,7 +9780,7 @@
         <v>45086</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9885,7 +9885,7 @@
         <v>45007</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9990,7 +9990,7 @@
         <v>45180</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10099,7 +10099,7 @@
         <v>45167</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>45007</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10309,7 +10309,7 @@
         <v>45917</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>44915</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10519,7 +10519,7 @@
         <v>44914</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10624,7 +10624,7 @@
         <v>44991</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10729,7 +10729,7 @@
         <v>44810</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10834,7 +10834,7 @@
         <v>45069</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10939,7 +10939,7 @@
         <v>44855</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11049,7 +11049,7 @@
         <v>45063</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11163,7 +11163,7 @@
         <v>44949</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>45117</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11373,7 +11373,7 @@
         <v>46177</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11487,7 +11487,7 @@
         <v>45083</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11592,7 +11592,7 @@
         <v>46188</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>46112</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11806,7 +11806,7 @@
         <v>46119</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
         <v>46199</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12016,7 +12016,7 @@
         <v>46247</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12121,7 +12121,7 @@
         <v>46247</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12235,7 +12235,7 @@
         <v>44931</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12340,7 +12340,7 @@
         <v>45090</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
         <v>44931</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12550,7 +12550,7 @@
         <v>46258</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12655,7 +12655,7 @@
         <v>45007</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12764,7 +12764,7 @@
         <v>45775</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12869,7 +12869,7 @@
         <v>45544</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12978,7 +12978,7 @@
         <v>45782</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13088,7 +13088,7 @@
         <v>45454</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13193,7 +13193,7 @@
         <v>45791</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13298,7 +13298,7 @@
         <v>45574</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13408,7 +13408,7 @@
         <v>45868</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13513,7 +13513,7 @@
         <v>44810</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13623,7 +13623,7 @@
         <v>44586</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13728,7 +13728,7 @@
         <v>45611</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13833,7 +13833,7 @@
         <v>45373</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13942,7 +13942,7 @@
         <v>46063</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14047,7 +14047,7 @@
         <v>46087</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14152,7 +14152,7 @@
         <v>44629</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14225,7 +14225,7 @@
         <v>44643</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14298,7 +14298,7 @@
         <v>44823</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14371,7 +14371,7 @@
         <v>44497</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14444,7 +14444,7 @@
         <v>44460</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14517,7 +14517,7 @@
         <v>44505</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14590,7 +14590,7 @@
         <v>44852</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14663,7 +14663,7 @@
         <v>44684</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14736,7 +14736,7 @@
         <v>44539</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14809,7 +14809,7 @@
         <v>44498</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14882,7 +14882,7 @@
         <v>44498</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14955,7 +14955,7 @@
         <v>44489</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>44525</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15101,7 +15101,7 @@
         <v>44823</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         <v>44790</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15247,7 +15247,7 @@
         <v>44531</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15320,7 +15320,7 @@
         <v>44602</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15393,7 +15393,7 @@
         <v>44858</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15466,7 +15466,7 @@
         <v>44522</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15539,7 +15539,7 @@
         <v>44823</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15612,7 +15612,7 @@
         <v>44818</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15685,7 +15685,7 @@
         <v>44858</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15758,7 +15758,7 @@
         <v>44858</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15831,7 +15831,7 @@
         <v>44852</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15904,7 +15904,7 @@
         <v>44858</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15977,7 +15977,7 @@
         <v>44615</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16050,7 +16050,7 @@
         <v>44586</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16123,7 +16123,7 @@
         <v>44502</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16196,7 +16196,7 @@
         <v>44552</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16269,7 +16269,7 @@
         <v>44482</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16342,7 +16342,7 @@
         <v>44620</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16415,7 +16415,7 @@
         <v>44625</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16488,7 +16488,7 @@
         <v>44461</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>44784</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
         <v>44654</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16707,7 +16707,7 @@
         <v>44855</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         <v>44858</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16853,7 +16853,7 @@
         <v>44732</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>44810</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16999,7 +16999,7 @@
         <v>44461</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17072,7 +17072,7 @@
         <v>44858</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17145,7 +17145,7 @@
         <v>44511</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17218,7 +17218,7 @@
         <v>45411</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17291,7 +17291,7 @@
         <v>44924</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17364,7 +17364,7 @@
         <v>44988</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>45205</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17510,7 +17510,7 @@
         <v>45161</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17583,7 +17583,7 @@
         <v>45090</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>45090</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17729,7 +17729,7 @@
         <v>45090</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
         <v>45097</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17875,7 +17875,7 @@
         <v>45735</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17948,7 +17948,7 @@
         <v>45272</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18021,7 +18021,7 @@
         <v>44502</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18094,7 +18094,7 @@
         <v>44477</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18167,7 +18167,7 @@
         <v>44595</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>44993</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18313,7 +18313,7 @@
         <v>45099</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18386,7 +18386,7 @@
         <v>45618</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18459,7 +18459,7 @@
         <v>44846</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>45349</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18605,7 +18605,7 @@
         <v>44855</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18678,7 +18678,7 @@
         <v>45233</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18751,7 +18751,7 @@
         <v>44861</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>44924</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18897,7 +18897,7 @@
         <v>45153</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18970,7 +18970,7 @@
         <v>44991</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19043,7 +19043,7 @@
         <v>44864</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19116,7 +19116,7 @@
         <v>45173</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19189,7 +19189,7 @@
         <v>45173</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19262,7 +19262,7 @@
         <v>44712</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19335,7 +19335,7 @@
         <v>45250</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>45195</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19481,7 +19481,7 @@
         <v>44993</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19554,7 +19554,7 @@
         <v>45219</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19627,7 +19627,7 @@
         <v>45219</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>45272</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19773,7 +19773,7 @@
         <v>44782</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>45028</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19919,7 +19919,7 @@
         <v>45400</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19992,7 +19992,7 @@
         <v>45189</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20065,7 +20065,7 @@
         <v>45239</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>45058</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20216,7 +20216,7 @@
         <v>45720</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20289,7 +20289,7 @@
         <v>45182</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20362,7 +20362,7 @@
         <v>45110</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20440,7 +20440,7 @@
         <v>45104</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20518,7 +20518,7 @@
         <v>45341</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20591,7 +20591,7 @@
         <v>44529</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20664,7 +20664,7 @@
         <v>45104</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20737,7 +20737,7 @@
         <v>45104</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20810,7 +20810,7 @@
         <v>45335</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20888,7 +20888,7 @@
         <v>44971</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20961,7 +20961,7 @@
         <v>45180</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21034,7 +21034,7 @@
         <v>45061</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21107,7 +21107,7 @@
         <v>44984</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21200,7 +21200,7 @@
         <v>44984</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21273,7 +21273,7 @@
         <v>44617</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21346,7 +21346,7 @@
         <v>44617</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21419,7 +21419,7 @@
         <v>45007</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21492,7 +21492,7 @@
         <v>45007</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21565,7 +21565,7 @@
         <v>45205</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21638,7 +21638,7 @@
         <v>45096</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21711,7 +21711,7 @@
         <v>45212</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21784,7 +21784,7 @@
         <v>45170</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21857,7 +21857,7 @@
         <v>45091</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21930,7 +21930,7 @@
         <v>44973</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22003,7 +22003,7 @@
         <v>44645</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22076,7 +22076,7 @@
         <v>45707</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22149,7 +22149,7 @@
         <v>44963</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22222,7 +22222,7 @@
         <v>45796</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22295,7 +22295,7 @@
         <v>45540</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22368,7 +22368,7 @@
         <v>44816</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22441,7 +22441,7 @@
         <v>44914</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22514,7 +22514,7 @@
         <v>45688</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
         <v>45636</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22660,7 +22660,7 @@
         <v>45544</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22738,7 +22738,7 @@
         <v>45923</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22811,7 +22811,7 @@
         <v>45173</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22884,7 +22884,7 @@
         <v>45104</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22957,7 +22957,7 @@
         <v>45113</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23030,7 +23030,7 @@
         <v>45091</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23103,7 +23103,7 @@
         <v>45167</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23176,7 +23176,7 @@
         <v>45233</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23249,7 +23249,7 @@
         <v>46036</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23322,7 +23322,7 @@
         <v>45796</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23395,7 +23395,7 @@
         <v>45252</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23468,7 +23468,7 @@
         <v>45544</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23541,7 +23541,7 @@
         <v>45688</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23614,7 +23614,7 @@
         <v>45406</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23687,7 +23687,7 @@
         <v>44529</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23760,7 +23760,7 @@
         <v>45564</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23833,7 +23833,7 @@
         <v>45267</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23906,7 +23906,7 @@
         <v>45789</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23979,7 +23979,7 @@
         <v>45492</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24052,7 +24052,7 @@
         <v>44502</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24125,7 +24125,7 @@
         <v>44872</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
         <v>45104</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24271,7 +24271,7 @@
         <v>45198</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24344,7 +24344,7 @@
         <v>46139</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24417,7 +24417,7 @@
         <v>45243</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24490,7 +24490,7 @@
         <v>44994</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24563,7 +24563,7 @@
         <v>45764</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24636,7 +24636,7 @@
         <v>44846</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24709,7 +24709,7 @@
         <v>45630</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24782,7 +24782,7 @@
         <v>45727</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24855,7 +24855,7 @@
         <v>45548</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24928,7 +24928,7 @@
         <v>45840</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25001,7 +25001,7 @@
         <v>45912</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25074,7 +25074,7 @@
         <v>45070</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25152,7 +25152,7 @@
         <v>45912</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25225,7 +25225,7 @@
         <v>44909</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25298,7 +25298,7 @@
         <v>45215</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25371,7 +25371,7 @@
         <v>45719</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25449,7 +25449,7 @@
         <v>45246</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25522,7 +25522,7 @@
         <v>45923</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25595,7 +25595,7 @@
         <v>45924</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25668,7 +25668,7 @@
         <v>45268</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25741,7 +25741,7 @@
         <v>45229</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25814,7 +25814,7 @@
         <v>46099</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25887,7 +25887,7 @@
         <v>45595</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25960,7 +25960,7 @@
         <v>45628</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26033,7 +26033,7 @@
         <v>45252</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26106,7 +26106,7 @@
         <v>45930</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         <v>45233</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26252,7 +26252,7 @@
         <v>44566</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26325,7 +26325,7 @@
         <v>45932</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26398,7 +26398,7 @@
         <v>45418</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26471,7 +26471,7 @@
         <v>45716</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26544,7 +26544,7 @@
         <v>45345</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26617,7 +26617,7 @@
         <v>45028</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26690,7 +26690,7 @@
         <v>45713</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26763,7 +26763,7 @@
         <v>45939</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26836,7 +26836,7 @@
         <v>44497</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26909,7 +26909,7 @@
         <v>45618</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26982,7 +26982,7 @@
         <v>45695</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27055,7 +27055,7 @@
         <v>45006</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27128,7 +27128,7 @@
         <v>45229</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27201,7 +27201,7 @@
         <v>44971</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27274,7 +27274,7 @@
         <v>45093</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27347,7 +27347,7 @@
         <v>45153</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27420,7 +27420,7 @@
         <v>44915</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27493,7 +27493,7 @@
         <v>44914</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27566,7 +27566,7 @@
         <v>44895</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27639,7 +27639,7 @@
         <v>45551</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27712,7 +27712,7 @@
         <v>45327</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27785,7 +27785,7 @@
         <v>46155</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27858,7 +27858,7 @@
         <v>44939</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27931,7 +27931,7 @@
         <v>45246</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28004,7 +28004,7 @@
         <v>45246</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28077,7 +28077,7 @@
         <v>44973</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28150,7 +28150,7 @@
         <v>45378</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28223,7 +28223,7 @@
         <v>45175</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28296,7 +28296,7 @@
         <v>45173</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28369,7 +28369,7 @@
         <v>45930</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28442,7 +28442,7 @@
         <v>45306</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28515,7 +28515,7 @@
         <v>45978</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28588,7 +28588,7 @@
         <v>45091</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28661,7 +28661,7 @@
         <v>46155</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28734,7 +28734,7 @@
         <v>46155</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28807,7 +28807,7 @@
         <v>44629</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28880,7 +28880,7 @@
         <v>45903</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28953,7 +28953,7 @@
         <v>45624</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29031,7 +29031,7 @@
         <v>44862</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29104,7 +29104,7 @@
         <v>45574</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29182,7 +29182,7 @@
         <v>45097</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29255,7 +29255,7 @@
         <v>46160</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29328,7 +29328,7 @@
         <v>44539</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29401,7 +29401,7 @@
         <v>45154</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29474,7 +29474,7 @@
         <v>45236</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29547,7 +29547,7 @@
         <v>46160</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29620,7 +29620,7 @@
         <v>45182</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29693,7 +29693,7 @@
         <v>46162</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29766,7 +29766,7 @@
         <v>46162</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29839,7 +29839,7 @@
         <v>44909</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29912,7 +29912,7 @@
         <v>44988</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29985,7 +29985,7 @@
         <v>45624</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30063,7 +30063,7 @@
         <v>45266</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30136,7 +30136,7 @@
         <v>45625</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30209,7 +30209,7 @@
         <v>46162</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30282,7 +30282,7 @@
         <v>45629</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30355,7 +30355,7 @@
         <v>45188</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30428,7 +30428,7 @@
         <v>44803</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30501,7 +30501,7 @@
         <v>45402</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30579,7 +30579,7 @@
         <v>45680</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30652,7 +30652,7 @@
         <v>46008</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30725,7 +30725,7 @@
         <v>46008</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30798,7 +30798,7 @@
         <v>44966</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30871,7 +30871,7 @@
         <v>46010</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30944,7 +30944,7 @@
         <v>46013</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31017,7 +31017,7 @@
         <v>44595</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31090,7 +31090,7 @@
         <v>45097</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31163,7 +31163,7 @@
         <v>45685</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31236,7 +31236,7 @@
         <v>45044</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31309,7 +31309,7 @@
         <v>44939</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31382,7 +31382,7 @@
         <v>45470</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31455,7 +31455,7 @@
         <v>46026</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31528,7 +31528,7 @@
         <v>45125</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31601,7 +31601,7 @@
         <v>45387</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31674,7 +31674,7 @@
         <v>45387</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31747,7 +31747,7 @@
         <v>45476</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31820,7 +31820,7 @@
         <v>44882</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31893,7 +31893,7 @@
         <v>45624</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31966,7 +31966,7 @@
         <v>45534</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32039,7 +32039,7 @@
         <v>44959</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32112,7 +32112,7 @@
         <v>45628</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32185,7 +32185,7 @@
         <v>46099</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32258,7 +32258,7 @@
         <v>44544</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32331,7 +32331,7 @@
         <v>44847</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32404,7 +32404,7 @@
         <v>44543</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32477,7 +32477,7 @@
         <v>46048</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32550,7 +32550,7 @@
         <v>45202</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32623,7 +32623,7 @@
         <v>45050</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32696,7 +32696,7 @@
         <v>45308</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32769,7 +32769,7 @@
         <v>46049</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32842,7 +32842,7 @@
         <v>46054</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32915,7 +32915,7 @@
         <v>46054</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32988,7 +32988,7 @@
         <v>44993</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33061,7 +33061,7 @@
         <v>44782</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33134,7 +33134,7 @@
         <v>45075</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33207,7 +33207,7 @@
         <v>45915</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33280,7 +33280,7 @@
         <v>46177</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33353,7 +33353,7 @@
         <v>46063</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33426,7 +33426,7 @@
         <v>46062</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33499,7 +33499,7 @@
         <v>46063</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33572,7 +33572,7 @@
         <v>46063</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33645,7 +33645,7 @@
         <v>45114</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33718,7 +33718,7 @@
         <v>46070</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33791,7 +33791,7 @@
         <v>46070</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33864,7 +33864,7 @@
         <v>46070</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33937,7 +33937,7 @@
         <v>45173</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34010,7 +34010,7 @@
         <v>45387</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34083,7 +34083,7 @@
         <v>45387</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34156,7 +34156,7 @@
         <v>44564</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34229,7 +34229,7 @@
         <v>46188</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34302,7 +34302,7 @@
         <v>45149</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34375,7 +34375,7 @@
         <v>45149</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34448,7 +34448,7 @@
         <v>45141</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34521,7 +34521,7 @@
         <v>46185</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34594,7 +34594,7 @@
         <v>44971</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34667,7 +34667,7 @@
         <v>46092</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34740,7 +34740,7 @@
         <v>45205</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34813,7 +34813,7 @@
         <v>46092</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34886,7 +34886,7 @@
         <v>45524</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34959,7 +34959,7 @@
         <v>45099</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35032,7 +35032,7 @@
         <v>46093</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35105,7 +35105,7 @@
         <v>45212</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35178,7 +35178,7 @@
         <v>46036</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35251,7 +35251,7 @@
         <v>46178</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35324,7 +35324,7 @@
         <v>46099</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35397,7 +35397,7 @@
         <v>45607</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35470,7 +35470,7 @@
         <v>45233</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35543,7 +35543,7 @@
         <v>45540</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35616,7 +35616,7 @@
         <v>45169</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35689,7 +35689,7 @@
         <v>44482</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35762,7 +35762,7 @@
         <v>45246</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35835,7 +35835,7 @@
         <v>46197</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35908,7 +35908,7 @@
         <v>46198</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35981,7 +35981,7 @@
         <v>46108</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36054,7 +36054,7 @@
         <v>45118</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36127,7 +36127,7 @@
         <v>46112</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36200,7 +36200,7 @@
         <v>44656</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36273,7 +36273,7 @@
         <v>44690</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36346,7 +36346,7 @@
         <v>46199</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36419,7 +36419,7 @@
         <v>44819</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>44952</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36565,7 +36565,7 @@
         <v>46119</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36638,7 +36638,7 @@
         <v>46119</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36711,7 +36711,7 @@
         <v>45323</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36784,7 +36784,7 @@
         <v>45092</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36857,7 +36857,7 @@
         <v>45086</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36930,7 +36930,7 @@
         <v>46202</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37003,7 +37003,7 @@
         <v>44895</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37076,7 +37076,7 @@
         <v>45156</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37149,7 +37149,7 @@
         <v>46203</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37222,7 +37222,7 @@
         <v>45034</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37295,7 +37295,7 @@
         <v>45254</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37368,7 +37368,7 @@
         <v>45174</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37441,7 +37441,7 @@
         <v>46134</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37514,7 +37514,7 @@
         <v>46247</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37592,7 +37592,7 @@
         <v>45363</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37665,7 +37665,7 @@
         <v>46134</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37738,7 +37738,7 @@
         <v>44818</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37811,7 +37811,7 @@
         <v>45531</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37884,7 +37884,7 @@
         <v>45324</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37957,7 +37957,7 @@
         <v>46139</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38030,7 +38030,7 @@
         <v>45915</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38103,7 +38103,7 @@
         <v>46247</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38176,7 +38176,7 @@
         <v>44574</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38249,7 +38249,7 @@
         <v>45034</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38322,7 +38322,7 @@
         <v>46009</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38395,7 +38395,7 @@
         <v>46247</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38468,7 +38468,7 @@
         <v>46139</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38541,7 +38541,7 @@
         <v>45454</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38614,7 +38614,7 @@
         <v>46154</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38687,7 +38687,7 @@
         <v>45703</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38760,7 +38760,7 @@
         <v>44564</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38833,7 +38833,7 @@
         <v>46253</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38906,7 +38906,7 @@
         <v>45209</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38979,7 +38979,7 @@
         <v>45209</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39052,7 +39052,7 @@
         <v>45091</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39125,7 +39125,7 @@
         <v>45260</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39198,7 +39198,7 @@
         <v>46253</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39271,7 +39271,7 @@
         <v>44978</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39344,7 +39344,7 @@
         <v>46254</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39422,7 +39422,7 @@
         <v>45273</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39495,7 +39495,7 @@
         <v>45334</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39568,7 +39568,7 @@
         <v>46212</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39641,7 +39641,7 @@
         <v>46254</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39719,7 +39719,7 @@
         <v>45189</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39792,7 +39792,7 @@
         <v>45356</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39865,7 +39865,7 @@
         <v>46259</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39938,7 +39938,7 @@
         <v>45027</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40011,7 +40011,7 @@
         <v>45067</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40084,7 +40084,7 @@
         <v>44823</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40157,7 +40157,7 @@
         <v>44823</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40230,7 +40230,7 @@
         <v>44732</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40303,7 +40303,7 @@
         <v>44963</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40376,7 +40376,7 @@
         <v>44963</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40449,7 +40449,7 @@
         <v>45341</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40522,7 +40522,7 @@
         <v>45336</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40595,7 +40595,7 @@
         <v>46063</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40668,7 +40668,7 @@
         <v>45618</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40741,7 +40741,7 @@
         <v>45540</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40814,7 +40814,7 @@
         <v>45076</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40892,7 +40892,7 @@
         <v>45156</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40965,7 +40965,7 @@
         <v>46111</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41038,7 +41038,7 @@
         <v>44824</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41111,7 +41111,7 @@
         <v>45001</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41184,7 +41184,7 @@
         <v>44658</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41257,7 +41257,7 @@
         <v>46223</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41330,7 +41330,7 @@
         <v>45114</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41403,7 +41403,7 @@
         <v>46269</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41476,7 +41476,7 @@
         <v>45229</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41549,7 +41549,7 @@
         <v>44924</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41622,7 +41622,7 @@
         <v>45119</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41695,7 +41695,7 @@
         <v>44858</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41768,7 +41768,7 @@
         <v>45181</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41841,7 +41841,7 @@
         <v>45775</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41914,7 +41914,7 @@
         <v>45558</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41992,7 +41992,7 @@
         <v>45439</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42065,7 +42065,7 @@
         <v>45443</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42138,7 +42138,7 @@
         <v>45551</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42211,7 +42211,7 @@
         <v>45246</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42284,7 +42284,7 @@
         <v>45782</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42362,7 +42362,7 @@
         <v>46272</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42435,7 +42435,7 @@
         <v>45785</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42508,7 +42508,7 @@
         <v>46273</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42581,7 +42581,7 @@
         <v>46273</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42654,7 +42654,7 @@
         <v>46275</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42727,7 +42727,7 @@
         <v>46274</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42800,7 +42800,7 @@
         <v>46276</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42873,7 +42873,7 @@
         <v>45664</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42946,7 +42946,7 @@
         <v>45664</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43019,7 +43019,7 @@
         <v>46276</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43092,7 +43092,7 @@
         <v>45566</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43165,7 +43165,7 @@
         <v>45730</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43238,7 +43238,7 @@
         <v>45363</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43311,7 +43311,7 @@
         <v>46281</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43384,7 +43384,7 @@
         <v>45791</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43457,7 +43457,7 @@
         <v>46281</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43530,7 +43530,7 @@
         <v>45792</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43608,7 +43608,7 @@
         <v>45720</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43681,7 +43681,7 @@
         <v>46281</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43754,7 +43754,7 @@
         <v>45805</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43827,7 +43827,7 @@
         <v>45812</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43900,7 +43900,7 @@
         <v>45824</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43973,7 +43973,7 @@
         <v>45842</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44046,7 +44046,7 @@
         <v>45842</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>45861</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44192,7 +44192,7 @@
         <v>45831</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44265,7 +44265,7 @@
         <v>45764</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44338,7 +44338,7 @@
         <v>45779</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44411,7 +44411,7 @@
         <v>45874</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44484,7 +44484,7 @@
         <v>45785</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44557,7 +44557,7 @@
         <v>45387</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44630,7 +44630,7 @@
         <v>45373</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44703,7 +44703,7 @@
         <v>45345</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44776,7 +44776,7 @@
         <v>45440</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44849,7 +44849,7 @@
         <v>44607</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44922,7 +44922,7 @@
         <v>45595</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44995,7 +44995,7 @@
         <v>44587</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45068,7 +45068,7 @@
         <v>44806</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45141,7 +45141,7 @@
         <v>44965</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45214,7 +45214,7 @@
         <v>44531</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45287,7 +45287,7 @@
         <v>44957</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45360,7 +45360,7 @@
         <v>45345</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45433,7 +45433,7 @@
         <v>45345</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45506,7 +45506,7 @@
         <v>45685</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45579,7 +45579,7 @@
         <v>45358</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45652,7 +45652,7 @@
         <v>44957</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45725,7 +45725,7 @@
         <v>45824</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45798,7 +45798,7 @@
         <v>44071</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45871,7 +45871,7 @@
         <v>45890</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45944,7 +45944,7 @@
         <v>45902</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46017,7 +46017,7 @@
         <v>46058</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46090,7 +46090,7 @@
         <v>46062</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46163,7 +46163,7 @@
         <v>46062</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46236,7 +46236,7 @@
         <v>46063</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46309,7 +46309,7 @@
         <v>46062</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46382,7 +46382,7 @@
         <v>46062</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46455,7 +46455,7 @@
         <v>46065</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46528,7 +46528,7 @@
         <v>46110</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>

--- a/Översikt KALMAR.xlsx
+++ b/Översikt KALMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45209</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>44876</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45952</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>45345</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>46066</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>44876</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>46058</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>44979</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>44601</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>44876</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>45947</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>44489</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>44476</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>45915</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>44876</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>45324</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>45664</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>45561</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>46085</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>44522</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>44951</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>44984</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>45463</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>44970</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>45953</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>44489</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>44853</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>44993</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>44979</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         <v>45254</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>45684</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>44595</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>44475</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>44489</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>44784</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>45943</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         <v>45118</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>44575</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         <v>45114</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
         <v>44785</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>44951</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         <v>44785</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>45044</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>45363</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>44616</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5795,7 +5795,7 @@
         <v>44595</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>45903</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>45954</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>44517</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>45190</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>44517</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
         <v>45243</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>44802</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>45924</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         <v>45105</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>44994</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
         <v>44994</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         <v>46119</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>46119</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7302,7 +7302,7 @@
         <v>45874</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>46055</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7514,7 +7514,7 @@
         <v>45722</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>44796</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         <v>44970</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7841,7 +7841,7 @@
         <v>46049</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         <v>45275</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>45575</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>45314</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>44827</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8380,7 +8380,7 @@
         <v>45966</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>46279</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8596,7 +8596,7 @@
         <v>46245</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>45475</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         <v>45448</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         <v>44623</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9019,7 +9019,7 @@
         <v>45083</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9124,7 +9124,7 @@
         <v>44855</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
         <v>45163</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         <v>44915</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>45086</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         <v>44914</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9658,7 +9658,7 @@
         <v>45574</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9768,7 +9768,7 @@
         <v>45007</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>44740</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
         <v>46119</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>44810</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10188,7 +10188,7 @@
         <v>45917</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>44575</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10402,7 +10402,7 @@
         <v>44991</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10507,7 +10507,7 @@
         <v>45069</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10612,7 +10612,7 @@
         <v>45007</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10721,7 +10721,7 @@
         <v>45264</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10830,7 +10830,7 @@
         <v>44895</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>44466</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11044,7 +11044,7 @@
         <v>45868</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         <v>46177</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>45117</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11368,7 +11368,7 @@
         <v>46188</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
         <v>46199</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>45180</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11687,7 +11687,7 @@
         <v>45167</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>46258</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11897,7 +11897,7 @@
         <v>46247</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12002,7 +12002,7 @@
         <v>46247</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12116,7 +12116,7 @@
         <v>45007</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>44931</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12326,7 +12326,7 @@
         <v>44949</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12431,7 +12431,7 @@
         <v>44931</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12536,7 +12536,7 @@
         <v>45090</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12641,7 +12641,7 @@
         <v>45063</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12755,7 +12755,7 @@
         <v>45544</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12864,7 +12864,7 @@
         <v>45775</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12969,7 +12969,7 @@
         <v>45782</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>45454</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13184,7 +13184,7 @@
         <v>45791</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>44586</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13394,7 +13394,7 @@
         <v>44810</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13504,7 +13504,7 @@
         <v>45611</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13609,7 +13609,7 @@
         <v>45373</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13718,7 +13718,7 @@
         <v>46063</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>46087</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13928,7 +13928,7 @@
         <v>44643</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14001,7 +14001,7 @@
         <v>44823</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
         <v>44497</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14147,7 +14147,7 @@
         <v>44629</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>44505</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14293,7 +14293,7 @@
         <v>44852</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14366,7 +14366,7 @@
         <v>44684</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
         <v>44539</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14512,7 +14512,7 @@
         <v>44498</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14585,7 +14585,7 @@
         <v>44498</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14658,7 +14658,7 @@
         <v>44489</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14731,7 +14731,7 @@
         <v>44525</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14804,7 +14804,7 @@
         <v>44823</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14877,7 +14877,7 @@
         <v>44790</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14950,7 +14950,7 @@
         <v>44531</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>44602</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15096,7 +15096,7 @@
         <v>44858</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15169,7 +15169,7 @@
         <v>44522</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>44823</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15315,7 +15315,7 @@
         <v>44818</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15388,7 +15388,7 @@
         <v>44858</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15461,7 +15461,7 @@
         <v>44858</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15534,7 +15534,7 @@
         <v>44852</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15607,7 +15607,7 @@
         <v>44858</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15680,7 +15680,7 @@
         <v>44615</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15753,7 +15753,7 @@
         <v>44586</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>44502</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15899,7 +15899,7 @@
         <v>44552</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15972,7 +15972,7 @@
         <v>44482</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>44620</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16118,7 +16118,7 @@
         <v>44625</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16191,7 +16191,7 @@
         <v>44784</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16264,7 +16264,7 @@
         <v>44654</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16337,7 +16337,7 @@
         <v>44855</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16410,7 +16410,7 @@
         <v>44858</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16483,7 +16483,7 @@
         <v>44732</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16556,7 +16556,7 @@
         <v>44810</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16629,7 +16629,7 @@
         <v>44858</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>44511</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16775,7 +16775,7 @@
         <v>45341</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16848,7 +16848,7 @@
         <v>45341</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>45324</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16994,7 +16994,7 @@
         <v>45044</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17067,7 +17067,7 @@
         <v>45267</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17140,7 +17140,7 @@
         <v>45716</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17213,7 +17213,7 @@
         <v>45215</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17286,7 +17286,7 @@
         <v>45334</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17359,7 +17359,7 @@
         <v>44782</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17432,7 +17432,7 @@
         <v>45097</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17505,7 +17505,7 @@
         <v>45209</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17578,7 +17578,7 @@
         <v>45209</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17651,7 +17651,7 @@
         <v>45091</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
         <v>45243</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17797,7 +17797,7 @@
         <v>45378</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17870,7 +17870,7 @@
         <v>45250</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17943,7 +17943,7 @@
         <v>44963</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18016,7 +18016,7 @@
         <v>45387</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18089,7 +18089,7 @@
         <v>45387</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18162,7 +18162,7 @@
         <v>45268</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18235,7 +18235,7 @@
         <v>44914</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18308,7 +18308,7 @@
         <v>46013</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18381,7 +18381,7 @@
         <v>45097</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18454,7 +18454,7 @@
         <v>45306</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>45096</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
         <v>46026</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18673,7 +18673,7 @@
         <v>45141</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18746,7 +18746,7 @@
         <v>45254</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18819,7 +18819,7 @@
         <v>45630</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18892,7 +18892,7 @@
         <v>45476</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18965,7 +18965,7 @@
         <v>44994</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>44872</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19111,7 +19111,7 @@
         <v>45796</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         <v>45789</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
         <v>45636</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>45492</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19403,7 +19403,7 @@
         <v>45796</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19476,7 +19476,7 @@
         <v>45273</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19549,7 +19549,7 @@
         <v>45246</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>45246</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19695,7 +19695,7 @@
         <v>44895</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19768,7 +19768,7 @@
         <v>44564</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19841,7 +19841,7 @@
         <v>44988</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19914,7 +19914,7 @@
         <v>44862</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19987,7 +19987,7 @@
         <v>46048</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20060,7 +20060,7 @@
         <v>46049</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20133,7 +20133,7 @@
         <v>45153</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20206,7 +20206,7 @@
         <v>45050</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20279,7 +20279,7 @@
         <v>44909</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20352,7 +20352,7 @@
         <v>45720</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>44924</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20498,7 +20498,7 @@
         <v>45840</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20571,7 +20571,7 @@
         <v>46054</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20644,7 +20644,7 @@
         <v>46054</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20717,7 +20717,7 @@
         <v>45912</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20790,7 +20790,7 @@
         <v>45912</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20863,7 +20863,7 @@
         <v>45548</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20936,7 +20936,7 @@
         <v>46062</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21009,7 +21009,7 @@
         <v>45551</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21082,7 +21082,7 @@
         <v>46063</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21155,7 +21155,7 @@
         <v>46063</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21228,7 +21228,7 @@
         <v>44595</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21301,7 +21301,7 @@
         <v>44595</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21374,7 +21374,7 @@
         <v>45028</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21447,7 +21447,7 @@
         <v>44502</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21520,7 +21520,7 @@
         <v>46070</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21593,7 +21593,7 @@
         <v>45695</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21666,7 +21666,7 @@
         <v>45924</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21739,7 +21739,7 @@
         <v>45923</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21812,7 +21812,7 @@
         <v>45104</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21885,7 +21885,7 @@
         <v>46070</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21958,7 +21958,7 @@
         <v>45930</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22031,7 +22031,7 @@
         <v>44971</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22104,7 +22104,7 @@
         <v>45805</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22177,7 +22177,7 @@
         <v>44539</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22250,7 +22250,7 @@
         <v>45932</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22323,7 +22323,7 @@
         <v>45167</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22396,7 +22396,7 @@
         <v>45058</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22469,7 +22469,7 @@
         <v>45720</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22542,7 +22542,7 @@
         <v>44915</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22615,7 +22615,7 @@
         <v>45229</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22688,7 +22688,7 @@
         <v>46092</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22761,7 +22761,7 @@
         <v>46092</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22834,7 +22834,7 @@
         <v>46093</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22907,7 +22907,7 @@
         <v>45939</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22980,7 +22980,7 @@
         <v>46099</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23053,7 +23053,7 @@
         <v>45219</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23126,7 +23126,7 @@
         <v>45205</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23199,7 +23199,7 @@
         <v>45006</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23272,7 +23272,7 @@
         <v>44959</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23345,7 +23345,7 @@
         <v>45061</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23418,7 +23418,7 @@
         <v>45091</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23491,7 +23491,7 @@
         <v>45156</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23564,7 +23564,7 @@
         <v>44816</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23637,7 +23637,7 @@
         <v>45272</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23710,7 +23710,7 @@
         <v>45624</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23788,7 +23788,7 @@
         <v>45812</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23861,7 +23861,7 @@
         <v>44993</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23934,7 +23934,7 @@
         <v>46108</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24007,7 +24007,7 @@
         <v>46112</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24080,7 +24080,7 @@
         <v>44909</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24153,7 +24153,7 @@
         <v>46119</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24226,7 +24226,7 @@
         <v>46119</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         <v>45624</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24372,7 +24372,7 @@
         <v>45624</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24450,7 +24450,7 @@
         <v>44952</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24523,7 +24523,7 @@
         <v>44966</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24596,7 +24596,7 @@
         <v>44984</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24689,7 +24689,7 @@
         <v>44984</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24762,7 +24762,7 @@
         <v>44973</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24835,7 +24835,7 @@
         <v>45618</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24908,7 +24908,7 @@
         <v>45001</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24981,7 +24981,7 @@
         <v>45978</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25054,7 +25054,7 @@
         <v>45680</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25127,7 +25127,7 @@
         <v>44993</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25200,7 +25200,7 @@
         <v>45930</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25273,7 +25273,7 @@
         <v>44732</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25346,7 +25346,7 @@
         <v>44924</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25419,7 +25419,7 @@
         <v>45161</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25492,7 +25492,7 @@
         <v>46134</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25565,7 +25565,7 @@
         <v>46134</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25638,7 +25638,7 @@
         <v>45114</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25711,7 +25711,7 @@
         <v>46036</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25784,7 +25784,7 @@
         <v>46009</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25857,7 +25857,7 @@
         <v>45544</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25935,7 +25935,7 @@
         <v>45688</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26008,7 +26008,7 @@
         <v>45764</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26081,7 +26081,7 @@
         <v>45923</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26154,7 +26154,7 @@
         <v>45688</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26227,7 +26227,7 @@
         <v>45915</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26300,7 +26300,7 @@
         <v>46139</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26373,7 +26373,7 @@
         <v>44574</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26446,7 +26446,7 @@
         <v>45719</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26524,7 +26524,7 @@
         <v>44824</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26597,7 +26597,7 @@
         <v>44564</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26670,7 +26670,7 @@
         <v>45091</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26743,7 +26743,7 @@
         <v>44988</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26816,7 +26816,7 @@
         <v>44482</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26889,7 +26889,7 @@
         <v>46008</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26962,7 +26962,7 @@
         <v>46008</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27035,7 +27035,7 @@
         <v>45229</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27108,7 +27108,7 @@
         <v>45028</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27181,7 +27181,7 @@
         <v>46010</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27254,7 +27254,7 @@
         <v>44823</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27327,7 +27327,7 @@
         <v>44823</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27400,7 +27400,7 @@
         <v>45824</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27473,7 +27473,7 @@
         <v>44617</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27546,7 +27546,7 @@
         <v>44617</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27619,7 +27619,7 @@
         <v>46139</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27692,7 +27692,7 @@
         <v>45205</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27765,7 +27765,7 @@
         <v>45034</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27838,7 +27838,7 @@
         <v>45727</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27911,7 +27911,7 @@
         <v>45239</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27989,7 +27989,7 @@
         <v>44629</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28062,7 +28062,7 @@
         <v>46099</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28135,7 +28135,7 @@
         <v>45180</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28208,7 +28208,7 @@
         <v>45540</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28281,7 +28281,7 @@
         <v>44502</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28354,7 +28354,7 @@
         <v>44566</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28427,7 +28427,7 @@
         <v>45233</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28500,7 +28500,7 @@
         <v>44846</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28573,7 +28573,7 @@
         <v>44939</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28646,7 +28646,7 @@
         <v>44882</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28719,7 +28719,7 @@
         <v>46155</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28792,7 +28792,7 @@
         <v>45092</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28865,7 +28865,7 @@
         <v>46155</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28938,7 +28938,7 @@
         <v>44914</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29011,7 +29011,7 @@
         <v>46155</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29084,7 +29084,7 @@
         <v>46160</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29157,7 +29157,7 @@
         <v>45099</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29230,7 +29230,7 @@
         <v>45236</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29303,7 +29303,7 @@
         <v>46160</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29376,7 +29376,7 @@
         <v>45903</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29449,7 +29449,7 @@
         <v>45104</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29522,7 +29522,7 @@
         <v>45104</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29595,7 +29595,7 @@
         <v>45104</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29668,7 +29668,7 @@
         <v>46162</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29741,7 +29741,7 @@
         <v>46162</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29814,7 +29814,7 @@
         <v>46162</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29887,7 +29887,7 @@
         <v>44924</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29960,7 +29960,7 @@
         <v>45842</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30033,7 +30033,7 @@
         <v>45842</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30106,7 +30106,7 @@
         <v>45118</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30179,7 +30179,7 @@
         <v>45086</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30252,7 +30252,7 @@
         <v>45202</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30325,7 +30325,7 @@
         <v>45387</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30398,7 +30398,7 @@
         <v>45387</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30471,7 +30471,7 @@
         <v>45099</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30544,7 +30544,7 @@
         <v>44477</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30617,7 +30617,7 @@
         <v>45628</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30690,7 +30690,7 @@
         <v>45861</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30763,7 +30763,7 @@
         <v>45831</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30836,7 +30836,7 @@
         <v>44544</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30909,7 +30909,7 @@
         <v>46099</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30982,7 +30982,7 @@
         <v>45779</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31055,7 +31055,7 @@
         <v>45764</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31128,7 +31128,7 @@
         <v>45544</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31201,7 +31201,7 @@
         <v>46177</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31274,7 +31274,7 @@
         <v>45915</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31347,7 +31347,7 @@
         <v>45104</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31425,7 +31425,7 @@
         <v>44991</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>45260</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31571,7 +31571,7 @@
         <v>45713</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31644,7 +31644,7 @@
         <v>45076</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31722,7 +31722,7 @@
         <v>45400</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31795,7 +31795,7 @@
         <v>45874</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31868,7 +31868,7 @@
         <v>46185</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31941,7 +31941,7 @@
         <v>45110</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32019,7 +32019,7 @@
         <v>45335</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32097,7 +32097,7 @@
         <v>46188</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32170,7 +32170,7 @@
         <v>44543</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32243,7 +32243,7 @@
         <v>45618</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32316,7 +32316,7 @@
         <v>45173</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32389,7 +32389,7 @@
         <v>45534</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32462,7 +32462,7 @@
         <v>45540</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>46178</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32608,7 +32608,7 @@
         <v>46036</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         <v>44818</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32754,7 +32754,7 @@
         <v>45195</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32827,7 +32827,7 @@
         <v>45114</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32900,7 +32900,7 @@
         <v>45205</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32973,7 +32973,7 @@
         <v>45531</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33046,7 +33046,7 @@
         <v>46197</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33119,7 +33119,7 @@
         <v>45090</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33192,7 +33192,7 @@
         <v>45090</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33265,7 +33265,7 @@
         <v>45618</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33338,7 +33338,7 @@
         <v>45189</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33411,7 +33411,7 @@
         <v>44645</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>46198</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33557,7 +33557,7 @@
         <v>46199</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33630,7 +33630,7 @@
         <v>46202</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33703,7 +33703,7 @@
         <v>46203</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33776,7 +33776,7 @@
         <v>45785</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33849,7 +33849,7 @@
         <v>45707</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33922,7 +33922,7 @@
         <v>44529</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33995,7 +33995,7 @@
         <v>45327</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34068,7 +34068,7 @@
         <v>45345</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34141,7 +34141,7 @@
         <v>46139</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34214,7 +34214,7 @@
         <v>45027</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34287,7 +34287,7 @@
         <v>44819</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34360,7 +34360,7 @@
         <v>45070</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34438,7 +34438,7 @@
         <v>46154</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34511,7 +34511,7 @@
         <v>45182</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34584,7 +34584,7 @@
         <v>44656</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34657,7 +34657,7 @@
         <v>45402</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34735,7 +34735,7 @@
         <v>46254</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34813,7 +34813,7 @@
         <v>45406</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34886,7 +34886,7 @@
         <v>46253</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34959,7 +34959,7 @@
         <v>45182</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35032,7 +35032,7 @@
         <v>45363</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35105,7 +35105,7 @@
         <v>46253</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35178,7 +35178,7 @@
         <v>46254</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35256,7 +35256,7 @@
         <v>45629</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35329,7 +35329,7 @@
         <v>45149</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35402,7 +35402,7 @@
         <v>45149</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35475,7 +35475,7 @@
         <v>45703</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35548,7 +35548,7 @@
         <v>45125</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35621,7 +35621,7 @@
         <v>45154</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>45574</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35772,7 +35772,7 @@
         <v>46212</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35845,7 +35845,7 @@
         <v>46259</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35918,7 +35918,7 @@
         <v>45233</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35991,7 +35991,7 @@
         <v>45233</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36064,7 +36064,7 @@
         <v>45198</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36137,7 +36137,7 @@
         <v>46111</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36210,7 +36210,7 @@
         <v>46063</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36283,7 +36283,7 @@
         <v>45189</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36356,7 +36356,7 @@
         <v>45685</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36429,7 +36429,7 @@
         <v>45169</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36502,7 +36502,7 @@
         <v>44861</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36575,7 +36575,7 @@
         <v>45119</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36648,7 +36648,7 @@
         <v>45153</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36721,7 +36721,7 @@
         <v>45233</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36794,7 +36794,7 @@
         <v>45173</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36867,7 +36867,7 @@
         <v>45173</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36940,7 +36940,7 @@
         <v>45246</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37013,7 +37013,7 @@
         <v>44782</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37086,7 +37086,7 @@
         <v>45252</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37159,7 +37159,7 @@
         <v>46223</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37232,7 +37232,7 @@
         <v>45170</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37305,7 +37305,7 @@
         <v>44973</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37378,7 +37378,7 @@
         <v>45356</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37451,7 +37451,7 @@
         <v>44847</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37524,7 +37524,7 @@
         <v>45454</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37597,7 +37597,7 @@
         <v>44690</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37670,7 +37670,7 @@
         <v>45349</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37743,7 +37743,7 @@
         <v>46272</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37816,7 +37816,7 @@
         <v>45212</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37889,7 +37889,7 @@
         <v>45007</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37962,7 +37962,7 @@
         <v>45007</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38035,7 +38035,7 @@
         <v>46269</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38108,7 +38108,7 @@
         <v>45266</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38181,7 +38181,7 @@
         <v>45323</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38254,7 +38254,7 @@
         <v>46273</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38327,7 +38327,7 @@
         <v>46273</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38400,7 +38400,7 @@
         <v>46274</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38473,7 +38473,7 @@
         <v>44963</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38546,7 +38546,7 @@
         <v>44963</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38619,7 +38619,7 @@
         <v>46276</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38692,7 +38692,7 @@
         <v>46275</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38765,7 +38765,7 @@
         <v>46276</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38838,7 +38838,7 @@
         <v>45093</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38911,7 +38911,7 @@
         <v>45229</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38984,7 +38984,7 @@
         <v>44864</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39057,7 +39057,7 @@
         <v>46281</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39130,7 +39130,7 @@
         <v>45308</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39203,7 +39203,7 @@
         <v>46281</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39276,7 +39276,7 @@
         <v>45595</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39349,7 +39349,7 @@
         <v>46063</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39422,7 +39422,7 @@
         <v>46281</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39495,7 +39495,7 @@
         <v>44658</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39568,7 +39568,7 @@
         <v>44858</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39641,7 +39641,7 @@
         <v>45336</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39714,7 +39714,7 @@
         <v>45524</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39787,7 +39787,7 @@
         <v>44712</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39860,7 +39860,7 @@
         <v>44803</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39933,7 +39933,7 @@
         <v>44978</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40006,7 +40006,7 @@
         <v>44939</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40079,7 +40079,7 @@
         <v>46247</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40152,7 +40152,7 @@
         <v>46290</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40225,7 +40225,7 @@
         <v>44497</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40298,7 +40298,7 @@
         <v>46247</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40376,7 +40376,7 @@
         <v>45607</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40449,7 +40449,7 @@
         <v>45075</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40522,7 +40522,7 @@
         <v>44855</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40595,7 +40595,7 @@
         <v>45091</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40668,7 +40668,7 @@
         <v>45252</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40741,7 +40741,7 @@
         <v>45470</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40814,7 +40814,7 @@
         <v>45034</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40887,7 +40887,7 @@
         <v>44895</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40960,7 +40960,7 @@
         <v>45540</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41033,7 +41033,7 @@
         <v>45418</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41106,7 +41106,7 @@
         <v>44971</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41179,7 +41179,7 @@
         <v>45090</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41252,7 +41252,7 @@
         <v>44529</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41325,7 +41325,7 @@
         <v>45156</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41398,7 +41398,7 @@
         <v>44993</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41471,7 +41471,7 @@
         <v>45625</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41544,7 +41544,7 @@
         <v>45212</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41617,7 +41617,7 @@
         <v>45564</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41690,7 +41690,7 @@
         <v>45411</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41763,7 +41763,7 @@
         <v>45067</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41836,7 +41836,7 @@
         <v>45246</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41909,7 +41909,7 @@
         <v>44846</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41982,7 +41982,7 @@
         <v>45173</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42055,7 +42055,7 @@
         <v>45174</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42128,7 +42128,7 @@
         <v>45097</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42201,7 +42201,7 @@
         <v>45219</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42274,7 +42274,7 @@
         <v>45628</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42347,7 +42347,7 @@
         <v>45272</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42420,7 +42420,7 @@
         <v>45113</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42493,7 +42493,7 @@
         <v>45173</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42566,7 +42566,7 @@
         <v>44971</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42639,7 +42639,7 @@
         <v>45735</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42712,7 +42712,7 @@
         <v>45175</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42785,7 +42785,7 @@
         <v>45188</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42858,7 +42858,7 @@
         <v>45181</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42931,7 +42931,7 @@
         <v>45439</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43004,7 +43004,7 @@
         <v>45246</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43077,7 +43077,7 @@
         <v>45551</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43150,7 +43150,7 @@
         <v>45558</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43228,7 +43228,7 @@
         <v>45775</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43301,7 +43301,7 @@
         <v>45443</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43374,7 +43374,7 @@
         <v>45782</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43452,7 +43452,7 @@
         <v>45566</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43525,7 +43525,7 @@
         <v>45664</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43598,7 +43598,7 @@
         <v>45363</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43671,7 +43671,7 @@
         <v>45785</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43744,7 +43744,7 @@
         <v>45664</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43817,7 +43817,7 @@
         <v>45730</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43890,7 +43890,7 @@
         <v>45792</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43968,7 +43968,7 @@
         <v>45791</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44041,7 +44041,7 @@
         <v>44607</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44114,7 +44114,7 @@
         <v>44587</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44187,7 +44187,7 @@
         <v>45387</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44260,7 +44260,7 @@
         <v>45373</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44333,7 +44333,7 @@
         <v>45345</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44406,7 +44406,7 @@
         <v>45440</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44479,7 +44479,7 @@
         <v>45595</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44552,7 +44552,7 @@
         <v>44806</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44625,7 +44625,7 @@
         <v>44965</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44698,7 +44698,7 @@
         <v>44531</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44771,7 +44771,7 @@
         <v>44957</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44844,7 +44844,7 @@
         <v>45345</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44917,7 +44917,7 @@
         <v>45345</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44990,7 +44990,7 @@
         <v>45685</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45063,7 +45063,7 @@
         <v>45358</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45136,7 +45136,7 @@
         <v>44957</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45209,7 +45209,7 @@
         <v>45824</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45282,7 +45282,7 @@
         <v>44071</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45355,7 +45355,7 @@
         <v>45890</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45428,7 +45428,7 @@
         <v>45902</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45501,7 +45501,7 @@
         <v>46058</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45574,7 +45574,7 @@
         <v>46062</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45647,7 +45647,7 @@
         <v>46062</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45720,7 +45720,7 @@
         <v>46063</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45793,7 +45793,7 @@
         <v>46062</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45866,7 +45866,7 @@
         <v>46062</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45939,7 +45939,7 @@
         <v>46065</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46012,7 +46012,7 @@
         <v>46110</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>

--- a/Översikt KALMAR.xlsx
+++ b/Översikt KALMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45209</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>44876</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45952</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>45345</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>46066</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>44876</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>46058</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>44979</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>44601</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>44876</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>45947</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>44489</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>44476</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>45915</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>44876</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>45324</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>45664</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>45561</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>46085</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>44522</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>44951</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>44984</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>45463</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>44970</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>45953</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>44489</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>44853</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>44993</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>44979</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         <v>45254</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>45684</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>44595</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>44475</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>44489</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>44784</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>45943</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         <v>45118</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>44575</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         <v>45114</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
         <v>44785</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>44951</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         <v>44785</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>45044</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>45363</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>44616</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5795,7 +5795,7 @@
         <v>44595</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>45903</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>45954</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>44517</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>45190</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>44517</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
         <v>45243</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>44802</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>45924</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         <v>45105</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>44994</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
         <v>44994</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         <v>46119</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>46119</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7302,7 +7302,7 @@
         <v>45874</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>46055</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7514,7 +7514,7 @@
         <v>45722</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>44796</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         <v>44970</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7841,7 +7841,7 @@
         <v>46049</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         <v>45275</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>45575</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>45314</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>44827</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8380,7 +8380,7 @@
         <v>45966</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>46279</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8596,7 +8596,7 @@
         <v>46245</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>45475</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         <v>45448</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         <v>44623</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9019,7 +9019,7 @@
         <v>45083</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9124,7 +9124,7 @@
         <v>44855</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
         <v>45163</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         <v>44915</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>45086</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         <v>44914</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9658,7 +9658,7 @@
         <v>45574</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9768,7 +9768,7 @@
         <v>45007</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>44740</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
         <v>46119</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>44810</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10188,7 +10188,7 @@
         <v>45917</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>44575</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10402,7 +10402,7 @@
         <v>44991</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10507,7 +10507,7 @@
         <v>45069</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10612,7 +10612,7 @@
         <v>45007</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10721,7 +10721,7 @@
         <v>45264</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10830,7 +10830,7 @@
         <v>44895</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>44466</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11044,7 +11044,7 @@
         <v>45868</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         <v>46177</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>45117</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11368,7 +11368,7 @@
         <v>46188</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
         <v>46199</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>45180</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11687,7 +11687,7 @@
         <v>45167</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>46258</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11897,7 +11897,7 @@
         <v>46247</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12002,7 +12002,7 @@
         <v>46247</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12116,7 +12116,7 @@
         <v>45007</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>44931</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12326,7 +12326,7 @@
         <v>44949</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12431,7 +12431,7 @@
         <v>44931</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12536,7 +12536,7 @@
         <v>45090</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12641,7 +12641,7 @@
         <v>45063</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12755,7 +12755,7 @@
         <v>45544</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12864,7 +12864,7 @@
         <v>45775</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12969,7 +12969,7 @@
         <v>45782</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>45454</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13184,7 +13184,7 @@
         <v>45791</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>44586</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13394,7 +13394,7 @@
         <v>44810</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13504,7 +13504,7 @@
         <v>45611</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13609,7 +13609,7 @@
         <v>45373</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13718,7 +13718,7 @@
         <v>46063</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>46087</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13928,7 +13928,7 @@
         <v>44643</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14001,7 +14001,7 @@
         <v>44823</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
         <v>44497</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14147,7 +14147,7 @@
         <v>44629</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>44505</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14293,7 +14293,7 @@
         <v>44852</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14366,7 +14366,7 @@
         <v>44684</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
         <v>44539</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14512,7 +14512,7 @@
         <v>44498</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14585,7 +14585,7 @@
         <v>44498</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14658,7 +14658,7 @@
         <v>44489</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14731,7 +14731,7 @@
         <v>44525</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14804,7 +14804,7 @@
         <v>44823</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14877,7 +14877,7 @@
         <v>44790</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14950,7 +14950,7 @@
         <v>44531</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>44602</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15096,7 +15096,7 @@
         <v>44858</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15169,7 +15169,7 @@
         <v>44522</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>44823</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15315,7 +15315,7 @@
         <v>44818</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15388,7 +15388,7 @@
         <v>44858</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15461,7 +15461,7 @@
         <v>44858</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15534,7 +15534,7 @@
         <v>44852</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15607,7 +15607,7 @@
         <v>44858</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15680,7 +15680,7 @@
         <v>44615</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15753,7 +15753,7 @@
         <v>44586</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>44502</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15899,7 +15899,7 @@
         <v>44552</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15972,7 +15972,7 @@
         <v>44482</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>44620</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16118,7 +16118,7 @@
         <v>44625</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16191,7 +16191,7 @@
         <v>44784</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16264,7 +16264,7 @@
         <v>44654</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16337,7 +16337,7 @@
         <v>44855</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16410,7 +16410,7 @@
         <v>44858</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16483,7 +16483,7 @@
         <v>44732</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16556,7 +16556,7 @@
         <v>44810</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16629,7 +16629,7 @@
         <v>44858</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>44511</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16775,7 +16775,7 @@
         <v>45341</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16848,7 +16848,7 @@
         <v>45341</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>45324</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16994,7 +16994,7 @@
         <v>45044</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17067,7 +17067,7 @@
         <v>45267</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17140,7 +17140,7 @@
         <v>45716</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17213,7 +17213,7 @@
         <v>45215</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17286,7 +17286,7 @@
         <v>45334</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17359,7 +17359,7 @@
         <v>44782</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17432,7 +17432,7 @@
         <v>45097</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17505,7 +17505,7 @@
         <v>45209</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17578,7 +17578,7 @@
         <v>45209</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17651,7 +17651,7 @@
         <v>45091</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
         <v>45243</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17797,7 +17797,7 @@
         <v>45378</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17870,7 +17870,7 @@
         <v>45250</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17943,7 +17943,7 @@
         <v>44963</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18016,7 +18016,7 @@
         <v>45387</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18089,7 +18089,7 @@
         <v>45387</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18162,7 +18162,7 @@
         <v>45268</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18235,7 +18235,7 @@
         <v>44914</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18308,7 +18308,7 @@
         <v>46013</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18381,7 +18381,7 @@
         <v>45097</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18454,7 +18454,7 @@
         <v>45306</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>45096</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
         <v>46026</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18673,7 +18673,7 @@
         <v>45141</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18746,7 +18746,7 @@
         <v>45254</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18819,7 +18819,7 @@
         <v>45630</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18892,7 +18892,7 @@
         <v>45476</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18965,7 +18965,7 @@
         <v>44994</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>44872</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19111,7 +19111,7 @@
         <v>45796</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         <v>45789</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
         <v>45636</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>45492</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19403,7 +19403,7 @@
         <v>45796</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19476,7 +19476,7 @@
         <v>45273</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19549,7 +19549,7 @@
         <v>45246</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>45246</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19695,7 +19695,7 @@
         <v>44895</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19768,7 +19768,7 @@
         <v>44564</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19841,7 +19841,7 @@
         <v>44988</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19914,7 +19914,7 @@
         <v>44862</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19987,7 +19987,7 @@
         <v>46048</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20060,7 +20060,7 @@
         <v>46049</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20133,7 +20133,7 @@
         <v>45153</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20206,7 +20206,7 @@
         <v>45050</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20279,7 +20279,7 @@
         <v>44909</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20352,7 +20352,7 @@
         <v>45720</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>44924</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20498,7 +20498,7 @@
         <v>45840</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20571,7 +20571,7 @@
         <v>46054</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20644,7 +20644,7 @@
         <v>46054</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20717,7 +20717,7 @@
         <v>45912</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20790,7 +20790,7 @@
         <v>45912</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20863,7 +20863,7 @@
         <v>45548</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20936,7 +20936,7 @@
         <v>46062</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21009,7 +21009,7 @@
         <v>45551</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21082,7 +21082,7 @@
         <v>46063</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21155,7 +21155,7 @@
         <v>46063</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21228,7 +21228,7 @@
         <v>44595</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21301,7 +21301,7 @@
         <v>44595</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21374,7 +21374,7 @@
         <v>45028</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21447,7 +21447,7 @@
         <v>44502</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21520,7 +21520,7 @@
         <v>46070</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21593,7 +21593,7 @@
         <v>45695</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21666,7 +21666,7 @@
         <v>45924</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21739,7 +21739,7 @@
         <v>45923</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21812,7 +21812,7 @@
         <v>45104</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21885,7 +21885,7 @@
         <v>46070</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21958,7 +21958,7 @@
         <v>45930</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22031,7 +22031,7 @@
         <v>44971</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22104,7 +22104,7 @@
         <v>45805</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22177,7 +22177,7 @@
         <v>44539</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22250,7 +22250,7 @@
         <v>45932</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22323,7 +22323,7 @@
         <v>45167</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22396,7 +22396,7 @@
         <v>45058</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22469,7 +22469,7 @@
         <v>45720</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22542,7 +22542,7 @@
         <v>44915</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22615,7 +22615,7 @@
         <v>45229</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22688,7 +22688,7 @@
         <v>46092</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22761,7 +22761,7 @@
         <v>46092</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22834,7 +22834,7 @@
         <v>46093</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22907,7 +22907,7 @@
         <v>45939</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22980,7 +22980,7 @@
         <v>46099</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23053,7 +23053,7 @@
         <v>45219</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23126,7 +23126,7 @@
         <v>45205</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23199,7 +23199,7 @@
         <v>45006</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23272,7 +23272,7 @@
         <v>44959</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23345,7 +23345,7 @@
         <v>45061</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23418,7 +23418,7 @@
         <v>45091</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23491,7 +23491,7 @@
         <v>45156</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23564,7 +23564,7 @@
         <v>44816</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23637,7 +23637,7 @@
         <v>45272</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23710,7 +23710,7 @@
         <v>45624</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23788,7 +23788,7 @@
         <v>45812</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23861,7 +23861,7 @@
         <v>44993</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23934,7 +23934,7 @@
         <v>46108</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24007,7 +24007,7 @@
         <v>46112</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24080,7 +24080,7 @@
         <v>44909</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24153,7 +24153,7 @@
         <v>46119</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24226,7 +24226,7 @@
         <v>46119</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         <v>45624</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24372,7 +24372,7 @@
         <v>45624</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24450,7 +24450,7 @@
         <v>44952</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24523,7 +24523,7 @@
         <v>44966</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24596,7 +24596,7 @@
         <v>44984</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24689,7 +24689,7 @@
         <v>44984</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24762,7 +24762,7 @@
         <v>44973</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24835,7 +24835,7 @@
         <v>45618</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24908,7 +24908,7 @@
         <v>45001</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24981,7 +24981,7 @@
         <v>45978</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25054,7 +25054,7 @@
         <v>45680</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25127,7 +25127,7 @@
         <v>44993</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25200,7 +25200,7 @@
         <v>45930</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25273,7 +25273,7 @@
         <v>44732</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25346,7 +25346,7 @@
         <v>44924</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25419,7 +25419,7 @@
         <v>45161</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25492,7 +25492,7 @@
         <v>46134</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25565,7 +25565,7 @@
         <v>46134</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25638,7 +25638,7 @@
         <v>45114</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25711,7 +25711,7 @@
         <v>46036</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25784,7 +25784,7 @@
         <v>46009</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25857,7 +25857,7 @@
         <v>45544</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25935,7 +25935,7 @@
         <v>45688</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26008,7 +26008,7 @@
         <v>45764</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26081,7 +26081,7 @@
         <v>45923</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26154,7 +26154,7 @@
         <v>45688</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26227,7 +26227,7 @@
         <v>45915</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26300,7 +26300,7 @@
         <v>46139</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26373,7 +26373,7 @@
         <v>44574</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26446,7 +26446,7 @@
         <v>45719</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26524,7 +26524,7 @@
         <v>44824</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26597,7 +26597,7 @@
         <v>44564</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26670,7 +26670,7 @@
         <v>45091</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26743,7 +26743,7 @@
         <v>44988</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26816,7 +26816,7 @@
         <v>44482</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26889,7 +26889,7 @@
         <v>46008</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26962,7 +26962,7 @@
         <v>46008</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27035,7 +27035,7 @@
         <v>45229</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27108,7 +27108,7 @@
         <v>45028</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27181,7 +27181,7 @@
         <v>46010</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27254,7 +27254,7 @@
         <v>44823</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27327,7 +27327,7 @@
         <v>44823</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27400,7 +27400,7 @@
         <v>45824</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27473,7 +27473,7 @@
         <v>44617</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27546,7 +27546,7 @@
         <v>44617</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27619,7 +27619,7 @@
         <v>46139</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27692,7 +27692,7 @@
         <v>45205</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27765,7 +27765,7 @@
         <v>45034</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27838,7 +27838,7 @@
         <v>45727</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27911,7 +27911,7 @@
         <v>45239</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27989,7 +27989,7 @@
         <v>44629</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28062,7 +28062,7 @@
         <v>46099</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28135,7 +28135,7 @@
         <v>45180</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28208,7 +28208,7 @@
         <v>45540</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28281,7 +28281,7 @@
         <v>44502</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28354,7 +28354,7 @@
         <v>44566</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28427,7 +28427,7 @@
         <v>45233</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28500,7 +28500,7 @@
         <v>44846</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28573,7 +28573,7 @@
         <v>44939</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28646,7 +28646,7 @@
         <v>44882</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28719,7 +28719,7 @@
         <v>46155</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28792,7 +28792,7 @@
         <v>45092</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28865,7 +28865,7 @@
         <v>46155</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28938,7 +28938,7 @@
         <v>44914</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29011,7 +29011,7 @@
         <v>46155</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29084,7 +29084,7 @@
         <v>46160</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29157,7 +29157,7 @@
         <v>45099</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29230,7 +29230,7 @@
         <v>45236</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29303,7 +29303,7 @@
         <v>46160</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29376,7 +29376,7 @@
         <v>45903</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29449,7 +29449,7 @@
         <v>45104</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29522,7 +29522,7 @@
         <v>45104</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29595,7 +29595,7 @@
         <v>45104</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29668,7 +29668,7 @@
         <v>46162</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29741,7 +29741,7 @@
         <v>46162</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29814,7 +29814,7 @@
         <v>46162</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29887,7 +29887,7 @@
         <v>44924</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29960,7 +29960,7 @@
         <v>45842</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30033,7 +30033,7 @@
         <v>45842</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30106,7 +30106,7 @@
         <v>45118</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30179,7 +30179,7 @@
         <v>45086</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30252,7 +30252,7 @@
         <v>45202</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30325,7 +30325,7 @@
         <v>45387</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30398,7 +30398,7 @@
         <v>45387</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30471,7 +30471,7 @@
         <v>45099</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30544,7 +30544,7 @@
         <v>44477</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30617,7 +30617,7 @@
         <v>45628</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30690,7 +30690,7 @@
         <v>45861</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30763,7 +30763,7 @@
         <v>45831</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30836,7 +30836,7 @@
         <v>44544</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30909,7 +30909,7 @@
         <v>46099</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30982,7 +30982,7 @@
         <v>45779</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31055,7 +31055,7 @@
         <v>45764</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31128,7 +31128,7 @@
         <v>45544</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31201,7 +31201,7 @@
         <v>46177</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31274,7 +31274,7 @@
         <v>45915</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31347,7 +31347,7 @@
         <v>45104</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31425,7 +31425,7 @@
         <v>44991</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>45260</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31571,7 +31571,7 @@
         <v>45713</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31644,7 +31644,7 @@
         <v>45076</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31722,7 +31722,7 @@
         <v>45400</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31795,7 +31795,7 @@
         <v>45874</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31868,7 +31868,7 @@
         <v>46185</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31941,7 +31941,7 @@
         <v>45110</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32019,7 +32019,7 @@
         <v>45335</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32097,7 +32097,7 @@
         <v>46188</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32170,7 +32170,7 @@
         <v>44543</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32243,7 +32243,7 @@
         <v>45618</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32316,7 +32316,7 @@
         <v>45173</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32389,7 +32389,7 @@
         <v>45534</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32462,7 +32462,7 @@
         <v>45540</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>46178</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32608,7 +32608,7 @@
         <v>46036</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         <v>44818</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32754,7 +32754,7 @@
         <v>45195</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32827,7 +32827,7 @@
         <v>45114</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32900,7 +32900,7 @@
         <v>45205</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32973,7 +32973,7 @@
         <v>45531</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33046,7 +33046,7 @@
         <v>46197</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33119,7 +33119,7 @@
         <v>45090</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33192,7 +33192,7 @@
         <v>45090</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33265,7 +33265,7 @@
         <v>45618</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33338,7 +33338,7 @@
         <v>45189</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33411,7 +33411,7 @@
         <v>44645</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>46198</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33557,7 +33557,7 @@
         <v>46199</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33630,7 +33630,7 @@
         <v>46202</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33703,7 +33703,7 @@
         <v>46203</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33776,7 +33776,7 @@
         <v>45785</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33849,7 +33849,7 @@
         <v>45707</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33922,7 +33922,7 @@
         <v>44529</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33995,7 +33995,7 @@
         <v>45327</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34068,7 +34068,7 @@
         <v>45345</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34141,7 +34141,7 @@
         <v>46139</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34214,7 +34214,7 @@
         <v>45027</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34287,7 +34287,7 @@
         <v>44819</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34360,7 +34360,7 @@
         <v>45070</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34438,7 +34438,7 @@
         <v>46154</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34511,7 +34511,7 @@
         <v>45182</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34584,7 +34584,7 @@
         <v>44656</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34657,7 +34657,7 @@
         <v>45402</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34735,7 +34735,7 @@
         <v>46254</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34813,7 +34813,7 @@
         <v>45406</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34886,7 +34886,7 @@
         <v>46253</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34959,7 +34959,7 @@
         <v>45182</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35032,7 +35032,7 @@
         <v>45363</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35105,7 +35105,7 @@
         <v>46253</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35178,7 +35178,7 @@
         <v>46254</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35256,7 +35256,7 @@
         <v>45629</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35329,7 +35329,7 @@
         <v>45149</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35402,7 +35402,7 @@
         <v>45149</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35475,7 +35475,7 @@
         <v>45703</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35548,7 +35548,7 @@
         <v>45125</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35621,7 +35621,7 @@
         <v>45154</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>45574</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35772,7 +35772,7 @@
         <v>46212</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35845,7 +35845,7 @@
         <v>46259</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35918,7 +35918,7 @@
         <v>45233</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35991,7 +35991,7 @@
         <v>45233</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36064,7 +36064,7 @@
         <v>45198</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36137,7 +36137,7 @@
         <v>46111</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36210,7 +36210,7 @@
         <v>46063</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36283,7 +36283,7 @@
         <v>45189</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36356,7 +36356,7 @@
         <v>45685</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36429,7 +36429,7 @@
         <v>45169</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36502,7 +36502,7 @@
         <v>44861</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36575,7 +36575,7 @@
         <v>45119</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36648,7 +36648,7 @@
         <v>45153</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36721,7 +36721,7 @@
         <v>45233</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36794,7 +36794,7 @@
         <v>45173</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36867,7 +36867,7 @@
         <v>45173</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36940,7 +36940,7 @@
         <v>45246</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37013,7 +37013,7 @@
         <v>44782</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37086,7 +37086,7 @@
         <v>45252</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37159,7 +37159,7 @@
         <v>46223</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37232,7 +37232,7 @@
         <v>45170</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37305,7 +37305,7 @@
         <v>44973</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37378,7 +37378,7 @@
         <v>45356</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37451,7 +37451,7 @@
         <v>44847</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37524,7 +37524,7 @@
         <v>45454</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37597,7 +37597,7 @@
         <v>44690</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37670,7 +37670,7 @@
         <v>45349</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37743,7 +37743,7 @@
         <v>46272</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37816,7 +37816,7 @@
         <v>45212</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37889,7 +37889,7 @@
         <v>45007</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37962,7 +37962,7 @@
         <v>45007</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38035,7 +38035,7 @@
         <v>46269</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38108,7 +38108,7 @@
         <v>45266</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38181,7 +38181,7 @@
         <v>45323</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38254,7 +38254,7 @@
         <v>46273</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38327,7 +38327,7 @@
         <v>46273</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38400,7 +38400,7 @@
         <v>46274</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38473,7 +38473,7 @@
         <v>44963</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38546,7 +38546,7 @@
         <v>44963</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38619,7 +38619,7 @@
         <v>46276</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38692,7 +38692,7 @@
         <v>46275</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38765,7 +38765,7 @@
         <v>46276</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38838,7 +38838,7 @@
         <v>45093</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38911,7 +38911,7 @@
         <v>45229</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38984,7 +38984,7 @@
         <v>44864</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39057,7 +39057,7 @@
         <v>46281</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39130,7 +39130,7 @@
         <v>45308</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39203,7 +39203,7 @@
         <v>46281</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39276,7 +39276,7 @@
         <v>45595</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39349,7 +39349,7 @@
         <v>46063</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39422,7 +39422,7 @@
         <v>46281</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39495,7 +39495,7 @@
         <v>44658</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39568,7 +39568,7 @@
         <v>44858</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39641,7 +39641,7 @@
         <v>45336</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39714,7 +39714,7 @@
         <v>45524</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39787,7 +39787,7 @@
         <v>44712</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39860,7 +39860,7 @@
         <v>44803</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39933,7 +39933,7 @@
         <v>44978</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40006,7 +40006,7 @@
         <v>44939</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40079,7 +40079,7 @@
         <v>46247</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40152,7 +40152,7 @@
         <v>46290</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40225,7 +40225,7 @@
         <v>44497</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40298,7 +40298,7 @@
         <v>46247</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40376,7 +40376,7 @@
         <v>45607</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40449,7 +40449,7 @@
         <v>45075</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40522,7 +40522,7 @@
         <v>44855</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40595,7 +40595,7 @@
         <v>45091</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40668,7 +40668,7 @@
         <v>45252</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40741,7 +40741,7 @@
         <v>45470</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40814,7 +40814,7 @@
         <v>45034</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40887,7 +40887,7 @@
         <v>44895</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40960,7 +40960,7 @@
         <v>45540</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41033,7 +41033,7 @@
         <v>45418</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41106,7 +41106,7 @@
         <v>44971</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41179,7 +41179,7 @@
         <v>45090</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41252,7 +41252,7 @@
         <v>44529</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41325,7 +41325,7 @@
         <v>45156</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41398,7 +41398,7 @@
         <v>44993</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41471,7 +41471,7 @@
         <v>45625</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41544,7 +41544,7 @@
         <v>45212</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41617,7 +41617,7 @@
         <v>45564</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41690,7 +41690,7 @@
         <v>45411</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41763,7 +41763,7 @@
         <v>45067</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41836,7 +41836,7 @@
         <v>45246</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41909,7 +41909,7 @@
         <v>44846</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41982,7 +41982,7 @@
         <v>45173</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42055,7 +42055,7 @@
         <v>45174</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42128,7 +42128,7 @@
         <v>45097</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42201,7 +42201,7 @@
         <v>45219</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42274,7 +42274,7 @@
         <v>45628</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42347,7 +42347,7 @@
         <v>45272</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42420,7 +42420,7 @@
         <v>45113</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42493,7 +42493,7 @@
         <v>45173</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42566,7 +42566,7 @@
         <v>44971</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42639,7 +42639,7 @@
         <v>45735</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42712,7 +42712,7 @@
         <v>45175</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42785,7 +42785,7 @@
         <v>45188</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42858,7 +42858,7 @@
         <v>45181</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42931,7 +42931,7 @@
         <v>45439</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43004,7 +43004,7 @@
         <v>45246</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43077,7 +43077,7 @@
         <v>45551</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43150,7 +43150,7 @@
         <v>45558</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43228,7 +43228,7 @@
         <v>45775</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43301,7 +43301,7 @@
         <v>45443</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43374,7 +43374,7 @@
         <v>45782</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43452,7 +43452,7 @@
         <v>45566</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43525,7 +43525,7 @@
         <v>45664</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43598,7 +43598,7 @@
         <v>45363</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43671,7 +43671,7 @@
         <v>45785</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43744,7 +43744,7 @@
         <v>45664</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43817,7 +43817,7 @@
         <v>45730</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43890,7 +43890,7 @@
         <v>45792</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43968,7 +43968,7 @@
         <v>45791</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44041,7 +44041,7 @@
         <v>44607</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44114,7 +44114,7 @@
         <v>44587</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44187,7 +44187,7 @@
         <v>45387</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44260,7 +44260,7 @@
         <v>45373</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44333,7 +44333,7 @@
         <v>45345</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44406,7 +44406,7 @@
         <v>45440</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44479,7 +44479,7 @@
         <v>45595</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44552,7 +44552,7 @@
         <v>44806</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44625,7 +44625,7 @@
         <v>44965</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44698,7 +44698,7 @@
         <v>44531</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44771,7 +44771,7 @@
         <v>44957</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44844,7 +44844,7 @@
         <v>45345</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44917,7 +44917,7 @@
         <v>45345</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44990,7 +44990,7 @@
         <v>45685</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45063,7 +45063,7 @@
         <v>45358</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45136,7 +45136,7 @@
         <v>44957</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45209,7 +45209,7 @@
         <v>45824</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45282,7 +45282,7 @@
         <v>44071</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45355,7 +45355,7 @@
         <v>45890</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45428,7 +45428,7 @@
         <v>45902</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45501,7 +45501,7 @@
         <v>46058</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45574,7 +45574,7 @@
         <v>46062</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45647,7 +45647,7 @@
         <v>46062</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45720,7 +45720,7 @@
         <v>46063</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45793,7 +45793,7 @@
         <v>46062</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45866,7 +45866,7 @@
         <v>46062</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45939,7 +45939,7 @@
         <v>46065</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46012,7 +46012,7 @@
         <v>46110</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>

--- a/Översikt KALMAR.xlsx
+++ b/Översikt KALMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45209</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>44876</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45952</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>45345</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>46066</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>44876</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>46058</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>44979</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>44601</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>45947</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>44489</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>44876</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>44476</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>45915</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>44876</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>45324</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>45664</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>45561</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>46085</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>44522</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>44951</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>44984</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>45463</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>44970</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>45953</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>44993</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>44853</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>44979</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>45254</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
         <v>44489</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>45684</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>44595</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>44475</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>44489</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>44784</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>44785</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>44575</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
         <v>45943</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>44785</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
         <v>45118</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>45044</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>44951</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>45114</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>45363</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>44616</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5795,7 +5795,7 @@
         <v>44595</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>45903</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>45954</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>44517</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>44970</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>44802</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>45575</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6548,7 +6548,7 @@
         <v>45924</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>45243</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>46119</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
         <v>46119</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6972,7 +6972,7 @@
         <v>45722</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>44994</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7197,7 +7197,7 @@
         <v>44994</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>44796</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7409,7 +7409,7 @@
         <v>46055</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         <v>45874</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>46049</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>45190</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         <v>45105</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7943,7 +7943,7 @@
         <v>45966</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>46279</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8159,7 +8159,7 @@
         <v>46245</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8265,7 +8265,7 @@
         <v>45314</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>44517</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8481,7 +8481,7 @@
         <v>46253</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8591,7 +8591,7 @@
         <v>45275</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>44827</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         <v>45475</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8918,7 +8918,7 @@
         <v>45448</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         <v>44623</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>44740</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
         <v>44895</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9339,7 +9339,7 @@
         <v>45454</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         <v>45791</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
         <v>44575</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9658,7 +9658,7 @@
         <v>45264</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9767,7 +9767,7 @@
         <v>45574</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9877,7 +9877,7 @@
         <v>45163</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         <v>45086</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10091,7 +10091,7 @@
         <v>45007</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10196,7 +10196,7 @@
         <v>45180</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10305,7 +10305,7 @@
         <v>45167</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>45007</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10515,7 +10515,7 @@
         <v>46119</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10620,7 +10620,7 @@
         <v>44915</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10725,7 +10725,7 @@
         <v>44914</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10830,7 +10830,7 @@
         <v>45917</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>44991</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v>45868</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11145,7 +11145,7 @@
         <v>44810</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11250,7 +11250,7 @@
         <v>45069</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11355,7 +11355,7 @@
         <v>46177</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         <v>46188</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>44855</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11684,7 +11684,7 @@
         <v>46199</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         <v>45063</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11903,7 +11903,7 @@
         <v>44949</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
         <v>45117</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12113,7 +12113,7 @@
         <v>46258</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12218,7 +12218,7 @@
         <v>45083</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
         <v>46247</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12428,7 +12428,7 @@
         <v>46247</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12542,7 +12542,7 @@
         <v>44931</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12647,7 +12647,7 @@
         <v>45090</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
         <v>44931</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12857,7 +12857,7 @@
         <v>45007</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12966,7 +12966,7 @@
         <v>45775</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13071,7 +13071,7 @@
         <v>45544</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13180,7 +13180,7 @@
         <v>45782</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>44810</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         <v>44586</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>45611</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13610,7 +13610,7 @@
         <v>45373</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13719,7 +13719,7 @@
         <v>46063</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13824,7 +13824,7 @@
         <v>46087</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13929,7 +13929,7 @@
         <v>44643</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>44823</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14075,7 +14075,7 @@
         <v>44497</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>44505</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>44852</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14294,7 +14294,7 @@
         <v>44629</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14367,7 +14367,7 @@
         <v>44684</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>44539</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14513,7 +14513,7 @@
         <v>44498</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14586,7 +14586,7 @@
         <v>44498</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14659,7 +14659,7 @@
         <v>44489</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14732,7 +14732,7 @@
         <v>44525</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14805,7 +14805,7 @@
         <v>44823</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14878,7 +14878,7 @@
         <v>44790</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>44531</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15024,7 +15024,7 @@
         <v>44602</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15097,7 +15097,7 @@
         <v>44858</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15170,7 +15170,7 @@
         <v>44522</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15243,7 +15243,7 @@
         <v>44823</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15316,7 +15316,7 @@
         <v>44818</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15389,7 +15389,7 @@
         <v>44858</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>44858</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15535,7 +15535,7 @@
         <v>44852</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
         <v>44858</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15681,7 +15681,7 @@
         <v>44615</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15754,7 +15754,7 @@
         <v>44586</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>44502</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15900,7 +15900,7 @@
         <v>44552</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15973,7 +15973,7 @@
         <v>44482</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16046,7 +16046,7 @@
         <v>44620</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16119,7 +16119,7 @@
         <v>44625</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16192,7 +16192,7 @@
         <v>44784</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16265,7 +16265,7 @@
         <v>44654</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16338,7 +16338,7 @@
         <v>44855</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>44858</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16484,7 +16484,7 @@
         <v>44732</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16557,7 +16557,7 @@
         <v>44810</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16630,7 +16630,7 @@
         <v>44858</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16703,7 +16703,7 @@
         <v>44511</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16776,7 +16776,7 @@
         <v>45411</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16849,7 +16849,7 @@
         <v>44924</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16922,7 +16922,7 @@
         <v>44477</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16995,7 +16995,7 @@
         <v>44595</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17068,7 +17068,7 @@
         <v>44988</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17141,7 +17141,7 @@
         <v>45090</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17214,7 +17214,7 @@
         <v>45090</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17287,7 +17287,7 @@
         <v>45090</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17360,7 +17360,7 @@
         <v>45161</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17433,7 +17433,7 @@
         <v>45097</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17506,7 +17506,7 @@
         <v>45735</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17579,7 +17579,7 @@
         <v>45205</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17652,7 +17652,7 @@
         <v>45272</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17725,7 +17725,7 @@
         <v>44872</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17798,7 +17798,7 @@
         <v>45618</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17871,7 +17871,7 @@
         <v>44846</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17944,7 +17944,7 @@
         <v>44502</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18017,7 +18017,7 @@
         <v>45566</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18090,7 +18090,7 @@
         <v>44993</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18163,7 +18163,7 @@
         <v>45730</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18236,7 +18236,7 @@
         <v>44994</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18309,7 +18309,7 @@
         <v>45630</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18382,7 +18382,7 @@
         <v>45363</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18455,7 +18455,7 @@
         <v>45796</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18528,7 +18528,7 @@
         <v>45195</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
         <v>45099</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>46008</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18747,7 +18747,7 @@
         <v>46010</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18820,7 +18820,7 @@
         <v>46013</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18893,7 +18893,7 @@
         <v>45349</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18966,7 +18966,7 @@
         <v>44855</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19039,7 +19039,7 @@
         <v>45233</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19112,7 +19112,7 @@
         <v>45791</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19185,7 +19185,7 @@
         <v>45796</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19258,7 +19258,7 @@
         <v>44861</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19331,7 +19331,7 @@
         <v>44924</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19404,7 +19404,7 @@
         <v>46026</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19477,7 +19477,7 @@
         <v>44864</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19550,7 +19550,7 @@
         <v>44991</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19623,7 +19623,7 @@
         <v>45173</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19696,7 +19696,7 @@
         <v>45173</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19769,7 +19769,7 @@
         <v>45153</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>45792</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19920,7 +19920,7 @@
         <v>44712</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19993,7 +19993,7 @@
         <v>45219</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20066,7 +20066,7 @@
         <v>45250</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20139,7 +20139,7 @@
         <v>44993</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20212,7 +20212,7 @@
         <v>45840</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         <v>45219</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20358,7 +20358,7 @@
         <v>45912</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
         <v>45189</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20504,7 +20504,7 @@
         <v>45912</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>45272</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20650,7 +20650,7 @@
         <v>45028</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20723,7 +20723,7 @@
         <v>45400</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20796,7 +20796,7 @@
         <v>46048</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20869,7 +20869,7 @@
         <v>45239</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20947,7 +20947,7 @@
         <v>45720</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
         <v>46049</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21093,7 +21093,7 @@
         <v>45805</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21166,7 +21166,7 @@
         <v>44782</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21239,7 +21239,7 @@
         <v>45058</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21312,7 +21312,7 @@
         <v>46054</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21385,7 +21385,7 @@
         <v>46054</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21458,7 +21458,7 @@
         <v>45923</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21531,7 +21531,7 @@
         <v>45924</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21604,7 +21604,7 @@
         <v>45720</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21677,7 +21677,7 @@
         <v>45930</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21750,7 +21750,7 @@
         <v>45182</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21823,7 +21823,7 @@
         <v>46063</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21896,7 +21896,7 @@
         <v>46062</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21969,7 +21969,7 @@
         <v>46063</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22042,7 +22042,7 @@
         <v>45932</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22115,7 +22115,7 @@
         <v>45110</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22193,7 +22193,7 @@
         <v>45104</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22271,7 +22271,7 @@
         <v>46070</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22344,7 +22344,7 @@
         <v>46070</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22417,7 +22417,7 @@
         <v>45939</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22490,7 +22490,7 @@
         <v>45104</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22563,7 +22563,7 @@
         <v>45104</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22636,7 +22636,7 @@
         <v>45341</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22709,7 +22709,7 @@
         <v>44529</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22782,7 +22782,7 @@
         <v>45335</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22860,7 +22860,7 @@
         <v>45180</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22933,7 +22933,7 @@
         <v>44971</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23006,7 +23006,7 @@
         <v>45061</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23079,7 +23079,7 @@
         <v>45812</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23152,7 +23152,7 @@
         <v>44617</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23225,7 +23225,7 @@
         <v>44617</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23298,7 +23298,7 @@
         <v>44984</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23391,7 +23391,7 @@
         <v>44984</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23464,7 +23464,7 @@
         <v>46092</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23537,7 +23537,7 @@
         <v>46092</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23610,7 +23610,7 @@
         <v>45007</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23683,7 +23683,7 @@
         <v>45007</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23756,7 +23756,7 @@
         <v>45205</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23829,7 +23829,7 @@
         <v>46093</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23902,7 +23902,7 @@
         <v>45096</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23975,7 +23975,7 @@
         <v>45170</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24048,7 +24048,7 @@
         <v>46099</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24121,7 +24121,7 @@
         <v>45930</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24194,7 +24194,7 @@
         <v>45212</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24267,7 +24267,7 @@
         <v>45091</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24340,7 +24340,7 @@
         <v>45978</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24413,7 +24413,7 @@
         <v>46108</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24486,7 +24486,7 @@
         <v>44645</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24559,7 +24559,7 @@
         <v>46112</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24632,7 +24632,7 @@
         <v>44973</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24705,7 +24705,7 @@
         <v>46119</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24778,7 +24778,7 @@
         <v>46119</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24851,7 +24851,7 @@
         <v>44963</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24924,7 +24924,7 @@
         <v>45540</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24997,7 +24997,7 @@
         <v>44816</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25070,7 +25070,7 @@
         <v>44914</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25143,7 +25143,7 @@
         <v>45544</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25221,7 +25221,7 @@
         <v>45173</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25294,7 +25294,7 @@
         <v>45104</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25367,7 +25367,7 @@
         <v>45113</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25440,7 +25440,7 @@
         <v>45091</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25513,7 +25513,7 @@
         <v>45167</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25586,7 +25586,7 @@
         <v>45233</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25659,7 +25659,7 @@
         <v>46134</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25732,7 +25732,7 @@
         <v>45252</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25805,7 +25805,7 @@
         <v>45544</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25878,7 +25878,7 @@
         <v>46134</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25951,7 +25951,7 @@
         <v>45406</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26024,7 +26024,7 @@
         <v>45564</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26097,7 +26097,7 @@
         <v>45267</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26170,7 +26170,7 @@
         <v>46139</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26243,7 +26243,7 @@
         <v>45915</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26316,7 +26316,7 @@
         <v>44502</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26389,7 +26389,7 @@
         <v>45104</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26462,7 +26462,7 @@
         <v>45198</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26535,7 +26535,7 @@
         <v>44574</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26608,7 +26608,7 @@
         <v>45034</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26681,7 +26681,7 @@
         <v>45243</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26754,7 +26754,7 @@
         <v>46009</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26827,7 +26827,7 @@
         <v>44846</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26900,7 +26900,7 @@
         <v>45842</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26973,7 +26973,7 @@
         <v>45842</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27046,7 +27046,7 @@
         <v>45688</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27119,7 +27119,7 @@
         <v>45548</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27192,7 +27192,7 @@
         <v>45923</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27265,7 +27265,7 @@
         <v>45070</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27343,7 +27343,7 @@
         <v>44909</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27416,7 +27416,7 @@
         <v>45215</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27489,7 +27489,7 @@
         <v>46036</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27562,7 +27562,7 @@
         <v>45246</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27635,7 +27635,7 @@
         <v>45688</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27708,7 +27708,7 @@
         <v>45268</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27781,7 +27781,7 @@
         <v>46139</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27854,7 +27854,7 @@
         <v>45229</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27927,7 +27927,7 @@
         <v>45764</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28000,7 +28000,7 @@
         <v>45595</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28073,7 +28073,7 @@
         <v>45628</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28146,7 +28146,7 @@
         <v>45252</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28219,7 +28219,7 @@
         <v>45861</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28292,7 +28292,7 @@
         <v>45233</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28365,7 +28365,7 @@
         <v>45727</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28438,7 +28438,7 @@
         <v>44566</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28511,7 +28511,7 @@
         <v>45418</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28584,7 +28584,7 @@
         <v>45716</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         <v>45345</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28730,7 +28730,7 @@
         <v>45831</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28803,7 +28803,7 @@
         <v>45028</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28876,7 +28876,7 @@
         <v>45764</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28949,7 +28949,7 @@
         <v>45779</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29022,7 +29022,7 @@
         <v>45713</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29095,7 +29095,7 @@
         <v>44497</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29168,7 +29168,7 @@
         <v>45618</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29241,7 +29241,7 @@
         <v>45695</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29314,7 +29314,7 @@
         <v>45719</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29392,7 +29392,7 @@
         <v>45006</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29465,7 +29465,7 @@
         <v>46099</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29538,7 +29538,7 @@
         <v>45229</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29611,7 +29611,7 @@
         <v>44971</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29684,7 +29684,7 @@
         <v>45093</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29757,7 +29757,7 @@
         <v>45153</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29830,7 +29830,7 @@
         <v>44915</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29903,7 +29903,7 @@
         <v>44914</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29976,7 +29976,7 @@
         <v>44895</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30049,7 +30049,7 @@
         <v>45551</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30122,7 +30122,7 @@
         <v>46155</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30195,7 +30195,7 @@
         <v>45327</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30268,7 +30268,7 @@
         <v>46155</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30341,7 +30341,7 @@
         <v>44939</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30414,7 +30414,7 @@
         <v>45246</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30487,7 +30487,7 @@
         <v>45246</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30560,7 +30560,7 @@
         <v>45903</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30633,7 +30633,7 @@
         <v>44973</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30706,7 +30706,7 @@
         <v>45378</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>45175</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30852,7 +30852,7 @@
         <v>46160</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30925,7 +30925,7 @@
         <v>45173</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30998,7 +30998,7 @@
         <v>45236</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31071,7 +31071,7 @@
         <v>45874</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31144,7 +31144,7 @@
         <v>46160</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31217,7 +31217,7 @@
         <v>46162</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31290,7 +31290,7 @@
         <v>46162</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31363,7 +31363,7 @@
         <v>45306</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31436,7 +31436,7 @@
         <v>46162</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31509,7 +31509,7 @@
         <v>45091</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31582,7 +31582,7 @@
         <v>44629</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31655,7 +31655,7 @@
         <v>45785</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31728,7 +31728,7 @@
         <v>45624</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31806,7 +31806,7 @@
         <v>44862</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31879,7 +31879,7 @@
         <v>45574</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31957,7 +31957,7 @@
         <v>45097</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32030,7 +32030,7 @@
         <v>45628</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32103,7 +32103,7 @@
         <v>46099</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32176,7 +32176,7 @@
         <v>45707</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32249,7 +32249,7 @@
         <v>44539</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32322,7 +32322,7 @@
         <v>45154</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32395,7 +32395,7 @@
         <v>44529</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32468,7 +32468,7 @@
         <v>45789</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32541,7 +32541,7 @@
         <v>45492</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32614,7 +32614,7 @@
         <v>45182</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32687,7 +32687,7 @@
         <v>45915</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32760,7 +32760,7 @@
         <v>46177</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32833,7 +32833,7 @@
         <v>44909</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32906,7 +32906,7 @@
         <v>44988</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32979,7 +32979,7 @@
         <v>45624</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33057,7 +33057,7 @@
         <v>45266</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33130,7 +33130,7 @@
         <v>45625</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33203,7 +33203,7 @@
         <v>45629</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33276,7 +33276,7 @@
         <v>46188</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33349,7 +33349,7 @@
         <v>46185</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33422,7 +33422,7 @@
         <v>45188</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33495,7 +33495,7 @@
         <v>44803</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33568,7 +33568,7 @@
         <v>45402</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33646,7 +33646,7 @@
         <v>45680</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33719,7 +33719,7 @@
         <v>46036</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33792,7 +33792,7 @@
         <v>46178</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33865,7 +33865,7 @@
         <v>44966</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33938,7 +33938,7 @@
         <v>44595</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34011,7 +34011,7 @@
         <v>45097</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34084,7 +34084,7 @@
         <v>46197</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34157,7 +34157,7 @@
         <v>46198</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34230,7 +34230,7 @@
         <v>45685</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34303,7 +34303,7 @@
         <v>45044</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34376,7 +34376,7 @@
         <v>44939</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34449,7 +34449,7 @@
         <v>46199</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34522,7 +34522,7 @@
         <v>45470</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34595,7 +34595,7 @@
         <v>46202</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34668,7 +34668,7 @@
         <v>46203</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34741,7 +34741,7 @@
         <v>45125</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34814,7 +34814,7 @@
         <v>45387</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34887,7 +34887,7 @@
         <v>45387</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34960,7 +34960,7 @@
         <v>46139</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35033,7 +35033,7 @@
         <v>45476</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35106,7 +35106,7 @@
         <v>46154</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35179,7 +35179,7 @@
         <v>44882</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35252,7 +35252,7 @@
         <v>45624</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35325,7 +35325,7 @@
         <v>45534</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35398,7 +35398,7 @@
         <v>44959</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35471,7 +35471,7 @@
         <v>46212</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35544,7 +35544,7 @@
         <v>44544</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35617,7 +35617,7 @@
         <v>44847</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35690,7 +35690,7 @@
         <v>46259</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35763,7 +35763,7 @@
         <v>44543</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35836,7 +35836,7 @@
         <v>45202</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35909,7 +35909,7 @@
         <v>45050</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35982,7 +35982,7 @@
         <v>45308</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36055,7 +36055,7 @@
         <v>46063</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36128,7 +36128,7 @@
         <v>44993</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36201,7 +36201,7 @@
         <v>46111</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36274,7 +36274,7 @@
         <v>44782</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36347,7 +36347,7 @@
         <v>45075</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36420,7 +36420,7 @@
         <v>46223</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36493,7 +36493,7 @@
         <v>45114</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36566,7 +36566,7 @@
         <v>46269</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36639,7 +36639,7 @@
         <v>45173</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36712,7 +36712,7 @@
         <v>45387</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>45387</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36858,7 +36858,7 @@
         <v>46272</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36931,7 +36931,7 @@
         <v>46273</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37004,7 +37004,7 @@
         <v>46273</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37077,7 +37077,7 @@
         <v>46275</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37150,7 +37150,7 @@
         <v>46274</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37223,7 +37223,7 @@
         <v>46276</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37296,7 +37296,7 @@
         <v>46276</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37369,7 +37369,7 @@
         <v>44564</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37442,7 +37442,7 @@
         <v>46281</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37515,7 +37515,7 @@
         <v>45149</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37588,7 +37588,7 @@
         <v>45149</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37661,7 +37661,7 @@
         <v>45141</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37734,7 +37734,7 @@
         <v>46281</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37807,7 +37807,7 @@
         <v>44971</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37880,7 +37880,7 @@
         <v>45205</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37953,7 +37953,7 @@
         <v>45524</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38026,7 +38026,7 @@
         <v>45099</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38099,7 +38099,7 @@
         <v>45212</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38172,7 +38172,7 @@
         <v>46281</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38245,7 +38245,7 @@
         <v>45607</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38318,7 +38318,7 @@
         <v>45233</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38391,7 +38391,7 @@
         <v>45540</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38464,7 +38464,7 @@
         <v>45169</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38537,7 +38537,7 @@
         <v>44482</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38610,7 +38610,7 @@
         <v>46063</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38683,7 +38683,7 @@
         <v>45246</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38756,7 +38756,7 @@
         <v>45118</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38829,7 +38829,7 @@
         <v>44656</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38902,7 +38902,7 @@
         <v>44690</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38975,7 +38975,7 @@
         <v>44819</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39048,7 +39048,7 @@
         <v>44952</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39121,7 +39121,7 @@
         <v>45323</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39194,7 +39194,7 @@
         <v>45092</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39267,7 +39267,7 @@
         <v>46247</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39345,7 +39345,7 @@
         <v>45086</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39418,7 +39418,7 @@
         <v>46290</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39491,7 +39491,7 @@
         <v>44895</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39564,7 +39564,7 @@
         <v>45156</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39637,7 +39637,7 @@
         <v>45034</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39710,7 +39710,7 @@
         <v>45254</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39783,7 +39783,7 @@
         <v>45174</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39856,7 +39856,7 @@
         <v>46247</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39929,7 +39929,7 @@
         <v>45363</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40002,7 +40002,7 @@
         <v>44818</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40075,7 +40075,7 @@
         <v>45531</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40148,7 +40148,7 @@
         <v>45324</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40221,7 +40221,7 @@
         <v>45454</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40294,7 +40294,7 @@
         <v>46254</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40372,7 +40372,7 @@
         <v>45703</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40445,7 +40445,7 @@
         <v>46254</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40523,7 +40523,7 @@
         <v>46253</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40596,7 +40596,7 @@
         <v>44564</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40669,7 +40669,7 @@
         <v>45209</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40742,7 +40742,7 @@
         <v>45209</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40815,7 +40815,7 @@
         <v>45091</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40888,7 +40888,7 @@
         <v>45260</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40961,7 +40961,7 @@
         <v>44978</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41034,7 +41034,7 @@
         <v>45273</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41107,7 +41107,7 @@
         <v>45334</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41180,7 +41180,7 @@
         <v>45189</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41253,7 +41253,7 @@
         <v>45356</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41326,7 +41326,7 @@
         <v>45027</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41399,7 +41399,7 @@
         <v>45067</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41472,7 +41472,7 @@
         <v>44823</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41545,7 +41545,7 @@
         <v>44823</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41618,7 +41618,7 @@
         <v>44732</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41691,7 +41691,7 @@
         <v>44963</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41764,7 +41764,7 @@
         <v>44963</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41837,7 +41837,7 @@
         <v>45341</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41910,7 +41910,7 @@
         <v>45336</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41983,7 +41983,7 @@
         <v>45618</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42056,7 +42056,7 @@
         <v>45540</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42129,7 +42129,7 @@
         <v>45076</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42207,7 +42207,7 @@
         <v>45156</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42280,7 +42280,7 @@
         <v>44824</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42353,7 +42353,7 @@
         <v>45001</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42426,7 +42426,7 @@
         <v>44658</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42499,7 +42499,7 @@
         <v>45114</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42572,7 +42572,7 @@
         <v>45229</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42645,7 +42645,7 @@
         <v>44924</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42718,7 +42718,7 @@
         <v>45119</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42791,7 +42791,7 @@
         <v>44858</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42864,7 +42864,7 @@
         <v>45181</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42937,7 +42937,7 @@
         <v>45775</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43010,7 +43010,7 @@
         <v>45558</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43088,7 +43088,7 @@
         <v>45439</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43161,7 +43161,7 @@
         <v>45443</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43234,7 +43234,7 @@
         <v>45551</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43307,7 +43307,7 @@
         <v>45246</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43380,7 +43380,7 @@
         <v>45782</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43458,7 +43458,7 @@
         <v>45785</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43531,7 +43531,7 @@
         <v>45664</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43604,7 +43604,7 @@
         <v>45664</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43677,7 +43677,7 @@
         <v>45387</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43750,7 +43750,7 @@
         <v>45373</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43823,7 +43823,7 @@
         <v>45345</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43896,7 +43896,7 @@
         <v>45440</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43969,7 +43969,7 @@
         <v>44607</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44042,7 +44042,7 @@
         <v>45595</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44115,7 +44115,7 @@
         <v>44587</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44188,7 +44188,7 @@
         <v>44806</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44261,7 +44261,7 @@
         <v>44965</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44334,7 +44334,7 @@
         <v>44531</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44407,7 +44407,7 @@
         <v>44957</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44480,7 +44480,7 @@
         <v>45345</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44553,7 +44553,7 @@
         <v>45345</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44626,7 +44626,7 @@
         <v>45685</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44699,7 +44699,7 @@
         <v>45358</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44772,7 +44772,7 @@
         <v>44957</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44845,7 +44845,7 @@
         <v>45824</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44918,7 +44918,7 @@
         <v>44071</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44991,7 +44991,7 @@
         <v>45890</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45064,7 +45064,7 @@
         <v>45902</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45137,7 +45137,7 @@
         <v>46058</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45210,7 +45210,7 @@
         <v>46062</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45283,7 +45283,7 @@
         <v>46062</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45356,7 +45356,7 @@
         <v>46063</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45429,7 +45429,7 @@
         <v>46062</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45502,7 +45502,7 @@
         <v>46062</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45575,7 +45575,7 @@
         <v>46065</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45648,7 +45648,7 @@
         <v>46110</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>

--- a/Översikt KALMAR.xlsx
+++ b/Översikt KALMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45209</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>44876</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45952</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>45345</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>46066</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>44876</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>46058</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>44979</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>44601</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>45947</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>44489</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>44876</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>44476</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>45915</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>44876</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>45324</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>45664</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>45561</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>46085</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>44522</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>44951</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>44984</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>45463</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>44970</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>45953</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>44993</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>44853</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>44979</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>45254</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
         <v>44489</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>45684</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>44595</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>44475</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>44489</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>44784</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>44785</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>44575</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
         <v>45943</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>44785</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
         <v>45118</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>45044</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>44951</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>45114</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>45363</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>44616</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5795,7 +5795,7 @@
         <v>44595</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>45903</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>45954</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>44517</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>44970</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>44802</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>45575</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6548,7 +6548,7 @@
         <v>45924</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>45243</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>46119</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
         <v>46119</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6972,7 +6972,7 @@
         <v>45722</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>44994</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7197,7 +7197,7 @@
         <v>44994</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>44796</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7409,7 +7409,7 @@
         <v>46055</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         <v>45874</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>46049</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>45190</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         <v>45105</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7943,7 +7943,7 @@
         <v>45966</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>46279</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8159,7 +8159,7 @@
         <v>46245</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8265,7 +8265,7 @@
         <v>45314</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>44517</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8481,7 +8481,7 @@
         <v>46253</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8591,7 +8591,7 @@
         <v>45275</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>44827</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         <v>45475</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8918,7 +8918,7 @@
         <v>45448</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         <v>44623</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>44740</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
         <v>44895</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9339,7 +9339,7 @@
         <v>45454</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         <v>45791</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
         <v>44575</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9658,7 +9658,7 @@
         <v>45264</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9767,7 +9767,7 @@
         <v>45574</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9877,7 +9877,7 @@
         <v>45163</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         <v>45086</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10091,7 +10091,7 @@
         <v>45007</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10196,7 +10196,7 @@
         <v>45180</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10305,7 +10305,7 @@
         <v>45167</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>45007</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10515,7 +10515,7 @@
         <v>46119</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10620,7 +10620,7 @@
         <v>44915</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10725,7 +10725,7 @@
         <v>44914</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10830,7 +10830,7 @@
         <v>45917</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>44991</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v>45868</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11145,7 +11145,7 @@
         <v>44810</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11250,7 +11250,7 @@
         <v>45069</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11355,7 +11355,7 @@
         <v>46177</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         <v>46188</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>44855</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11684,7 +11684,7 @@
         <v>46199</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         <v>45063</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11903,7 +11903,7 @@
         <v>44949</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
         <v>45117</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12113,7 +12113,7 @@
         <v>46258</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12218,7 +12218,7 @@
         <v>45083</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
         <v>46247</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12428,7 +12428,7 @@
         <v>46247</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12542,7 +12542,7 @@
         <v>44931</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12647,7 +12647,7 @@
         <v>45090</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
         <v>44931</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12857,7 +12857,7 @@
         <v>45007</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12966,7 +12966,7 @@
         <v>45775</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13071,7 +13071,7 @@
         <v>45544</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13180,7 +13180,7 @@
         <v>45782</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>44810</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         <v>44586</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>45611</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13610,7 +13610,7 @@
         <v>45373</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13719,7 +13719,7 @@
         <v>46063</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13824,7 +13824,7 @@
         <v>46087</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13929,7 +13929,7 @@
         <v>44643</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>44823</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14075,7 +14075,7 @@
         <v>44497</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>44505</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>44852</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14294,7 +14294,7 @@
         <v>44629</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14367,7 +14367,7 @@
         <v>44684</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>44539</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14513,7 +14513,7 @@
         <v>44498</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14586,7 +14586,7 @@
         <v>44498</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14659,7 +14659,7 @@
         <v>44489</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14732,7 +14732,7 @@
         <v>44525</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14805,7 +14805,7 @@
         <v>44823</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14878,7 +14878,7 @@
         <v>44790</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>44531</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15024,7 +15024,7 @@
         <v>44602</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15097,7 +15097,7 @@
         <v>44858</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15170,7 +15170,7 @@
         <v>44522</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15243,7 +15243,7 @@
         <v>44823</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15316,7 +15316,7 @@
         <v>44818</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15389,7 +15389,7 @@
         <v>44858</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>44858</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15535,7 +15535,7 @@
         <v>44852</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
         <v>44858</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15681,7 +15681,7 @@
         <v>44615</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15754,7 +15754,7 @@
         <v>44586</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>44502</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15900,7 +15900,7 @@
         <v>44552</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15973,7 +15973,7 @@
         <v>44482</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16046,7 +16046,7 @@
         <v>44620</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16119,7 +16119,7 @@
         <v>44625</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16192,7 +16192,7 @@
         <v>44784</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16265,7 +16265,7 @@
         <v>44654</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16338,7 +16338,7 @@
         <v>44855</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>44858</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16484,7 +16484,7 @@
         <v>44732</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16557,7 +16557,7 @@
         <v>44810</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16630,7 +16630,7 @@
         <v>44858</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16703,7 +16703,7 @@
         <v>44511</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16776,7 +16776,7 @@
         <v>45411</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16849,7 +16849,7 @@
         <v>44924</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16922,7 +16922,7 @@
         <v>44477</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16995,7 +16995,7 @@
         <v>44595</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17068,7 +17068,7 @@
         <v>44988</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17141,7 +17141,7 @@
         <v>45090</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17214,7 +17214,7 @@
         <v>45090</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17287,7 +17287,7 @@
         <v>45090</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17360,7 +17360,7 @@
         <v>45161</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17433,7 +17433,7 @@
         <v>45097</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17506,7 +17506,7 @@
         <v>45735</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17579,7 +17579,7 @@
         <v>45205</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17652,7 +17652,7 @@
         <v>45272</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17725,7 +17725,7 @@
         <v>44872</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17798,7 +17798,7 @@
         <v>45618</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17871,7 +17871,7 @@
         <v>44846</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17944,7 +17944,7 @@
         <v>44502</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18017,7 +18017,7 @@
         <v>45566</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18090,7 +18090,7 @@
         <v>44993</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18163,7 +18163,7 @@
         <v>45730</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18236,7 +18236,7 @@
         <v>44994</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18309,7 +18309,7 @@
         <v>45630</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18382,7 +18382,7 @@
         <v>45363</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18455,7 +18455,7 @@
         <v>45796</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18528,7 +18528,7 @@
         <v>45195</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
         <v>45099</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>46008</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18747,7 +18747,7 @@
         <v>46010</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18820,7 +18820,7 @@
         <v>46013</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18893,7 +18893,7 @@
         <v>45349</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18966,7 +18966,7 @@
         <v>44855</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19039,7 +19039,7 @@
         <v>45233</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19112,7 +19112,7 @@
         <v>45791</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19185,7 +19185,7 @@
         <v>45796</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19258,7 +19258,7 @@
         <v>44861</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19331,7 +19331,7 @@
         <v>44924</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19404,7 +19404,7 @@
         <v>46026</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19477,7 +19477,7 @@
         <v>44864</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19550,7 +19550,7 @@
         <v>44991</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19623,7 +19623,7 @@
         <v>45173</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19696,7 +19696,7 @@
         <v>45173</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19769,7 +19769,7 @@
         <v>45153</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>45792</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19920,7 +19920,7 @@
         <v>44712</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19993,7 +19993,7 @@
         <v>45219</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20066,7 +20066,7 @@
         <v>45250</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20139,7 +20139,7 @@
         <v>44993</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20212,7 +20212,7 @@
         <v>45840</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         <v>45219</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20358,7 +20358,7 @@
         <v>45912</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
         <v>45189</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20504,7 +20504,7 @@
         <v>45912</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>45272</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20650,7 +20650,7 @@
         <v>45028</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20723,7 +20723,7 @@
         <v>45400</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20796,7 +20796,7 @@
         <v>46048</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20869,7 +20869,7 @@
         <v>45239</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20947,7 +20947,7 @@
         <v>45720</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
         <v>46049</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21093,7 +21093,7 @@
         <v>45805</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21166,7 +21166,7 @@
         <v>44782</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21239,7 +21239,7 @@
         <v>45058</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21312,7 +21312,7 @@
         <v>46054</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21385,7 +21385,7 @@
         <v>46054</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21458,7 +21458,7 @@
         <v>45923</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21531,7 +21531,7 @@
         <v>45924</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21604,7 +21604,7 @@
         <v>45720</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21677,7 +21677,7 @@
         <v>45930</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21750,7 +21750,7 @@
         <v>45182</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21823,7 +21823,7 @@
         <v>46063</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21896,7 +21896,7 @@
         <v>46062</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21969,7 +21969,7 @@
         <v>46063</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22042,7 +22042,7 @@
         <v>45932</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22115,7 +22115,7 @@
         <v>45110</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22193,7 +22193,7 @@
         <v>45104</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22271,7 +22271,7 @@
         <v>46070</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22344,7 +22344,7 @@
         <v>46070</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22417,7 +22417,7 @@
         <v>45939</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22490,7 +22490,7 @@
         <v>45104</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22563,7 +22563,7 @@
         <v>45104</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22636,7 +22636,7 @@
         <v>45341</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22709,7 +22709,7 @@
         <v>44529</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22782,7 +22782,7 @@
         <v>45335</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22860,7 +22860,7 @@
         <v>45180</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22933,7 +22933,7 @@
         <v>44971</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23006,7 +23006,7 @@
         <v>45061</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23079,7 +23079,7 @@
         <v>45812</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23152,7 +23152,7 @@
         <v>44617</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23225,7 +23225,7 @@
         <v>44617</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23298,7 +23298,7 @@
         <v>44984</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23391,7 +23391,7 @@
         <v>44984</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23464,7 +23464,7 @@
         <v>46092</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23537,7 +23537,7 @@
         <v>46092</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23610,7 +23610,7 @@
         <v>45007</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23683,7 +23683,7 @@
         <v>45007</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23756,7 +23756,7 @@
         <v>45205</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23829,7 +23829,7 @@
         <v>46093</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23902,7 +23902,7 @@
         <v>45096</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23975,7 +23975,7 @@
         <v>45170</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24048,7 +24048,7 @@
         <v>46099</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24121,7 +24121,7 @@
         <v>45930</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24194,7 +24194,7 @@
         <v>45212</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24267,7 +24267,7 @@
         <v>45091</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24340,7 +24340,7 @@
         <v>45978</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24413,7 +24413,7 @@
         <v>46108</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24486,7 +24486,7 @@
         <v>44645</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24559,7 +24559,7 @@
         <v>46112</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24632,7 +24632,7 @@
         <v>44973</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24705,7 +24705,7 @@
         <v>46119</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24778,7 +24778,7 @@
         <v>46119</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24851,7 +24851,7 @@
         <v>44963</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24924,7 +24924,7 @@
         <v>45540</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24997,7 +24997,7 @@
         <v>44816</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25070,7 +25070,7 @@
         <v>44914</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25143,7 +25143,7 @@
         <v>45544</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25221,7 +25221,7 @@
         <v>45173</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25294,7 +25294,7 @@
         <v>45104</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25367,7 +25367,7 @@
         <v>45113</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25440,7 +25440,7 @@
         <v>45091</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25513,7 +25513,7 @@
         <v>45167</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25586,7 +25586,7 @@
         <v>45233</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25659,7 +25659,7 @@
         <v>46134</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25732,7 +25732,7 @@
         <v>45252</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25805,7 +25805,7 @@
         <v>45544</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25878,7 +25878,7 @@
         <v>46134</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25951,7 +25951,7 @@
         <v>45406</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26024,7 +26024,7 @@
         <v>45564</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26097,7 +26097,7 @@
         <v>45267</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26170,7 +26170,7 @@
         <v>46139</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26243,7 +26243,7 @@
         <v>45915</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26316,7 +26316,7 @@
         <v>44502</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26389,7 +26389,7 @@
         <v>45104</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26462,7 +26462,7 @@
         <v>45198</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26535,7 +26535,7 @@
         <v>44574</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26608,7 +26608,7 @@
         <v>45034</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26681,7 +26681,7 @@
         <v>45243</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26754,7 +26754,7 @@
         <v>46009</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26827,7 +26827,7 @@
         <v>44846</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26900,7 +26900,7 @@
         <v>45842</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26973,7 +26973,7 @@
         <v>45842</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27046,7 +27046,7 @@
         <v>45688</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27119,7 +27119,7 @@
         <v>45548</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27192,7 +27192,7 @@
         <v>45923</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27265,7 +27265,7 @@
         <v>45070</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27343,7 +27343,7 @@
         <v>44909</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27416,7 +27416,7 @@
         <v>45215</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27489,7 +27489,7 @@
         <v>46036</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27562,7 +27562,7 @@
         <v>45246</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27635,7 +27635,7 @@
         <v>45688</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27708,7 +27708,7 @@
         <v>45268</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27781,7 +27781,7 @@
         <v>46139</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27854,7 +27854,7 @@
         <v>45229</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27927,7 +27927,7 @@
         <v>45764</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28000,7 +28000,7 @@
         <v>45595</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28073,7 +28073,7 @@
         <v>45628</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28146,7 +28146,7 @@
         <v>45252</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28219,7 +28219,7 @@
         <v>45861</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28292,7 +28292,7 @@
         <v>45233</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28365,7 +28365,7 @@
         <v>45727</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28438,7 +28438,7 @@
         <v>44566</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28511,7 +28511,7 @@
         <v>45418</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28584,7 +28584,7 @@
         <v>45716</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         <v>45345</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28730,7 +28730,7 @@
         <v>45831</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28803,7 +28803,7 @@
         <v>45028</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28876,7 +28876,7 @@
         <v>45764</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28949,7 +28949,7 @@
         <v>45779</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29022,7 +29022,7 @@
         <v>45713</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29095,7 +29095,7 @@
         <v>44497</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29168,7 +29168,7 @@
         <v>45618</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29241,7 +29241,7 @@
         <v>45695</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29314,7 +29314,7 @@
         <v>45719</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29392,7 +29392,7 @@
         <v>45006</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29465,7 +29465,7 @@
         <v>46099</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29538,7 +29538,7 @@
         <v>45229</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29611,7 +29611,7 @@
         <v>44971</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29684,7 +29684,7 @@
         <v>45093</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29757,7 +29757,7 @@
         <v>45153</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29830,7 +29830,7 @@
         <v>44915</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29903,7 +29903,7 @@
         <v>44914</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29976,7 +29976,7 @@
         <v>44895</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30049,7 +30049,7 @@
         <v>45551</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30122,7 +30122,7 @@
         <v>46155</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30195,7 +30195,7 @@
         <v>45327</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30268,7 +30268,7 @@
         <v>46155</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30341,7 +30341,7 @@
         <v>44939</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30414,7 +30414,7 @@
         <v>45246</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30487,7 +30487,7 @@
         <v>45246</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30560,7 +30560,7 @@
         <v>45903</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30633,7 +30633,7 @@
         <v>44973</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30706,7 +30706,7 @@
         <v>45378</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>45175</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30852,7 +30852,7 @@
         <v>46160</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30925,7 +30925,7 @@
         <v>45173</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30998,7 +30998,7 @@
         <v>45236</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31071,7 +31071,7 @@
         <v>45874</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31144,7 +31144,7 @@
         <v>46160</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31217,7 +31217,7 @@
         <v>46162</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31290,7 +31290,7 @@
         <v>46162</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31363,7 +31363,7 @@
         <v>45306</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31436,7 +31436,7 @@
         <v>46162</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31509,7 +31509,7 @@
         <v>45091</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31582,7 +31582,7 @@
         <v>44629</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31655,7 +31655,7 @@
         <v>45785</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31728,7 +31728,7 @@
         <v>45624</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31806,7 +31806,7 @@
         <v>44862</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31879,7 +31879,7 @@
         <v>45574</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31957,7 +31957,7 @@
         <v>45097</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32030,7 +32030,7 @@
         <v>45628</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32103,7 +32103,7 @@
         <v>46099</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32176,7 +32176,7 @@
         <v>45707</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32249,7 +32249,7 @@
         <v>44539</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32322,7 +32322,7 @@
         <v>45154</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32395,7 +32395,7 @@
         <v>44529</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32468,7 +32468,7 @@
         <v>45789</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32541,7 +32541,7 @@
         <v>45492</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32614,7 +32614,7 @@
         <v>45182</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32687,7 +32687,7 @@
         <v>45915</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32760,7 +32760,7 @@
         <v>46177</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32833,7 +32833,7 @@
         <v>44909</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32906,7 +32906,7 @@
         <v>44988</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32979,7 +32979,7 @@
         <v>45624</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33057,7 +33057,7 @@
         <v>45266</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33130,7 +33130,7 @@
         <v>45625</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33203,7 +33203,7 @@
         <v>45629</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33276,7 +33276,7 @@
         <v>46188</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33349,7 +33349,7 @@
         <v>46185</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33422,7 +33422,7 @@
         <v>45188</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33495,7 +33495,7 @@
         <v>44803</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33568,7 +33568,7 @@
         <v>45402</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33646,7 +33646,7 @@
         <v>45680</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33719,7 +33719,7 @@
         <v>46036</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33792,7 +33792,7 @@
         <v>46178</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33865,7 +33865,7 @@
         <v>44966</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33938,7 +33938,7 @@
         <v>44595</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34011,7 +34011,7 @@
         <v>45097</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34084,7 +34084,7 @@
         <v>46197</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34157,7 +34157,7 @@
         <v>46198</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34230,7 +34230,7 @@
         <v>45685</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34303,7 +34303,7 @@
         <v>45044</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34376,7 +34376,7 @@
         <v>44939</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34449,7 +34449,7 @@
         <v>46199</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34522,7 +34522,7 @@
         <v>45470</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34595,7 +34595,7 @@
         <v>46202</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34668,7 +34668,7 @@
         <v>46203</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34741,7 +34741,7 @@
         <v>45125</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34814,7 +34814,7 @@
         <v>45387</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34887,7 +34887,7 @@
         <v>45387</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34960,7 +34960,7 @@
         <v>46139</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35033,7 +35033,7 @@
         <v>45476</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35106,7 +35106,7 @@
         <v>46154</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35179,7 +35179,7 @@
         <v>44882</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35252,7 +35252,7 @@
         <v>45624</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35325,7 +35325,7 @@
         <v>45534</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35398,7 +35398,7 @@
         <v>44959</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35471,7 +35471,7 @@
         <v>46212</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35544,7 +35544,7 @@
         <v>44544</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35617,7 +35617,7 @@
         <v>44847</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35690,7 +35690,7 @@
         <v>46259</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35763,7 +35763,7 @@
         <v>44543</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35836,7 +35836,7 @@
         <v>45202</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35909,7 +35909,7 @@
         <v>45050</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35982,7 +35982,7 @@
         <v>45308</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36055,7 +36055,7 @@
         <v>46063</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36128,7 +36128,7 @@
         <v>44993</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36201,7 +36201,7 @@
         <v>46111</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36274,7 +36274,7 @@
         <v>44782</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36347,7 +36347,7 @@
         <v>45075</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36420,7 +36420,7 @@
         <v>46223</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36493,7 +36493,7 @@
         <v>45114</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36566,7 +36566,7 @@
         <v>46269</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36639,7 +36639,7 @@
         <v>45173</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36712,7 +36712,7 @@
         <v>45387</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>45387</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36858,7 +36858,7 @@
         <v>46272</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36931,7 +36931,7 @@
         <v>46273</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37004,7 +37004,7 @@
         <v>46273</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37077,7 +37077,7 @@
         <v>46275</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37150,7 +37150,7 @@
         <v>46274</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37223,7 +37223,7 @@
         <v>46276</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37296,7 +37296,7 @@
         <v>46276</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37369,7 +37369,7 @@
         <v>44564</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37442,7 +37442,7 @@
         <v>46281</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37515,7 +37515,7 @@
         <v>45149</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37588,7 +37588,7 @@
         <v>45149</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37661,7 +37661,7 @@
         <v>45141</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37734,7 +37734,7 @@
         <v>46281</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37807,7 +37807,7 @@
         <v>44971</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37880,7 +37880,7 @@
         <v>45205</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37953,7 +37953,7 @@
         <v>45524</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38026,7 +38026,7 @@
         <v>45099</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38099,7 +38099,7 @@
         <v>45212</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38172,7 +38172,7 @@
         <v>46281</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38245,7 +38245,7 @@
         <v>45607</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38318,7 +38318,7 @@
         <v>45233</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38391,7 +38391,7 @@
         <v>45540</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38464,7 +38464,7 @@
         <v>45169</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38537,7 +38537,7 @@
         <v>44482</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38610,7 +38610,7 @@
         <v>46063</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38683,7 +38683,7 @@
         <v>45246</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38756,7 +38756,7 @@
         <v>45118</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38829,7 +38829,7 @@
         <v>44656</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38902,7 +38902,7 @@
         <v>44690</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38975,7 +38975,7 @@
         <v>44819</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39048,7 +39048,7 @@
         <v>44952</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39121,7 +39121,7 @@
         <v>45323</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39194,7 +39194,7 @@
         <v>45092</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39267,7 +39267,7 @@
         <v>46247</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39345,7 +39345,7 @@
         <v>45086</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39418,7 +39418,7 @@
         <v>46290</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39491,7 +39491,7 @@
         <v>44895</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39564,7 +39564,7 @@
         <v>45156</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39637,7 +39637,7 @@
         <v>45034</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39710,7 +39710,7 @@
         <v>45254</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39783,7 +39783,7 @@
         <v>45174</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39856,7 +39856,7 @@
         <v>46247</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39929,7 +39929,7 @@
         <v>45363</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40002,7 +40002,7 @@
         <v>44818</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40075,7 +40075,7 @@
         <v>45531</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40148,7 +40148,7 @@
         <v>45324</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40221,7 +40221,7 @@
         <v>45454</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40294,7 +40294,7 @@
         <v>46254</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40372,7 +40372,7 @@
         <v>45703</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40445,7 +40445,7 @@
         <v>46254</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40523,7 +40523,7 @@
         <v>46253</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40596,7 +40596,7 @@
         <v>44564</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40669,7 +40669,7 @@
         <v>45209</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40742,7 +40742,7 @@
         <v>45209</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40815,7 +40815,7 @@
         <v>45091</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40888,7 +40888,7 @@
         <v>45260</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40961,7 +40961,7 @@
         <v>44978</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41034,7 +41034,7 @@
         <v>45273</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41107,7 +41107,7 @@
         <v>45334</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41180,7 +41180,7 @@
         <v>45189</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41253,7 +41253,7 @@
         <v>45356</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41326,7 +41326,7 @@
         <v>45027</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41399,7 +41399,7 @@
         <v>45067</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41472,7 +41472,7 @@
         <v>44823</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41545,7 +41545,7 @@
         <v>44823</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41618,7 +41618,7 @@
         <v>44732</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41691,7 +41691,7 @@
         <v>44963</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41764,7 +41764,7 @@
         <v>44963</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41837,7 +41837,7 @@
         <v>45341</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41910,7 +41910,7 @@
         <v>45336</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41983,7 +41983,7 @@
         <v>45618</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42056,7 +42056,7 @@
         <v>45540</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42129,7 +42129,7 @@
         <v>45076</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42207,7 +42207,7 @@
         <v>45156</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42280,7 +42280,7 @@
         <v>44824</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42353,7 +42353,7 @@
         <v>45001</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42426,7 +42426,7 @@
         <v>44658</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42499,7 +42499,7 @@
         <v>45114</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42572,7 +42572,7 @@
         <v>45229</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42645,7 +42645,7 @@
         <v>44924</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42718,7 +42718,7 @@
         <v>45119</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42791,7 +42791,7 @@
         <v>44858</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42864,7 +42864,7 @@
         <v>45181</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42937,7 +42937,7 @@
         <v>45775</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43010,7 +43010,7 @@
         <v>45558</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43088,7 +43088,7 @@
         <v>45439</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43161,7 +43161,7 @@
         <v>45443</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43234,7 +43234,7 @@
         <v>45551</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43307,7 +43307,7 @@
         <v>45246</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43380,7 +43380,7 @@
         <v>45782</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43458,7 +43458,7 @@
         <v>45785</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43531,7 +43531,7 @@
         <v>45664</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43604,7 +43604,7 @@
         <v>45664</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43677,7 +43677,7 @@
         <v>45387</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43750,7 +43750,7 @@
         <v>45373</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43823,7 +43823,7 @@
         <v>45345</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43896,7 +43896,7 @@
         <v>45440</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43969,7 +43969,7 @@
         <v>44607</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44042,7 +44042,7 @@
         <v>45595</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44115,7 +44115,7 @@
         <v>44587</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44188,7 +44188,7 @@
         <v>44806</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44261,7 +44261,7 @@
         <v>44965</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44334,7 +44334,7 @@
         <v>44531</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44407,7 +44407,7 @@
         <v>44957</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44480,7 +44480,7 @@
         <v>45345</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44553,7 +44553,7 @@
         <v>45345</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44626,7 +44626,7 @@
         <v>45685</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44699,7 +44699,7 @@
         <v>45358</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44772,7 +44772,7 @@
         <v>44957</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44845,7 +44845,7 @@
         <v>45824</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44918,7 +44918,7 @@
         <v>44071</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44991,7 +44991,7 @@
         <v>45890</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45064,7 +45064,7 @@
         <v>45902</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45137,7 +45137,7 @@
         <v>46058</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45210,7 +45210,7 @@
         <v>46062</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45283,7 +45283,7 @@
         <v>46062</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45356,7 +45356,7 @@
         <v>46063</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45429,7 +45429,7 @@
         <v>46062</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45502,7 +45502,7 @@
         <v>46062</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45575,7 +45575,7 @@
         <v>46065</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45648,7 +45648,7 @@
         <v>46110</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>

--- a/Översikt KALMAR.xlsx
+++ b/Översikt KALMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45209</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>44876</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45952</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>45345</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>46066</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>44876</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>46058</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>44979</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>44601</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>44876</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>44489</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>45947</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>45915</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>44876</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>45664</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>45324</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>45561</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>46085</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>44522</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>44951</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>46300</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>46303</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44984</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>45463</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>44970</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3568,7 +3568,7 @@
         <v>45953</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>45684</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>44979</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>44489</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4005,7 +4005,7 @@
         <v>45254</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>44993</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>44853</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>44595</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>44489</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>44784</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>44785</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>45044</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>45363</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         <v>45114</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
         <v>45943</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>44785</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5335,7 +5335,7 @@
         <v>45118</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>44970</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
         <v>44575</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>44951</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         <v>46300</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
         <v>44616</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>44595</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
         <v>45903</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>45954</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         <v>44517</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6430,7 +6430,7 @@
         <v>45190</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>44517</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
         <v>45243</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6756,7 +6756,7 @@
         <v>44802</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>45275</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         <v>45924</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         <v>45105</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7185,7 +7185,7 @@
         <v>45575</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7291,7 +7291,7 @@
         <v>44994</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7401,7 +7401,7 @@
         <v>44994</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         <v>45314</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>45722</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         <v>44796</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>44827</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7944,7 +7944,7 @@
         <v>46119</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>46119</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         <v>45874</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         <v>46055</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8368,7 +8368,7 @@
         <v>46049</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8474,7 +8474,7 @@
         <v>45966</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8580,7 +8580,7 @@
         <v>46279</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8690,7 +8690,7 @@
         <v>46245</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         <v>46253</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         <v>45475</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9012,7 +9012,7 @@
         <v>45448</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>44623</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>45090</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>45264</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         <v>44895</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>45063</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>45083</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9761,7 +9761,7 @@
         <v>44855</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9871,7 +9871,7 @@
         <v>45163</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9980,7 +9980,7 @@
         <v>44915</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10085,7 +10085,7 @@
         <v>45086</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10190,7 +10190,7 @@
         <v>45544</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10299,7 +10299,7 @@
         <v>45775</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>44914</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10509,7 +10509,7 @@
         <v>45117</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>45454</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10719,7 +10719,7 @@
         <v>45791</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
         <v>45180</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10933,7 +10933,7 @@
         <v>45574</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11043,7 +11043,7 @@
         <v>45007</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11148,7 +11148,7 @@
         <v>44740</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
         <v>45167</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11358,7 +11358,7 @@
         <v>44810</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>45868</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11568,7 +11568,7 @@
         <v>44575</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>44991</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
         <v>45069</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11887,7 +11887,7 @@
         <v>45007</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
         <v>46119</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         <v>45917</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12206,7 +12206,7 @@
         <v>45007</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12311,7 +12311,7 @@
         <v>44931</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12416,7 +12416,7 @@
         <v>44949</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12521,7 +12521,7 @@
         <v>44931</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
         <v>46177</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12740,7 +12740,7 @@
         <v>46188</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12845,7 +12845,7 @@
         <v>46199</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12950,7 +12950,7 @@
         <v>46247</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>46247</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>46300</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13274,7 +13274,7 @@
         <v>46300</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13388,7 +13388,7 @@
         <v>45782</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13498,7 +13498,7 @@
         <v>46300</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>46258</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13713,7 +13713,7 @@
         <v>46304</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13818,7 +13818,7 @@
         <v>44586</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13923,7 +13923,7 @@
         <v>44810</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14033,7 +14033,7 @@
         <v>45611</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14138,7 +14138,7 @@
         <v>45373</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14247,7 +14247,7 @@
         <v>46063</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14352,7 +14352,7 @@
         <v>46087</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14457,7 +14457,7 @@
         <v>44629</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14530,7 +14530,7 @@
         <v>44643</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>44823</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14676,7 +14676,7 @@
         <v>44497</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14749,7 +14749,7 @@
         <v>44505</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14822,7 +14822,7 @@
         <v>44852</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14895,7 +14895,7 @@
         <v>44684</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>44539</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         <v>44498</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         <v>44498</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15187,7 +15187,7 @@
         <v>44489</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15260,7 +15260,7 @@
         <v>44525</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15333,7 +15333,7 @@
         <v>44823</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15406,7 +15406,7 @@
         <v>44790</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15479,7 +15479,7 @@
         <v>44531</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15552,7 +15552,7 @@
         <v>44602</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15625,7 +15625,7 @@
         <v>44858</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15698,7 +15698,7 @@
         <v>44522</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>44823</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15844,7 +15844,7 @@
         <v>44818</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15917,7 +15917,7 @@
         <v>44858</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15990,7 +15990,7 @@
         <v>44858</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16063,7 +16063,7 @@
         <v>44852</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16136,7 +16136,7 @@
         <v>44858</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16209,7 +16209,7 @@
         <v>44615</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16282,7 +16282,7 @@
         <v>44586</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16355,7 +16355,7 @@
         <v>44502</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16428,7 +16428,7 @@
         <v>44625</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16501,7 +16501,7 @@
         <v>44810</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         <v>44552</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16647,7 +16647,7 @@
         <v>44482</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16720,7 +16720,7 @@
         <v>44654</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16793,7 +16793,7 @@
         <v>44858</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16866,7 +16866,7 @@
         <v>44620</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16939,7 +16939,7 @@
         <v>44784</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17012,7 +17012,7 @@
         <v>44855</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17085,7 +17085,7 @@
         <v>44858</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17158,7 +17158,7 @@
         <v>44732</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17231,7 +17231,7 @@
         <v>44782</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17304,7 +17304,7 @@
         <v>45209</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17377,7 +17377,7 @@
         <v>45209</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17450,7 +17450,7 @@
         <v>44846</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17523,7 +17523,7 @@
         <v>45091</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17596,7 +17596,7 @@
         <v>44939</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17669,7 +17669,7 @@
         <v>44511</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17742,7 +17742,7 @@
         <v>44882</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17815,7 +17815,7 @@
         <v>45097</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17888,7 +17888,7 @@
         <v>44529</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17961,7 +17961,7 @@
         <v>45156</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18034,7 +18034,7 @@
         <v>45044</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18107,7 +18107,7 @@
         <v>45092</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>45341</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18253,7 +18253,7 @@
         <v>45341</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18326,7 +18326,7 @@
         <v>44993</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18399,7 +18399,7 @@
         <v>44914</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18472,7 +18472,7 @@
         <v>45099</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18545,7 +18545,7 @@
         <v>45324</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18618,7 +18618,7 @@
         <v>45243</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18691,7 +18691,7 @@
         <v>45625</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18764,7 +18764,7 @@
         <v>45212</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18837,7 +18837,7 @@
         <v>45564</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18910,7 +18910,7 @@
         <v>45411</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18983,7 +18983,7 @@
         <v>45104</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19056,7 +19056,7 @@
         <v>45104</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19129,7 +19129,7 @@
         <v>45267</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19202,7 +19202,7 @@
         <v>45378</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19275,7 +19275,7 @@
         <v>45250</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19348,7 +19348,7 @@
         <v>44924</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19421,7 +19421,7 @@
         <v>45067</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>45716</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19567,7 +19567,7 @@
         <v>45118</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19640,7 +19640,7 @@
         <v>45246</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         <v>45086</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19786,7 +19786,7 @@
         <v>45268</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19859,7 +19859,7 @@
         <v>45202</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19932,7 +19932,7 @@
         <v>44963</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>45215</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20078,7 +20078,7 @@
         <v>45334</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20151,7 +20151,7 @@
         <v>45387</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20224,7 +20224,7 @@
         <v>45387</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20297,7 +20297,7 @@
         <v>44846</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20370,7 +20370,7 @@
         <v>45707</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>44529</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20516,7 +20516,7 @@
         <v>45387</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20589,7 +20589,7 @@
         <v>45387</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20662,7 +20662,7 @@
         <v>45099</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20735,7 +20735,7 @@
         <v>44914</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20808,7 +20808,7 @@
         <v>45097</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>45173</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20954,7 +20954,7 @@
         <v>45174</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21027,7 +21027,7 @@
         <v>45306</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>45630</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21173,7 +21173,7 @@
         <v>45096</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>44994</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21319,7 +21319,7 @@
         <v>45141</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21392,7 +21392,7 @@
         <v>44872</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21465,7 +21465,7 @@
         <v>45097</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21538,7 +21538,7 @@
         <v>45219</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21611,7 +21611,7 @@
         <v>45628</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21684,7 +21684,7 @@
         <v>45796</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21757,7 +21757,7 @@
         <v>45789</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21830,7 +21830,7 @@
         <v>44544</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21903,7 +21903,7 @@
         <v>45272</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>45492</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22049,7 +22049,7 @@
         <v>45796</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22122,7 +22122,7 @@
         <v>45254</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22195,7 +22195,7 @@
         <v>45113</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22268,7 +22268,7 @@
         <v>45173</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         <v>44971</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22414,7 +22414,7 @@
         <v>45476</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22487,7 +22487,7 @@
         <v>45735</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22560,7 +22560,7 @@
         <v>45273</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22633,7 +22633,7 @@
         <v>45246</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22706,7 +22706,7 @@
         <v>45246</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22779,7 +22779,7 @@
         <v>44895</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22852,7 +22852,7 @@
         <v>44564</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22925,7 +22925,7 @@
         <v>45175</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22998,7 +22998,7 @@
         <v>45544</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23071,7 +23071,7 @@
         <v>44988</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23144,7 +23144,7 @@
         <v>45104</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23222,7 +23222,7 @@
         <v>44862</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23295,7 +23295,7 @@
         <v>44991</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23368,7 +23368,7 @@
         <v>45188</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23441,7 +23441,7 @@
         <v>45181</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23514,7 +23514,7 @@
         <v>45439</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23587,7 +23587,7 @@
         <v>45246</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23660,7 +23660,7 @@
         <v>45840</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23733,7 +23733,7 @@
         <v>45551</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23806,7 +23806,7 @@
         <v>45558</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23884,7 +23884,7 @@
         <v>45775</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23957,7 +23957,7 @@
         <v>45443</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24030,7 +24030,7 @@
         <v>45260</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>45912</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24176,7 +24176,7 @@
         <v>45713</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24249,7 +24249,7 @@
         <v>45153</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24322,7 +24322,7 @@
         <v>45050</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24395,7 +24395,7 @@
         <v>45912</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>45076</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24546,7 +24546,7 @@
         <v>44909</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24619,7 +24619,7 @@
         <v>45400</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>44924</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24765,7 +24765,7 @@
         <v>45566</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24838,7 +24838,7 @@
         <v>45664</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24911,7 +24911,7 @@
         <v>45363</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24984,7 +24984,7 @@
         <v>45785</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25057,7 +25057,7 @@
         <v>45664</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25130,7 +25130,7 @@
         <v>45110</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25208,7 +25208,7 @@
         <v>45335</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25286,7 +25286,7 @@
         <v>45548</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25359,7 +25359,7 @@
         <v>44543</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25432,7 +25432,7 @@
         <v>45618</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25505,7 +25505,7 @@
         <v>45173</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25578,7 +25578,7 @@
         <v>45551</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25651,7 +25651,7 @@
         <v>45730</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25724,7 +25724,7 @@
         <v>44595</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25797,7 +25797,7 @@
         <v>44595</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25870,7 +25870,7 @@
         <v>45028</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25943,7 +25943,7 @@
         <v>45534</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26016,7 +26016,7 @@
         <v>44502</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26089,7 +26089,7 @@
         <v>45924</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26162,7 +26162,7 @@
         <v>45923</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26235,7 +26235,7 @@
         <v>45540</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26308,7 +26308,7 @@
         <v>45695</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26381,7 +26381,7 @@
         <v>44818</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26454,7 +26454,7 @@
         <v>45104</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>45792</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26605,7 +26605,7 @@
         <v>45195</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26678,7 +26678,7 @@
         <v>45114</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26751,7 +26751,7 @@
         <v>45791</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26824,7 +26824,7 @@
         <v>45930</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26897,7 +26897,7 @@
         <v>45205</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26970,7 +26970,7 @@
         <v>44971</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27043,7 +27043,7 @@
         <v>44539</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27116,7 +27116,7 @@
         <v>45531</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27189,7 +27189,7 @@
         <v>45090</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27262,7 +27262,7 @@
         <v>45090</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27335,7 +27335,7 @@
         <v>45618</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27408,7 +27408,7 @@
         <v>45189</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27481,7 +27481,7 @@
         <v>44645</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27554,7 +27554,7 @@
         <v>45167</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27627,7 +27627,7 @@
         <v>45932</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27700,7 +27700,7 @@
         <v>45058</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27773,7 +27773,7 @@
         <v>45720</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27846,7 +27846,7 @@
         <v>44915</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27919,7 +27919,7 @@
         <v>45229</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27992,7 +27992,7 @@
         <v>45720</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28065,7 +28065,7 @@
         <v>45327</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28138,7 +28138,7 @@
         <v>45345</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28211,7 +28211,7 @@
         <v>45027</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28284,7 +28284,7 @@
         <v>45219</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28357,7 +28357,7 @@
         <v>45805</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28430,7 +28430,7 @@
         <v>45205</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28503,7 +28503,7 @@
         <v>45006</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28576,7 +28576,7 @@
         <v>44959</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28649,7 +28649,7 @@
         <v>45061</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28722,7 +28722,7 @@
         <v>44819</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28795,7 +28795,7 @@
         <v>45091</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28868,7 +28868,7 @@
         <v>45156</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28941,7 +28941,7 @@
         <v>44816</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29014,7 +29014,7 @@
         <v>45272</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29087,7 +29087,7 @@
         <v>45070</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29165,7 +29165,7 @@
         <v>45182</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29238,7 +29238,7 @@
         <v>44656</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29311,7 +29311,7 @@
         <v>45402</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29389,7 +29389,7 @@
         <v>45939</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29462,7 +29462,7 @@
         <v>45812</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29535,7 +29535,7 @@
         <v>45406</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29608,7 +29608,7 @@
         <v>45182</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29681,7 +29681,7 @@
         <v>45363</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29754,7 +29754,7 @@
         <v>44993</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29827,7 +29827,7 @@
         <v>45629</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29900,7 +29900,7 @@
         <v>45149</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29973,7 +29973,7 @@
         <v>45149</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>45703</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30119,7 +30119,7 @@
         <v>44909</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30192,7 +30192,7 @@
         <v>45125</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30265,7 +30265,7 @@
         <v>45154</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30338,7 +30338,7 @@
         <v>45624</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30411,7 +30411,7 @@
         <v>45574</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30489,7 +30489,7 @@
         <v>44952</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30562,7 +30562,7 @@
         <v>44966</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30635,7 +30635,7 @@
         <v>44984</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30728,7 +30728,7 @@
         <v>44984</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30801,7 +30801,7 @@
         <v>45233</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30874,7 +30874,7 @@
         <v>44973</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30947,7 +30947,7 @@
         <v>45233</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31020,7 +31020,7 @@
         <v>45618</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31093,7 +31093,7 @@
         <v>45198</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31166,7 +31166,7 @@
         <v>45001</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31239,7 +31239,7 @@
         <v>45680</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31312,7 +31312,7 @@
         <v>44993</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31385,7 +31385,7 @@
         <v>44732</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31458,7 +31458,7 @@
         <v>44924</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31531,7 +31531,7 @@
         <v>45161</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31604,7 +31604,7 @@
         <v>45189</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31677,7 +31677,7 @@
         <v>45685</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31750,7 +31750,7 @@
         <v>45114</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31823,7 +31823,7 @@
         <v>45169</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31896,7 +31896,7 @@
         <v>44861</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31969,7 +31969,7 @@
         <v>45119</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32042,7 +32042,7 @@
         <v>45153</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32115,7 +32115,7 @@
         <v>45842</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32188,7 +32188,7 @@
         <v>45842</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32261,7 +32261,7 @@
         <v>45544</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32339,7 +32339,7 @@
         <v>45233</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32412,7 +32412,7 @@
         <v>45173</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32485,7 +32485,7 @@
         <v>45173</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32558,7 +32558,7 @@
         <v>45246</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32631,7 +32631,7 @@
         <v>44782</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32704,7 +32704,7 @@
         <v>45252</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32777,7 +32777,7 @@
         <v>45170</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32850,7 +32850,7 @@
         <v>44973</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32923,7 +32923,7 @@
         <v>45978</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32996,7 +32996,7 @@
         <v>45356</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33069,7 +33069,7 @@
         <v>45861</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33142,7 +33142,7 @@
         <v>44847</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33215,7 +33215,7 @@
         <v>45454</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33288,7 +33288,7 @@
         <v>45831</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33361,7 +33361,7 @@
         <v>44690</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33434,7 +33434,7 @@
         <v>45779</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33507,7 +33507,7 @@
         <v>45764</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33580,7 +33580,7 @@
         <v>44824</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33653,7 +33653,7 @@
         <v>45349</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33726,7 +33726,7 @@
         <v>44564</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33799,7 +33799,7 @@
         <v>45930</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33872,7 +33872,7 @@
         <v>45212</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33945,7 +33945,7 @@
         <v>45007</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34018,7 +34018,7 @@
         <v>45007</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34091,7 +34091,7 @@
         <v>45091</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34164,7 +34164,7 @@
         <v>44988</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34237,7 +34237,7 @@
         <v>45266</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34310,7 +34310,7 @@
         <v>45323</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34383,7 +34383,7 @@
         <v>45874</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34456,7 +34456,7 @@
         <v>44482</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34529,7 +34529,7 @@
         <v>45229</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34602,7 +34602,7 @@
         <v>45028</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34675,7 +34675,7 @@
         <v>44823</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34748,7 +34748,7 @@
         <v>44823</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34821,7 +34821,7 @@
         <v>44963</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34894,7 +34894,7 @@
         <v>44963</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34967,7 +34967,7 @@
         <v>44617</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35040,7 +35040,7 @@
         <v>44617</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35113,7 +35113,7 @@
         <v>45205</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35186,7 +35186,7 @@
         <v>45785</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35259,7 +35259,7 @@
         <v>45093</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35332,7 +35332,7 @@
         <v>46099</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35405,7 +35405,7 @@
         <v>45239</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35483,7 +35483,7 @@
         <v>45229</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35556,7 +35556,7 @@
         <v>44629</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35629,7 +35629,7 @@
         <v>44864</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35702,7 +35702,7 @@
         <v>45308</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35775,7 +35775,7 @@
         <v>45595</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35848,7 +35848,7 @@
         <v>46108</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35921,7 +35921,7 @@
         <v>45180</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35994,7 +35994,7 @@
         <v>45540</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36067,7 +36067,7 @@
         <v>44502</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36140,7 +36140,7 @@
         <v>44566</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36213,7 +36213,7 @@
         <v>46112</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36286,7 +36286,7 @@
         <v>45233</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36359,7 +36359,7 @@
         <v>46119</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36432,7 +36432,7 @@
         <v>46119</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36505,7 +36505,7 @@
         <v>44658</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36578,7 +36578,7 @@
         <v>44858</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36651,7 +36651,7 @@
         <v>45524</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36724,7 +36724,7 @@
         <v>44712</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36797,7 +36797,7 @@
         <v>44803</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36870,7 +36870,7 @@
         <v>44978</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36943,7 +36943,7 @@
         <v>46134</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37016,7 +37016,7 @@
         <v>44939</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37089,7 +37089,7 @@
         <v>46134</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37162,7 +37162,7 @@
         <v>46036</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37235,7 +37235,7 @@
         <v>46009</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37308,7 +37308,7 @@
         <v>46008</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37381,7 +37381,7 @@
         <v>45688</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37454,7 +37454,7 @@
         <v>45764</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37527,7 +37527,7 @@
         <v>45923</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37600,7 +37600,7 @@
         <v>44497</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37673,7 +37673,7 @@
         <v>45688</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37746,7 +37746,7 @@
         <v>46010</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37819,7 +37819,7 @@
         <v>45915</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37892,7 +37892,7 @@
         <v>46139</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37965,7 +37965,7 @@
         <v>46013</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38038,7 +38038,7 @@
         <v>45607</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38111,7 +38111,7 @@
         <v>45075</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38184,7 +38184,7 @@
         <v>44855</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38257,7 +38257,7 @@
         <v>44574</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38330,7 +38330,7 @@
         <v>45719</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38408,7 +38408,7 @@
         <v>45091</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38481,7 +38481,7 @@
         <v>45252</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38554,7 +38554,7 @@
         <v>46139</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38627,7 +38627,7 @@
         <v>45470</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38700,7 +38700,7 @@
         <v>45034</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38773,7 +38773,7 @@
         <v>45034</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38846,7 +38846,7 @@
         <v>45727</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38919,7 +38919,7 @@
         <v>44895</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38992,7 +38992,7 @@
         <v>45540</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39065,7 +39065,7 @@
         <v>46048</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39138,7 +39138,7 @@
         <v>45418</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39211,7 +39211,7 @@
         <v>46049</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39284,7 +39284,7 @@
         <v>44971</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39357,7 +39357,7 @@
         <v>45090</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39430,7 +39430,7 @@
         <v>46054</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39503,7 +39503,7 @@
         <v>46054</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39576,7 +39576,7 @@
         <v>46099</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39649,7 +39649,7 @@
         <v>46062</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39722,7 +39722,7 @@
         <v>46063</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39795,7 +39795,7 @@
         <v>46063</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39868,7 +39868,7 @@
         <v>46070</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39941,7 +39941,7 @@
         <v>46155</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40014,7 +40014,7 @@
         <v>46155</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40087,7 +40087,7 @@
         <v>46160</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40160,7 +40160,7 @@
         <v>45236</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40233,7 +40233,7 @@
         <v>46160</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40306,7 +40306,7 @@
         <v>45903</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40379,7 +40379,7 @@
         <v>46092</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40452,7 +40452,7 @@
         <v>46092</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40525,7 +40525,7 @@
         <v>46093</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40598,7 +40598,7 @@
         <v>46162</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40671,7 +40671,7 @@
         <v>46162</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40744,7 +40744,7 @@
         <v>46162</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40817,7 +40817,7 @@
         <v>45628</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40890,7 +40890,7 @@
         <v>46099</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40963,7 +40963,7 @@
         <v>46177</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41036,7 +41036,7 @@
         <v>45915</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41109,7 +41109,7 @@
         <v>46185</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41182,7 +41182,7 @@
         <v>46188</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41255,7 +41255,7 @@
         <v>46178</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41328,7 +41328,7 @@
         <v>46036</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41401,7 +41401,7 @@
         <v>46197</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41474,7 +41474,7 @@
         <v>46198</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41547,7 +41547,7 @@
         <v>46199</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41620,7 +41620,7 @@
         <v>46202</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41693,7 +41693,7 @@
         <v>46203</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41766,7 +41766,7 @@
         <v>46139</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41839,7 +41839,7 @@
         <v>46154</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41912,7 +41912,7 @@
         <v>46212</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41985,7 +41985,7 @@
         <v>46111</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42058,7 +42058,7 @@
         <v>46063</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42131,7 +42131,7 @@
         <v>46223</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42204,7 +42204,7 @@
         <v>46272</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42277,7 +42277,7 @@
         <v>46269</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42350,7 +42350,7 @@
         <v>46273</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42423,7 +42423,7 @@
         <v>46273</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42496,7 +42496,7 @@
         <v>46274</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42569,7 +42569,7 @@
         <v>46276</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42642,7 +42642,7 @@
         <v>46275</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42715,7 +42715,7 @@
         <v>46276</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42788,7 +42788,7 @@
         <v>46281</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42861,7 +42861,7 @@
         <v>46281</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42934,7 +42934,7 @@
         <v>46063</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43007,7 +43007,7 @@
         <v>46281</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43080,7 +43080,7 @@
         <v>46247</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43153,7 +43153,7 @@
         <v>46290</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43226,7 +43226,7 @@
         <v>46247</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43304,7 +43304,7 @@
         <v>46300</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43377,7 +43377,7 @@
         <v>46254</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43455,7 +43455,7 @@
         <v>46300</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43533,7 +43533,7 @@
         <v>46254</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43611,7 +43611,7 @@
         <v>46253</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43684,7 +43684,7 @@
         <v>46070</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43757,7 +43757,7 @@
         <v>46259</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43830,7 +43830,7 @@
         <v>46304</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43903,7 +43903,7 @@
         <v>46304</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43976,7 +43976,7 @@
         <v>45104</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44049,7 +44049,7 @@
         <v>46026</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44122,7 +44122,7 @@
         <v>44607</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44195,7 +44195,7 @@
         <v>44587</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44268,7 +44268,7 @@
         <v>45387</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44341,7 +44341,7 @@
         <v>45373</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44414,7 +44414,7 @@
         <v>45345</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44487,7 +44487,7 @@
         <v>45440</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44560,7 +44560,7 @@
         <v>45595</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44633,7 +44633,7 @@
         <v>44806</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44706,7 +44706,7 @@
         <v>44965</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44779,7 +44779,7 @@
         <v>44531</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44852,7 +44852,7 @@
         <v>44957</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44925,7 +44925,7 @@
         <v>45345</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44998,7 +44998,7 @@
         <v>45345</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45071,7 +45071,7 @@
         <v>45685</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45144,7 +45144,7 @@
         <v>45358</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45217,7 +45217,7 @@
         <v>44957</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45290,7 +45290,7 @@
         <v>45824</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45363,7 +45363,7 @@
         <v>44071</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45436,7 +45436,7 @@
         <v>45890</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45509,7 +45509,7 @@
         <v>45902</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45582,7 +45582,7 @@
         <v>46058</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45655,7 +45655,7 @@
         <v>46062</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45728,7 +45728,7 @@
         <v>46062</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45801,7 +45801,7 @@
         <v>46063</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45874,7 +45874,7 @@
         <v>46062</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45947,7 +45947,7 @@
         <v>46062</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46020,7 +46020,7 @@
         <v>46065</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46093,7 +46093,7 @@
         <v>46110</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46166,7 +46166,7 @@
         <v>46300</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>

--- a/Översikt KALMAR.xlsx
+++ b/Översikt KALMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45209</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>44876</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45952</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>45345</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>46066</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>44876</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>46058</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>44979</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>44601</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>45947</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>44489</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>44876</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>45915</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>44876</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>45324</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>45664</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>45561</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>46085</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>44522</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>44951</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>46300</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>46303</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44984</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>45463</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>44970</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3568,7 +3568,7 @@
         <v>45953</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>44993</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>44979</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>44853</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4005,7 +4005,7 @@
         <v>45254</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>44489</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>45684</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>44595</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>44489</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>44784</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>44970</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>44785</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>44575</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>44785</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>45943</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>45118</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>45044</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5438,7 +5438,7 @@
         <v>44951</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5545,7 +5545,7 @@
         <v>45114</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5656,7 +5656,7 @@
         <v>45363</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         <v>46300</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
         <v>44616</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>44595</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
         <v>45903</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>45954</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         <v>44517</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6430,7 +6430,7 @@
         <v>45575</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6536,7 +6536,7 @@
         <v>45243</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
         <v>45722</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         <v>44802</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6863,7 +6863,7 @@
         <v>44994</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         <v>44994</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         <v>46055</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7185,7 +7185,7 @@
         <v>45874</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7291,7 +7291,7 @@
         <v>45924</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7397,7 +7397,7 @@
         <v>44796</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         <v>46049</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         <v>45190</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7719,7 +7719,7 @@
         <v>46119</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7825,7 +7825,7 @@
         <v>46119</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>45105</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         <v>45314</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>45966</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8249,7 +8249,7 @@
         <v>44517</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
         <v>46279</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>46245</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         <v>45275</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8686,7 +8686,7 @@
         <v>44827</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         <v>46253</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         <v>45475</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9012,7 +9012,7 @@
         <v>45448</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>44623</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>44740</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>44895</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         <v>45264</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>44575</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9651,7 +9651,7 @@
         <v>45163</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>45086</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9865,7 +9865,7 @@
         <v>45007</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>45180</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         <v>45167</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10184,7 +10184,7 @@
         <v>45007</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>45917</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10394,7 +10394,7 @@
         <v>44915</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>44914</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10604,7 +10604,7 @@
         <v>44991</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10709,7 +10709,7 @@
         <v>44810</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>45069</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10919,7 +10919,7 @@
         <v>46177</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>44855</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
         <v>46188</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11248,7 +11248,7 @@
         <v>45063</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11362,7 +11362,7 @@
         <v>44949</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11467,7 +11467,7 @@
         <v>45117</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11572,7 +11572,7 @@
         <v>46119</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>45083</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
         <v>46199</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11887,7 +11887,7 @@
         <v>44931</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>45090</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12097,7 +12097,7 @@
         <v>46247</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12202,7 +12202,7 @@
         <v>44931</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12307,7 +12307,7 @@
         <v>46247</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12421,7 +12421,7 @@
         <v>45007</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12530,7 +12530,7 @@
         <v>46300</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12640,7 +12640,7 @@
         <v>45782</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12750,7 +12750,7 @@
         <v>46300</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12864,7 +12864,7 @@
         <v>45775</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12969,7 +12969,7 @@
         <v>46258</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13074,7 +13074,7 @@
         <v>45544</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
         <v>46300</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13288,7 +13288,7 @@
         <v>45454</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13393,7 +13393,7 @@
         <v>45791</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13498,7 +13498,7 @@
         <v>46304</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13603,7 +13603,7 @@
         <v>45574</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13713,7 +13713,7 @@
         <v>45868</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13818,7 +13818,7 @@
         <v>44810</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13928,7 +13928,7 @@
         <v>44586</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14033,7 +14033,7 @@
         <v>45611</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14138,7 +14138,7 @@
         <v>45373</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14247,7 +14247,7 @@
         <v>46063</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14352,7 +14352,7 @@
         <v>46087</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14457,7 +14457,7 @@
         <v>44643</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14530,7 +14530,7 @@
         <v>44823</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>44497</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14676,7 +14676,7 @@
         <v>44505</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14749,7 +14749,7 @@
         <v>44852</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14822,7 +14822,7 @@
         <v>44684</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14895,7 +14895,7 @@
         <v>44629</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>44539</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         <v>44498</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         <v>44498</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15187,7 +15187,7 @@
         <v>44489</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15260,7 +15260,7 @@
         <v>44525</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15333,7 +15333,7 @@
         <v>44823</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15406,7 +15406,7 @@
         <v>44790</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15479,7 +15479,7 @@
         <v>44531</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15552,7 +15552,7 @@
         <v>44602</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15625,7 +15625,7 @@
         <v>44858</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15698,7 +15698,7 @@
         <v>44522</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>44823</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15844,7 +15844,7 @@
         <v>44818</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15917,7 +15917,7 @@
         <v>44858</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15990,7 +15990,7 @@
         <v>44858</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16063,7 +16063,7 @@
         <v>44852</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16136,7 +16136,7 @@
         <v>44858</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16209,7 +16209,7 @@
         <v>44615</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16282,7 +16282,7 @@
         <v>44586</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16355,7 +16355,7 @@
         <v>44502</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16428,7 +16428,7 @@
         <v>44552</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16501,7 +16501,7 @@
         <v>44620</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         <v>44625</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16647,7 +16647,7 @@
         <v>44784</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16720,7 +16720,7 @@
         <v>44654</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16793,7 +16793,7 @@
         <v>44855</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16866,7 +16866,7 @@
         <v>44858</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16939,7 +16939,7 @@
         <v>44810</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17012,7 +17012,7 @@
         <v>44732</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17085,7 +17085,7 @@
         <v>44858</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17158,7 +17158,7 @@
         <v>44511</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17231,7 +17231,7 @@
         <v>45411</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17304,7 +17304,7 @@
         <v>44924</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17377,7 +17377,7 @@
         <v>44595</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17450,7 +17450,7 @@
         <v>44988</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17523,7 +17523,7 @@
         <v>45161</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17596,7 +17596,7 @@
         <v>45090</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17669,7 +17669,7 @@
         <v>45090</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17742,7 +17742,7 @@
         <v>45090</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17815,7 +17815,7 @@
         <v>45097</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17888,7 +17888,7 @@
         <v>45735</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17961,7 +17961,7 @@
         <v>45205</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18034,7 +18034,7 @@
         <v>45272</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18107,7 +18107,7 @@
         <v>45618</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>44846</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18253,7 +18253,7 @@
         <v>44993</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18326,7 +18326,7 @@
         <v>45099</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18399,7 +18399,7 @@
         <v>44502</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18472,7 +18472,7 @@
         <v>45195</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18545,7 +18545,7 @@
         <v>45349</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18618,7 +18618,7 @@
         <v>44855</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18691,7 +18691,7 @@
         <v>45233</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18764,7 +18764,7 @@
         <v>44924</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18837,7 +18837,7 @@
         <v>44991</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18910,7 +18910,7 @@
         <v>44861</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18983,7 +18983,7 @@
         <v>45153</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19056,7 +19056,7 @@
         <v>44864</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19129,7 +19129,7 @@
         <v>45173</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19202,7 +19202,7 @@
         <v>45173</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19275,7 +19275,7 @@
         <v>44712</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19348,7 +19348,7 @@
         <v>45219</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19421,7 +19421,7 @@
         <v>45250</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>45219</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19567,7 +19567,7 @@
         <v>45272</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19640,7 +19640,7 @@
         <v>44993</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         <v>45028</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19786,7 +19786,7 @@
         <v>45189</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19859,7 +19859,7 @@
         <v>45400</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19932,7 +19932,7 @@
         <v>45239</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20010,7 +20010,7 @@
         <v>44782</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20083,7 +20083,7 @@
         <v>45058</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20156,7 +20156,7 @@
         <v>45720</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20229,7 +20229,7 @@
         <v>45104</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20307,7 +20307,7 @@
         <v>45110</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20385,7 +20385,7 @@
         <v>45341</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20458,7 +20458,7 @@
         <v>44529</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20531,7 +20531,7 @@
         <v>45104</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20604,7 +20604,7 @@
         <v>45104</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20677,7 +20677,7 @@
         <v>45335</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20755,7 +20755,7 @@
         <v>45180</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20828,7 +20828,7 @@
         <v>44971</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20901,7 +20901,7 @@
         <v>45061</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20974,7 +20974,7 @@
         <v>44984</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21067,7 +21067,7 @@
         <v>44984</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21140,7 +21140,7 @@
         <v>45182</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21213,7 +21213,7 @@
         <v>44617</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21286,7 +21286,7 @@
         <v>44617</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21359,7 +21359,7 @@
         <v>45007</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21432,7 +21432,7 @@
         <v>45007</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21505,7 +21505,7 @@
         <v>45205</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         <v>45096</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21651,7 +21651,7 @@
         <v>45170</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21724,7 +21724,7 @@
         <v>45212</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21797,7 +21797,7 @@
         <v>45091</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21870,7 +21870,7 @@
         <v>44645</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21943,7 +21943,7 @@
         <v>44973</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22016,7 +22016,7 @@
         <v>45707</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22089,7 +22089,7 @@
         <v>45796</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22162,7 +22162,7 @@
         <v>45688</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22235,7 +22235,7 @@
         <v>45923</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22308,7 +22308,7 @@
         <v>44963</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22381,7 +22381,7 @@
         <v>46036</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22454,7 +22454,7 @@
         <v>45540</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22527,7 +22527,7 @@
         <v>44816</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22600,7 +22600,7 @@
         <v>45688</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22673,7 +22673,7 @@
         <v>44914</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22746,7 +22746,7 @@
         <v>45796</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22819,7 +22819,7 @@
         <v>45544</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22897,7 +22897,7 @@
         <v>44529</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22970,7 +22970,7 @@
         <v>45789</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23043,7 +23043,7 @@
         <v>45492</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23116,7 +23116,7 @@
         <v>45173</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23189,7 +23189,7 @@
         <v>45104</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23262,7 +23262,7 @@
         <v>46139</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23335,7 +23335,7 @@
         <v>44872</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23408,7 +23408,7 @@
         <v>45113</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23481,7 +23481,7 @@
         <v>45091</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23554,7 +23554,7 @@
         <v>45167</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23627,7 +23627,7 @@
         <v>45764</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23700,7 +23700,7 @@
         <v>45233</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23773,7 +23773,7 @@
         <v>44994</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23846,7 +23846,7 @@
         <v>45630</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23919,7 +23919,7 @@
         <v>45727</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23992,7 +23992,7 @@
         <v>45252</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>45544</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24138,7 +24138,7 @@
         <v>45719</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24216,7 +24216,7 @@
         <v>45406</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24289,7 +24289,7 @@
         <v>45564</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24362,7 +24362,7 @@
         <v>45267</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24435,7 +24435,7 @@
         <v>44502</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24508,7 +24508,7 @@
         <v>45840</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24581,7 +24581,7 @@
         <v>46099</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24654,7 +24654,7 @@
         <v>45198</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24727,7 +24727,7 @@
         <v>45912</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24800,7 +24800,7 @@
         <v>45912</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>45243</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24946,7 +24946,7 @@
         <v>44846</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25019,7 +25019,7 @@
         <v>45548</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>45923</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25165,7 +25165,7 @@
         <v>45924</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25238,7 +25238,7 @@
         <v>45070</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25316,7 +25316,7 @@
         <v>44909</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25389,7 +25389,7 @@
         <v>45215</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25462,7 +25462,7 @@
         <v>45246</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         <v>45930</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25608,7 +25608,7 @@
         <v>45932</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>45268</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25754,7 +25754,7 @@
         <v>45939</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25827,7 +25827,7 @@
         <v>45229</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25900,7 +25900,7 @@
         <v>45595</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25973,7 +25973,7 @@
         <v>45628</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26046,7 +26046,7 @@
         <v>45252</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26119,7 +26119,7 @@
         <v>46155</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26192,7 +26192,7 @@
         <v>45233</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26265,7 +26265,7 @@
         <v>44566</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26338,7 +26338,7 @@
         <v>45418</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26411,7 +26411,7 @@
         <v>45716</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26484,7 +26484,7 @@
         <v>45345</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26557,7 +26557,7 @@
         <v>46155</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26630,7 +26630,7 @@
         <v>45028</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26703,7 +26703,7 @@
         <v>45713</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26776,7 +26776,7 @@
         <v>45903</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26849,7 +26849,7 @@
         <v>44497</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26922,7 +26922,7 @@
         <v>45618</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26995,7 +26995,7 @@
         <v>45695</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27068,7 +27068,7 @@
         <v>45006</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27141,7 +27141,7 @@
         <v>46160</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27214,7 +27214,7 @@
         <v>45236</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27287,7 +27287,7 @@
         <v>46160</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27360,7 +27360,7 @@
         <v>45229</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27433,7 +27433,7 @@
         <v>46162</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27506,7 +27506,7 @@
         <v>46162</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27579,7 +27579,7 @@
         <v>45930</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27652,7 +27652,7 @@
         <v>44971</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27725,7 +27725,7 @@
         <v>45093</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27798,7 +27798,7 @@
         <v>45978</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27871,7 +27871,7 @@
         <v>46162</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27944,7 +27944,7 @@
         <v>45153</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28017,7 +28017,7 @@
         <v>44915</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28090,7 +28090,7 @@
         <v>44914</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28163,7 +28163,7 @@
         <v>44895</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28236,7 +28236,7 @@
         <v>45551</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28309,7 +28309,7 @@
         <v>45327</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28382,7 +28382,7 @@
         <v>44939</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28455,7 +28455,7 @@
         <v>45246</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28528,7 +28528,7 @@
         <v>45246</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28601,7 +28601,7 @@
         <v>44973</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28674,7 +28674,7 @@
         <v>45378</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28747,7 +28747,7 @@
         <v>45175</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28820,7 +28820,7 @@
         <v>45173</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28893,7 +28893,7 @@
         <v>45306</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28966,7 +28966,7 @@
         <v>45091</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29039,7 +29039,7 @@
         <v>44629</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29112,7 +29112,7 @@
         <v>44862</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29185,7 +29185,7 @@
         <v>46008</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29258,7 +29258,7 @@
         <v>45574</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29336,7 +29336,7 @@
         <v>46010</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29409,7 +29409,7 @@
         <v>45097</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29482,7 +29482,7 @@
         <v>46013</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29555,7 +29555,7 @@
         <v>45628</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29628,7 +29628,7 @@
         <v>46099</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29701,7 +29701,7 @@
         <v>44539</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29774,7 +29774,7 @@
         <v>45154</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29847,7 +29847,7 @@
         <v>45182</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29920,7 +29920,7 @@
         <v>44909</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29993,7 +29993,7 @@
         <v>44988</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30066,7 +30066,7 @@
         <v>45266</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30139,7 +30139,7 @@
         <v>45625</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>45629</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30285,7 +30285,7 @@
         <v>45188</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30358,7 +30358,7 @@
         <v>45915</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30431,7 +30431,7 @@
         <v>46177</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30504,7 +30504,7 @@
         <v>44803</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30577,7 +30577,7 @@
         <v>45402</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30655,7 +30655,7 @@
         <v>45680</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30728,7 +30728,7 @@
         <v>46048</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30801,7 +30801,7 @@
         <v>46049</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30874,7 +30874,7 @@
         <v>46054</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30947,7 +30947,7 @@
         <v>46054</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31020,7 +31020,7 @@
         <v>44966</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31093,7 +31093,7 @@
         <v>44595</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31166,7 +31166,7 @@
         <v>45097</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31239,7 +31239,7 @@
         <v>45685</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31312,7 +31312,7 @@
         <v>46063</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31385,7 +31385,7 @@
         <v>46062</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31458,7 +31458,7 @@
         <v>45044</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31531,7 +31531,7 @@
         <v>46063</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31604,7 +31604,7 @@
         <v>44939</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31677,7 +31677,7 @@
         <v>45470</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31750,7 +31750,7 @@
         <v>46188</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31823,7 +31823,7 @@
         <v>46070</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31896,7 +31896,7 @@
         <v>45125</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31969,7 +31969,7 @@
         <v>46185</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32042,7 +32042,7 @@
         <v>45387</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32115,7 +32115,7 @@
         <v>45387</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32188,7 +32188,7 @@
         <v>45476</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32261,7 +32261,7 @@
         <v>44882</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32334,7 +32334,7 @@
         <v>45624</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32407,7 +32407,7 @@
         <v>45534</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32480,7 +32480,7 @@
         <v>44959</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32553,7 +32553,7 @@
         <v>46092</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32626,7 +32626,7 @@
         <v>46092</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32699,7 +32699,7 @@
         <v>46036</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32772,7 +32772,7 @@
         <v>46093</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32845,7 +32845,7 @@
         <v>44544</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32918,7 +32918,7 @@
         <v>44847</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32991,7 +32991,7 @@
         <v>46178</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33064,7 +33064,7 @@
         <v>44543</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33137,7 +33137,7 @@
         <v>45202</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33210,7 +33210,7 @@
         <v>46099</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33283,7 +33283,7 @@
         <v>45050</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33356,7 +33356,7 @@
         <v>45308</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33429,7 +33429,7 @@
         <v>44993</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33502,7 +33502,7 @@
         <v>44782</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33575,7 +33575,7 @@
         <v>46108</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33648,7 +33648,7 @@
         <v>46112</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33721,7 +33721,7 @@
         <v>46197</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33794,7 +33794,7 @@
         <v>45075</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33867,7 +33867,7 @@
         <v>46198</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33940,7 +33940,7 @@
         <v>46119</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34013,7 +34013,7 @@
         <v>46119</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34086,7 +34086,7 @@
         <v>46199</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34159,7 +34159,7 @@
         <v>45114</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34232,7 +34232,7 @@
         <v>46202</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34305,7 +34305,7 @@
         <v>45173</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34378,7 +34378,7 @@
         <v>45387</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34451,7 +34451,7 @@
         <v>45387</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34524,7 +34524,7 @@
         <v>46203</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34597,7 +34597,7 @@
         <v>46134</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34670,7 +34670,7 @@
         <v>46134</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34743,7 +34743,7 @@
         <v>44564</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34816,7 +34816,7 @@
         <v>46139</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34889,7 +34889,7 @@
         <v>45915</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34962,7 +34962,7 @@
         <v>46139</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35035,7 +35035,7 @@
         <v>45149</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35108,7 +35108,7 @@
         <v>45149</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35181,7 +35181,7 @@
         <v>45141</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35254,7 +35254,7 @@
         <v>46154</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35327,7 +35327,7 @@
         <v>44574</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35400,7 +35400,7 @@
         <v>44971</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35473,7 +35473,7 @@
         <v>45034</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35546,7 +35546,7 @@
         <v>45205</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35619,7 +35619,7 @@
         <v>46009</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35692,7 +35692,7 @@
         <v>45524</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35765,7 +35765,7 @@
         <v>45099</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35838,7 +35838,7 @@
         <v>45212</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35911,7 +35911,7 @@
         <v>45607</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35984,7 +35984,7 @@
         <v>45233</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36057,7 +36057,7 @@
         <v>45540</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36130,7 +36130,7 @@
         <v>45169</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36203,7 +36203,7 @@
         <v>45246</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36276,7 +36276,7 @@
         <v>46063</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36349,7 +36349,7 @@
         <v>45118</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36422,7 +36422,7 @@
         <v>46111</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36495,7 +36495,7 @@
         <v>44656</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36568,7 +36568,7 @@
         <v>44690</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36641,7 +36641,7 @@
         <v>46223</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36714,7 +36714,7 @@
         <v>44819</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36787,7 +36787,7 @@
         <v>44952</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36860,7 +36860,7 @@
         <v>45323</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36933,7 +36933,7 @@
         <v>45092</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37006,7 +37006,7 @@
         <v>46272</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37079,7 +37079,7 @@
         <v>45086</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37152,7 +37152,7 @@
         <v>46273</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37225,7 +37225,7 @@
         <v>46273</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37298,7 +37298,7 @@
         <v>44895</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37371,7 +37371,7 @@
         <v>45156</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37444,7 +37444,7 @@
         <v>46275</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37517,7 +37517,7 @@
         <v>46274</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37590,7 +37590,7 @@
         <v>45034</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37663,7 +37663,7 @@
         <v>45254</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37736,7 +37736,7 @@
         <v>45174</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37809,7 +37809,7 @@
         <v>46276</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37882,7 +37882,7 @@
         <v>45363</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37955,7 +37955,7 @@
         <v>44818</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38028,7 +38028,7 @@
         <v>46276</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38101,7 +38101,7 @@
         <v>45531</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38174,7 +38174,7 @@
         <v>45324</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38247,7 +38247,7 @@
         <v>46281</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38320,7 +38320,7 @@
         <v>46281</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38393,7 +38393,7 @@
         <v>45454</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38466,7 +38466,7 @@
         <v>46281</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38539,7 +38539,7 @@
         <v>45703</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38612,7 +38612,7 @@
         <v>44564</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38685,7 +38685,7 @@
         <v>46063</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38758,7 +38758,7 @@
         <v>45209</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38831,7 +38831,7 @@
         <v>45209</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38904,7 +38904,7 @@
         <v>45091</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38977,7 +38977,7 @@
         <v>45260</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39050,7 +39050,7 @@
         <v>44978</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39123,7 +39123,7 @@
         <v>45273</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39196,7 +39196,7 @@
         <v>45334</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39269,7 +39269,7 @@
         <v>45189</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39342,7 +39342,7 @@
         <v>45356</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39415,7 +39415,7 @@
         <v>46247</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39493,7 +39493,7 @@
         <v>45027</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39566,7 +39566,7 @@
         <v>46290</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39639,7 +39639,7 @@
         <v>45067</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39712,7 +39712,7 @@
         <v>44823</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39785,7 +39785,7 @@
         <v>44823</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39858,7 +39858,7 @@
         <v>44732</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39931,7 +39931,7 @@
         <v>44963</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40004,7 +40004,7 @@
         <v>44963</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40077,7 +40077,7 @@
         <v>45341</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40150,7 +40150,7 @@
         <v>46247</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40223,7 +40223,7 @@
         <v>45618</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40296,7 +40296,7 @@
         <v>45540</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40369,7 +40369,7 @@
         <v>45076</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40447,7 +40447,7 @@
         <v>45156</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40520,7 +40520,7 @@
         <v>44824</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40593,7 +40593,7 @@
         <v>45001</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40666,7 +40666,7 @@
         <v>44658</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40739,7 +40739,7 @@
         <v>45114</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40812,7 +40812,7 @@
         <v>46254</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40890,7 +40890,7 @@
         <v>46254</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40968,7 +40968,7 @@
         <v>46253</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41041,7 +41041,7 @@
         <v>45229</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41114,7 +41114,7 @@
         <v>44924</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41187,7 +41187,7 @@
         <v>45119</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41260,7 +41260,7 @@
         <v>44858</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41333,7 +41333,7 @@
         <v>46300</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41411,7 +41411,7 @@
         <v>45181</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41484,7 +41484,7 @@
         <v>45775</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41557,7 +41557,7 @@
         <v>45558</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41635,7 +41635,7 @@
         <v>45439</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41708,7 +41708,7 @@
         <v>45443</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41781,7 +41781,7 @@
         <v>45551</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41854,7 +41854,7 @@
         <v>45246</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41927,7 +41927,7 @@
         <v>46070</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42000,7 +42000,7 @@
         <v>45785</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42073,7 +42073,7 @@
         <v>46300</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42146,7 +42146,7 @@
         <v>45664</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42219,7 +42219,7 @@
         <v>45664</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42292,7 +42292,7 @@
         <v>45566</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42365,7 +42365,7 @@
         <v>45730</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42438,7 +42438,7 @@
         <v>45363</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42511,7 +42511,7 @@
         <v>45791</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42584,7 +42584,7 @@
         <v>46259</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42657,7 +42657,7 @@
         <v>45792</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42735,7 +42735,7 @@
         <v>46304</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42808,7 +42808,7 @@
         <v>45104</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42881,7 +42881,7 @@
         <v>46026</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42954,7 +42954,7 @@
         <v>46304</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43027,7 +43027,7 @@
         <v>45720</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43100,7 +43100,7 @@
         <v>45805</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43173,7 +43173,7 @@
         <v>45812</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43246,7 +43246,7 @@
         <v>46269</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43319,7 +43319,7 @@
         <v>45842</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43392,7 +43392,7 @@
         <v>45842</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43465,7 +43465,7 @@
         <v>45861</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43538,7 +43538,7 @@
         <v>45831</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43611,7 +43611,7 @@
         <v>45764</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43684,7 +43684,7 @@
         <v>45779</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43757,7 +43757,7 @@
         <v>45874</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43830,7 +43830,7 @@
         <v>45785</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43903,7 +43903,7 @@
         <v>45387</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43976,7 +43976,7 @@
         <v>45373</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44049,7 +44049,7 @@
         <v>45345</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44122,7 +44122,7 @@
         <v>45440</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44195,7 +44195,7 @@
         <v>44607</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44268,7 +44268,7 @@
         <v>45595</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44341,7 +44341,7 @@
         <v>44587</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44414,7 +44414,7 @@
         <v>44806</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44487,7 +44487,7 @@
         <v>44965</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44560,7 +44560,7 @@
         <v>44531</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44633,7 +44633,7 @@
         <v>44957</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44706,7 +44706,7 @@
         <v>45345</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44779,7 +44779,7 @@
         <v>45345</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44852,7 +44852,7 @@
         <v>45685</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44925,7 +44925,7 @@
         <v>45358</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44998,7 +44998,7 @@
         <v>44957</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45071,7 +45071,7 @@
         <v>45824</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45144,7 +45144,7 @@
         <v>44071</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45217,7 +45217,7 @@
         <v>45890</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45290,7 +45290,7 @@
         <v>45902</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45363,7 +45363,7 @@
         <v>46058</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45436,7 +45436,7 @@
         <v>46062</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45509,7 +45509,7 @@
         <v>46062</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45582,7 +45582,7 @@
         <v>46063</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45655,7 +45655,7 @@
         <v>46062</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45728,7 +45728,7 @@
         <v>46062</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45801,7 +45801,7 @@
         <v>46065</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45874,7 +45874,7 @@
         <v>46110</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45947,7 +45947,7 @@
         <v>46300</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>

--- a/Översikt KALMAR.xlsx
+++ b/Översikt KALMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45209</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>44876</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45952</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>45345</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>46066</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>44876</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>46058</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>44979</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>44601</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>45947</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>44489</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>44876</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>45915</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>44876</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>45324</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>45664</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>45561</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>46085</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>44522</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>44951</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>46300</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>46303</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44984</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>45463</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>44970</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3568,7 +3568,7 @@
         <v>45953</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>44993</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>44979</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>44853</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4005,7 +4005,7 @@
         <v>45254</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>44489</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>45684</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>44595</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>44489</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>44784</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>44970</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>44785</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>44575</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>44785</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>45943</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>45118</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>45044</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5438,7 +5438,7 @@
         <v>44951</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5545,7 +5545,7 @@
         <v>45114</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5656,7 +5656,7 @@
         <v>45363</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         <v>46300</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
         <v>44616</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>44595</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
         <v>45903</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>45954</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         <v>44517</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6430,7 +6430,7 @@
         <v>45575</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6536,7 +6536,7 @@
         <v>45243</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
         <v>45722</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         <v>44802</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6863,7 +6863,7 @@
         <v>44994</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         <v>44994</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         <v>46055</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7185,7 +7185,7 @@
         <v>45874</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7291,7 +7291,7 @@
         <v>45924</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7397,7 +7397,7 @@
         <v>44796</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         <v>46049</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         <v>45190</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7719,7 +7719,7 @@
         <v>46119</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7825,7 +7825,7 @@
         <v>46119</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>45105</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         <v>45314</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>45966</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8249,7 +8249,7 @@
         <v>44517</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
         <v>46279</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>46245</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         <v>45275</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8686,7 +8686,7 @@
         <v>44827</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         <v>46253</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         <v>45475</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9012,7 +9012,7 @@
         <v>45448</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>44623</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>44740</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>44895</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         <v>45264</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>44575</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9651,7 +9651,7 @@
         <v>45163</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>45086</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9865,7 +9865,7 @@
         <v>45007</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>45180</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         <v>45167</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10184,7 +10184,7 @@
         <v>45007</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>45917</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10394,7 +10394,7 @@
         <v>44915</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>44914</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10604,7 +10604,7 @@
         <v>44991</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10709,7 +10709,7 @@
         <v>44810</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>45069</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10919,7 +10919,7 @@
         <v>46177</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>44855</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
         <v>46188</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11248,7 +11248,7 @@
         <v>45063</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11362,7 +11362,7 @@
         <v>44949</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11467,7 +11467,7 @@
         <v>45117</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11572,7 +11572,7 @@
         <v>46119</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>45083</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
         <v>46199</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11887,7 +11887,7 @@
         <v>44931</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>45090</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12097,7 +12097,7 @@
         <v>46247</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12202,7 +12202,7 @@
         <v>44931</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12307,7 +12307,7 @@
         <v>46247</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12421,7 +12421,7 @@
         <v>45007</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12530,7 +12530,7 @@
         <v>46300</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12640,7 +12640,7 @@
         <v>45782</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12750,7 +12750,7 @@
         <v>46300</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12864,7 +12864,7 @@
         <v>45775</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12969,7 +12969,7 @@
         <v>46258</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13074,7 +13074,7 @@
         <v>45544</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
         <v>46300</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13288,7 +13288,7 @@
         <v>45454</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13393,7 +13393,7 @@
         <v>45791</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13498,7 +13498,7 @@
         <v>46304</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13603,7 +13603,7 @@
         <v>45574</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13713,7 +13713,7 @@
         <v>45868</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13818,7 +13818,7 @@
         <v>44810</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13928,7 +13928,7 @@
         <v>44586</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14033,7 +14033,7 @@
         <v>45611</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14138,7 +14138,7 @@
         <v>45373</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14247,7 +14247,7 @@
         <v>46063</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14352,7 +14352,7 @@
         <v>46087</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14457,7 +14457,7 @@
         <v>44643</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14530,7 +14530,7 @@
         <v>44823</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>44497</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14676,7 +14676,7 @@
         <v>44505</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14749,7 +14749,7 @@
         <v>44852</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14822,7 +14822,7 @@
         <v>44684</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14895,7 +14895,7 @@
         <v>44629</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>44539</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         <v>44498</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         <v>44498</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15187,7 +15187,7 @@
         <v>44489</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15260,7 +15260,7 @@
         <v>44525</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15333,7 +15333,7 @@
         <v>44823</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15406,7 +15406,7 @@
         <v>44790</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15479,7 +15479,7 @@
         <v>44531</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15552,7 +15552,7 @@
         <v>44602</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15625,7 +15625,7 @@
         <v>44858</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15698,7 +15698,7 @@
         <v>44522</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>44823</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15844,7 +15844,7 @@
         <v>44818</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15917,7 +15917,7 @@
         <v>44858</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15990,7 +15990,7 @@
         <v>44858</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16063,7 +16063,7 @@
         <v>44852</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16136,7 +16136,7 @@
         <v>44858</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16209,7 +16209,7 @@
         <v>44615</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16282,7 +16282,7 @@
         <v>44586</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16355,7 +16355,7 @@
         <v>44502</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16428,7 +16428,7 @@
         <v>44552</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16501,7 +16501,7 @@
         <v>44620</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         <v>44625</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16647,7 +16647,7 @@
         <v>44784</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16720,7 +16720,7 @@
         <v>44654</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16793,7 +16793,7 @@
         <v>44855</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16866,7 +16866,7 @@
         <v>44858</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16939,7 +16939,7 @@
         <v>44810</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17012,7 +17012,7 @@
         <v>44732</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17085,7 +17085,7 @@
         <v>44858</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17158,7 +17158,7 @@
         <v>44511</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17231,7 +17231,7 @@
         <v>45411</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17304,7 +17304,7 @@
         <v>44924</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17377,7 +17377,7 @@
         <v>44595</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17450,7 +17450,7 @@
         <v>44988</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17523,7 +17523,7 @@
         <v>45161</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17596,7 +17596,7 @@
         <v>45090</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17669,7 +17669,7 @@
         <v>45090</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17742,7 +17742,7 @@
         <v>45090</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17815,7 +17815,7 @@
         <v>45097</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17888,7 +17888,7 @@
         <v>45735</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17961,7 +17961,7 @@
         <v>45205</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18034,7 +18034,7 @@
         <v>45272</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18107,7 +18107,7 @@
         <v>45618</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>44846</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18253,7 +18253,7 @@
         <v>44993</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18326,7 +18326,7 @@
         <v>45099</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18399,7 +18399,7 @@
         <v>44502</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18472,7 +18472,7 @@
         <v>45195</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18545,7 +18545,7 @@
         <v>45349</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18618,7 +18618,7 @@
         <v>44855</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18691,7 +18691,7 @@
         <v>45233</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18764,7 +18764,7 @@
         <v>44924</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18837,7 +18837,7 @@
         <v>44991</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18910,7 +18910,7 @@
         <v>44861</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18983,7 +18983,7 @@
         <v>45153</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19056,7 +19056,7 @@
         <v>44864</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19129,7 +19129,7 @@
         <v>45173</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19202,7 +19202,7 @@
         <v>45173</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19275,7 +19275,7 @@
         <v>44712</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19348,7 +19348,7 @@
         <v>45219</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19421,7 +19421,7 @@
         <v>45250</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>45219</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19567,7 +19567,7 @@
         <v>45272</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19640,7 +19640,7 @@
         <v>44993</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         <v>45028</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19786,7 +19786,7 @@
         <v>45189</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19859,7 +19859,7 @@
         <v>45400</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19932,7 +19932,7 @@
         <v>45239</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20010,7 +20010,7 @@
         <v>44782</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20083,7 +20083,7 @@
         <v>45058</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20156,7 +20156,7 @@
         <v>45720</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20229,7 +20229,7 @@
         <v>45104</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20307,7 +20307,7 @@
         <v>45110</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20385,7 +20385,7 @@
         <v>45341</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20458,7 +20458,7 @@
         <v>44529</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20531,7 +20531,7 @@
         <v>45104</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20604,7 +20604,7 @@
         <v>45104</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20677,7 +20677,7 @@
         <v>45335</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20755,7 +20755,7 @@
         <v>45180</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20828,7 +20828,7 @@
         <v>44971</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20901,7 +20901,7 @@
         <v>45061</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20974,7 +20974,7 @@
         <v>44984</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21067,7 +21067,7 @@
         <v>44984</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21140,7 +21140,7 @@
         <v>45182</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21213,7 +21213,7 @@
         <v>44617</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21286,7 +21286,7 @@
         <v>44617</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21359,7 +21359,7 @@
         <v>45007</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21432,7 +21432,7 @@
         <v>45007</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21505,7 +21505,7 @@
         <v>45205</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         <v>45096</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21651,7 +21651,7 @@
         <v>45170</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21724,7 +21724,7 @@
         <v>45212</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21797,7 +21797,7 @@
         <v>45091</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21870,7 +21870,7 @@
         <v>44645</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21943,7 +21943,7 @@
         <v>44973</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22016,7 +22016,7 @@
         <v>45707</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22089,7 +22089,7 @@
         <v>45796</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22162,7 +22162,7 @@
         <v>45688</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22235,7 +22235,7 @@
         <v>45923</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22308,7 +22308,7 @@
         <v>44963</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22381,7 +22381,7 @@
         <v>46036</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22454,7 +22454,7 @@
         <v>45540</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22527,7 +22527,7 @@
         <v>44816</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22600,7 +22600,7 @@
         <v>45688</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22673,7 +22673,7 @@
         <v>44914</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22746,7 +22746,7 @@
         <v>45796</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22819,7 +22819,7 @@
         <v>45544</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22897,7 +22897,7 @@
         <v>44529</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22970,7 +22970,7 @@
         <v>45789</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23043,7 +23043,7 @@
         <v>45492</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23116,7 +23116,7 @@
         <v>45173</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23189,7 +23189,7 @@
         <v>45104</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23262,7 +23262,7 @@
         <v>46139</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23335,7 +23335,7 @@
         <v>44872</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23408,7 +23408,7 @@
         <v>45113</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23481,7 +23481,7 @@
         <v>45091</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23554,7 +23554,7 @@
         <v>45167</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23627,7 +23627,7 @@
         <v>45764</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23700,7 +23700,7 @@
         <v>45233</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23773,7 +23773,7 @@
         <v>44994</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23846,7 +23846,7 @@
         <v>45630</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23919,7 +23919,7 @@
         <v>45727</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23992,7 +23992,7 @@
         <v>45252</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>45544</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24138,7 +24138,7 @@
         <v>45719</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24216,7 +24216,7 @@
         <v>45406</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24289,7 +24289,7 @@
         <v>45564</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24362,7 +24362,7 @@
         <v>45267</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24435,7 +24435,7 @@
         <v>44502</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24508,7 +24508,7 @@
         <v>45840</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24581,7 +24581,7 @@
         <v>46099</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24654,7 +24654,7 @@
         <v>45198</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24727,7 +24727,7 @@
         <v>45912</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24800,7 +24800,7 @@
         <v>45912</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>45243</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24946,7 +24946,7 @@
         <v>44846</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25019,7 +25019,7 @@
         <v>45548</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>45923</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25165,7 +25165,7 @@
         <v>45924</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25238,7 +25238,7 @@
         <v>45070</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25316,7 +25316,7 @@
         <v>44909</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25389,7 +25389,7 @@
         <v>45215</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25462,7 +25462,7 @@
         <v>45246</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         <v>45930</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25608,7 +25608,7 @@
         <v>45932</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>45268</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25754,7 +25754,7 @@
         <v>45939</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25827,7 +25827,7 @@
         <v>45229</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25900,7 +25900,7 @@
         <v>45595</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25973,7 +25973,7 @@
         <v>45628</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26046,7 +26046,7 @@
         <v>45252</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26119,7 +26119,7 @@
         <v>46155</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26192,7 +26192,7 @@
         <v>45233</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26265,7 +26265,7 @@
         <v>44566</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26338,7 +26338,7 @@
         <v>45418</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26411,7 +26411,7 @@
         <v>45716</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26484,7 +26484,7 @@
         <v>45345</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26557,7 +26557,7 @@
         <v>46155</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26630,7 +26630,7 @@
         <v>45028</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26703,7 +26703,7 @@
         <v>45713</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26776,7 +26776,7 @@
         <v>45903</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26849,7 +26849,7 @@
         <v>44497</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26922,7 +26922,7 @@
         <v>45618</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26995,7 +26995,7 @@
         <v>45695</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27068,7 +27068,7 @@
         <v>45006</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27141,7 +27141,7 @@
         <v>46160</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27214,7 +27214,7 @@
         <v>45236</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27287,7 +27287,7 @@
         <v>46160</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27360,7 +27360,7 @@
         <v>45229</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27433,7 +27433,7 @@
         <v>46162</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27506,7 +27506,7 @@
         <v>46162</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27579,7 +27579,7 @@
         <v>45930</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27652,7 +27652,7 @@
         <v>44971</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27725,7 +27725,7 @@
         <v>45093</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27798,7 +27798,7 @@
         <v>45978</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27871,7 +27871,7 @@
         <v>46162</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27944,7 +27944,7 @@
         <v>45153</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28017,7 +28017,7 @@
         <v>44915</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28090,7 +28090,7 @@
         <v>44914</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28163,7 +28163,7 @@
         <v>44895</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28236,7 +28236,7 @@
         <v>45551</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28309,7 +28309,7 @@
         <v>45327</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28382,7 +28382,7 @@
         <v>44939</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28455,7 +28455,7 @@
         <v>45246</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28528,7 +28528,7 @@
         <v>45246</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28601,7 +28601,7 @@
         <v>44973</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28674,7 +28674,7 @@
         <v>45378</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28747,7 +28747,7 @@
         <v>45175</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28820,7 +28820,7 @@
         <v>45173</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28893,7 +28893,7 @@
         <v>45306</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28966,7 +28966,7 @@
         <v>45091</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29039,7 +29039,7 @@
         <v>44629</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29112,7 +29112,7 @@
         <v>44862</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29185,7 +29185,7 @@
         <v>46008</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29258,7 +29258,7 @@
         <v>45574</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29336,7 +29336,7 @@
         <v>46010</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29409,7 +29409,7 @@
         <v>45097</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29482,7 +29482,7 @@
         <v>46013</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29555,7 +29555,7 @@
         <v>45628</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29628,7 +29628,7 @@
         <v>46099</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29701,7 +29701,7 @@
         <v>44539</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29774,7 +29774,7 @@
         <v>45154</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29847,7 +29847,7 @@
         <v>45182</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29920,7 +29920,7 @@
         <v>44909</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29993,7 +29993,7 @@
         <v>44988</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30066,7 +30066,7 @@
         <v>45266</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30139,7 +30139,7 @@
         <v>45625</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>45629</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30285,7 +30285,7 @@
         <v>45188</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30358,7 +30358,7 @@
         <v>45915</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30431,7 +30431,7 @@
         <v>46177</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30504,7 +30504,7 @@
         <v>44803</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30577,7 +30577,7 @@
         <v>45402</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30655,7 +30655,7 @@
         <v>45680</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30728,7 +30728,7 @@
         <v>46048</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30801,7 +30801,7 @@
         <v>46049</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30874,7 +30874,7 @@
         <v>46054</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30947,7 +30947,7 @@
         <v>46054</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31020,7 +31020,7 @@
         <v>44966</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31093,7 +31093,7 @@
         <v>44595</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31166,7 +31166,7 @@
         <v>45097</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31239,7 +31239,7 @@
         <v>45685</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31312,7 +31312,7 @@
         <v>46063</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31385,7 +31385,7 @@
         <v>46062</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31458,7 +31458,7 @@
         <v>45044</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31531,7 +31531,7 @@
         <v>46063</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31604,7 +31604,7 @@
         <v>44939</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31677,7 +31677,7 @@
         <v>45470</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31750,7 +31750,7 @@
         <v>46188</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31823,7 +31823,7 @@
         <v>46070</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31896,7 +31896,7 @@
         <v>45125</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31969,7 +31969,7 @@
         <v>46185</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32042,7 +32042,7 @@
         <v>45387</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32115,7 +32115,7 @@
         <v>45387</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32188,7 +32188,7 @@
         <v>45476</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32261,7 +32261,7 @@
         <v>44882</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32334,7 +32334,7 @@
         <v>45624</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32407,7 +32407,7 @@
         <v>45534</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32480,7 +32480,7 @@
         <v>44959</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32553,7 +32553,7 @@
         <v>46092</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32626,7 +32626,7 @@
         <v>46092</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32699,7 +32699,7 @@
         <v>46036</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32772,7 +32772,7 @@
         <v>46093</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32845,7 +32845,7 @@
         <v>44544</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32918,7 +32918,7 @@
         <v>44847</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32991,7 +32991,7 @@
         <v>46178</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33064,7 +33064,7 @@
         <v>44543</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33137,7 +33137,7 @@
         <v>45202</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33210,7 +33210,7 @@
         <v>46099</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33283,7 +33283,7 @@
         <v>45050</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33356,7 +33356,7 @@
         <v>45308</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33429,7 +33429,7 @@
         <v>44993</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33502,7 +33502,7 @@
         <v>44782</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33575,7 +33575,7 @@
         <v>46108</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33648,7 +33648,7 @@
         <v>46112</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33721,7 +33721,7 @@
         <v>46197</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33794,7 +33794,7 @@
         <v>45075</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33867,7 +33867,7 @@
         <v>46198</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33940,7 +33940,7 @@
         <v>46119</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34013,7 +34013,7 @@
         <v>46119</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34086,7 +34086,7 @@
         <v>46199</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34159,7 +34159,7 @@
         <v>45114</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34232,7 +34232,7 @@
         <v>46202</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34305,7 +34305,7 @@
         <v>45173</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34378,7 +34378,7 @@
         <v>45387</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34451,7 +34451,7 @@
         <v>45387</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34524,7 +34524,7 @@
         <v>46203</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34597,7 +34597,7 @@
         <v>46134</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34670,7 +34670,7 @@
         <v>46134</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34743,7 +34743,7 @@
         <v>44564</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34816,7 +34816,7 @@
         <v>46139</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34889,7 +34889,7 @@
         <v>45915</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34962,7 +34962,7 @@
         <v>46139</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35035,7 +35035,7 @@
         <v>45149</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35108,7 +35108,7 @@
         <v>45149</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35181,7 +35181,7 @@
         <v>45141</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35254,7 +35254,7 @@
         <v>46154</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35327,7 +35327,7 @@
         <v>44574</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35400,7 +35400,7 @@
         <v>44971</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35473,7 +35473,7 @@
         <v>45034</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35546,7 +35546,7 @@
         <v>45205</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35619,7 +35619,7 @@
         <v>46009</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35692,7 +35692,7 @@
         <v>45524</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35765,7 +35765,7 @@
         <v>45099</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35838,7 +35838,7 @@
         <v>45212</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35911,7 +35911,7 @@
         <v>45607</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35984,7 +35984,7 @@
         <v>45233</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36057,7 +36057,7 @@
         <v>45540</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36130,7 +36130,7 @@
         <v>45169</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36203,7 +36203,7 @@
         <v>45246</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36276,7 +36276,7 @@
         <v>46063</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36349,7 +36349,7 @@
         <v>45118</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36422,7 +36422,7 @@
         <v>46111</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36495,7 +36495,7 @@
         <v>44656</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36568,7 +36568,7 @@
         <v>44690</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36641,7 +36641,7 @@
         <v>46223</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36714,7 +36714,7 @@
         <v>44819</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36787,7 +36787,7 @@
         <v>44952</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36860,7 +36860,7 @@
         <v>45323</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36933,7 +36933,7 @@
         <v>45092</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37006,7 +37006,7 @@
         <v>46272</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37079,7 +37079,7 @@
         <v>45086</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37152,7 +37152,7 @@
         <v>46273</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37225,7 +37225,7 @@
         <v>46273</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37298,7 +37298,7 @@
         <v>44895</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37371,7 +37371,7 @@
         <v>45156</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37444,7 +37444,7 @@
         <v>46275</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37517,7 +37517,7 @@
         <v>46274</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37590,7 +37590,7 @@
         <v>45034</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37663,7 +37663,7 @@
         <v>45254</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37736,7 +37736,7 @@
         <v>45174</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37809,7 +37809,7 @@
         <v>46276</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37882,7 +37882,7 @@
         <v>45363</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37955,7 +37955,7 @@
         <v>44818</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38028,7 +38028,7 @@
         <v>46276</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38101,7 +38101,7 @@
         <v>45531</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38174,7 +38174,7 @@
         <v>45324</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38247,7 +38247,7 @@
         <v>46281</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38320,7 +38320,7 @@
         <v>46281</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38393,7 +38393,7 @@
         <v>45454</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38466,7 +38466,7 @@
         <v>46281</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38539,7 +38539,7 @@
         <v>45703</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38612,7 +38612,7 @@
         <v>44564</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38685,7 +38685,7 @@
         <v>46063</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38758,7 +38758,7 @@
         <v>45209</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38831,7 +38831,7 @@
         <v>45209</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38904,7 +38904,7 @@
         <v>45091</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38977,7 +38977,7 @@
         <v>45260</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39050,7 +39050,7 @@
         <v>44978</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39123,7 +39123,7 @@
         <v>45273</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39196,7 +39196,7 @@
         <v>45334</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39269,7 +39269,7 @@
         <v>45189</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39342,7 +39342,7 @@
         <v>45356</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39415,7 +39415,7 @@
         <v>46247</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39493,7 +39493,7 @@
         <v>45027</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39566,7 +39566,7 @@
         <v>46290</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39639,7 +39639,7 @@
         <v>45067</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39712,7 +39712,7 @@
         <v>44823</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39785,7 +39785,7 @@
         <v>44823</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39858,7 +39858,7 @@
         <v>44732</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39931,7 +39931,7 @@
         <v>44963</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40004,7 +40004,7 @@
         <v>44963</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40077,7 +40077,7 @@
         <v>45341</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40150,7 +40150,7 @@
         <v>46247</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40223,7 +40223,7 @@
         <v>45618</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40296,7 +40296,7 @@
         <v>45540</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40369,7 +40369,7 @@
         <v>45076</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40447,7 +40447,7 @@
         <v>45156</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40520,7 +40520,7 @@
         <v>44824</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40593,7 +40593,7 @@
         <v>45001</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40666,7 +40666,7 @@
         <v>44658</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40739,7 +40739,7 @@
         <v>45114</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40812,7 +40812,7 @@
         <v>46254</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40890,7 +40890,7 @@
         <v>46254</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40968,7 +40968,7 @@
         <v>46253</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41041,7 +41041,7 @@
         <v>45229</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41114,7 +41114,7 @@
         <v>44924</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41187,7 +41187,7 @@
         <v>45119</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41260,7 +41260,7 @@
         <v>44858</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41333,7 +41333,7 @@
         <v>46300</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41411,7 +41411,7 @@
         <v>45181</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41484,7 +41484,7 @@
         <v>45775</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41557,7 +41557,7 @@
         <v>45558</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41635,7 +41635,7 @@
         <v>45439</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41708,7 +41708,7 @@
         <v>45443</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41781,7 +41781,7 @@
         <v>45551</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41854,7 +41854,7 @@
         <v>45246</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41927,7 +41927,7 @@
         <v>46070</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42000,7 +42000,7 @@
         <v>45785</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42073,7 +42073,7 @@
         <v>46300</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42146,7 +42146,7 @@
         <v>45664</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42219,7 +42219,7 @@
         <v>45664</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42292,7 +42292,7 @@
         <v>45566</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42365,7 +42365,7 @@
         <v>45730</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42438,7 +42438,7 @@
         <v>45363</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42511,7 +42511,7 @@
         <v>45791</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42584,7 +42584,7 @@
         <v>46259</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42657,7 +42657,7 @@
         <v>45792</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42735,7 +42735,7 @@
         <v>46304</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42808,7 +42808,7 @@
         <v>45104</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42881,7 +42881,7 @@
         <v>46026</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42954,7 +42954,7 @@
         <v>46304</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43027,7 +43027,7 @@
         <v>45720</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43100,7 +43100,7 @@
         <v>45805</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43173,7 +43173,7 @@
         <v>45812</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43246,7 +43246,7 @@
         <v>46269</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43319,7 +43319,7 @@
         <v>45842</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43392,7 +43392,7 @@
         <v>45842</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43465,7 +43465,7 @@
         <v>45861</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43538,7 +43538,7 @@
         <v>45831</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43611,7 +43611,7 @@
         <v>45764</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43684,7 +43684,7 @@
         <v>45779</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43757,7 +43757,7 @@
         <v>45874</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43830,7 +43830,7 @@
         <v>45785</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43903,7 +43903,7 @@
         <v>45387</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43976,7 +43976,7 @@
         <v>45373</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44049,7 +44049,7 @@
         <v>45345</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44122,7 +44122,7 @@
         <v>45440</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44195,7 +44195,7 @@
         <v>44607</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44268,7 +44268,7 @@
         <v>45595</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44341,7 +44341,7 @@
         <v>44587</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44414,7 +44414,7 @@
         <v>44806</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44487,7 +44487,7 @@
         <v>44965</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44560,7 +44560,7 @@
         <v>44531</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44633,7 +44633,7 @@
         <v>44957</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44706,7 +44706,7 @@
         <v>45345</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44779,7 +44779,7 @@
         <v>45345</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44852,7 +44852,7 @@
         <v>45685</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44925,7 +44925,7 @@
         <v>45358</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44998,7 +44998,7 @@
         <v>44957</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45071,7 +45071,7 @@
         <v>45824</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45144,7 +45144,7 @@
         <v>44071</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45217,7 +45217,7 @@
         <v>45890</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45290,7 +45290,7 @@
         <v>45902</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45363,7 +45363,7 @@
         <v>46058</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45436,7 +45436,7 @@
         <v>46062</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45509,7 +45509,7 @@
         <v>46062</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45582,7 +45582,7 @@
         <v>46063</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45655,7 +45655,7 @@
         <v>46062</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45728,7 +45728,7 @@
         <v>46062</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45801,7 +45801,7 @@
         <v>46065</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45874,7 +45874,7 @@
         <v>46110</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45947,7 +45947,7 @@
         <v>46300</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>

--- a/Översikt KALMAR.xlsx
+++ b/Översikt KALMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45209</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>44876</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45952</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>45345</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>46066</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>44876</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>46058</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>44979</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>44601</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>44876</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>45947</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>45915</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>44876</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>45324</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>45664</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>45561</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>46085</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         <v>46300</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2772,7 +2772,7 @@
         <v>44522</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
         <v>46303</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>44951</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>44984</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>45463</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>44970</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         <v>45953</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>45684</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>44853</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>44993</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>44979</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>45254</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>44595</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>44784</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>44951</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>45943</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>44785</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>45044</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>45363</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>46300</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>45118</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5094,7 +5094,7 @@
         <v>44970</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
         <v>44575</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>45114</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5423,7 +5423,7 @@
         <v>44785</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
         <v>44616</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
         <v>44595</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5766,7 +5766,7 @@
         <v>45903</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
         <v>45954</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
         <v>44517</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         <v>45190</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6200,7 +6200,7 @@
         <v>44802</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6306,7 +6306,7 @@
         <v>45924</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         <v>44517</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         <v>45243</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6628,7 +6628,7 @@
         <v>45966</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>46279</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>46245</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         <v>46253</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         <v>46119</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7166,7 +7166,7 @@
         <v>46119</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         <v>45874</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7378,7 +7378,7 @@
         <v>46055</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7484,7 +7484,7 @@
         <v>45105</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7590,7 +7590,7 @@
         <v>44994</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         <v>44994</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>46049</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>45722</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8027,7 +8027,7 @@
         <v>44796</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8133,7 +8133,7 @@
         <v>45275</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         <v>45575</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>45314</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         <v>44827</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8566,7 +8566,7 @@
         <v>45475</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         <v>45448</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
         <v>44623</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         <v>45007</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>44931</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         <v>44949</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         <v>44931</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
         <v>46177</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>45090</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         <v>46188</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>45063</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9741,7 +9741,7 @@
         <v>46199</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9846,7 +9846,7 @@
         <v>45083</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>45544</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>45775</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>45454</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10270,7 +10270,7 @@
         <v>45791</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>46247</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10480,7 +10480,7 @@
         <v>45574</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>46247</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>44855</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>46300</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10919,7 +10919,7 @@
         <v>46300</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>45782</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
         <v>45163</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>46300</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11362,7 +11362,7 @@
         <v>46258</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11467,7 +11467,7 @@
         <v>46304</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11572,7 +11572,7 @@
         <v>45868</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>46119</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
         <v>44915</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11887,7 +11887,7 @@
         <v>45086</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>45917</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12097,7 +12097,7 @@
         <v>44914</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12202,7 +12202,7 @@
         <v>45007</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12307,7 +12307,7 @@
         <v>44740</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12412,7 +12412,7 @@
         <v>44810</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12517,7 +12517,7 @@
         <v>44575</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
         <v>44991</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12731,7 +12731,7 @@
         <v>45069</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12836,7 +12836,7 @@
         <v>45007</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12945,7 +12945,7 @@
         <v>45264</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13054,7 +13054,7 @@
         <v>44895</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13159,7 +13159,7 @@
         <v>45117</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13264,7 +13264,7 @@
         <v>45180</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13373,7 +13373,7 @@
         <v>45167</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13478,7 +13478,7 @@
         <v>44586</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         <v>44810</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13693,7 +13693,7 @@
         <v>45611</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13798,7 +13798,7 @@
         <v>45373</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         <v>46063</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14012,7 +14012,7 @@
         <v>46087</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14117,7 +14117,7 @@
         <v>44629</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14190,7 +14190,7 @@
         <v>44643</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14263,7 +14263,7 @@
         <v>44823</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>44497</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14409,7 +14409,7 @@
         <v>44505</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14482,7 +14482,7 @@
         <v>44852</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14555,7 +14555,7 @@
         <v>44684</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14628,7 +14628,7 @@
         <v>44539</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>44498</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14774,7 +14774,7 @@
         <v>44498</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14847,7 +14847,7 @@
         <v>44525</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14920,7 +14920,7 @@
         <v>44823</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>44790</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>44531</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>44602</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15212,7 +15212,7 @@
         <v>44858</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>44522</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15358,7 +15358,7 @@
         <v>44823</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>44818</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15504,7 +15504,7 @@
         <v>44852</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15577,7 +15577,7 @@
         <v>44858</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15650,7 +15650,7 @@
         <v>44858</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15723,7 +15723,7 @@
         <v>44858</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15796,7 +15796,7 @@
         <v>44615</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15869,7 +15869,7 @@
         <v>44586</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>44502</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16015,7 +16015,7 @@
         <v>44552</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16088,7 +16088,7 @@
         <v>44620</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16161,7 +16161,7 @@
         <v>44625</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16234,7 +16234,7 @@
         <v>44784</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16307,7 +16307,7 @@
         <v>44654</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16380,7 +16380,7 @@
         <v>44855</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16453,7 +16453,7 @@
         <v>44858</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16526,7 +16526,7 @@
         <v>44732</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16599,7 +16599,7 @@
         <v>44810</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16672,7 +16672,7 @@
         <v>44858</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16745,7 +16745,7 @@
         <v>44529</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16818,7 +16818,7 @@
         <v>45630</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>44994</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16964,7 +16964,7 @@
         <v>44872</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17037,7 +17037,7 @@
         <v>44511</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17110,7 +17110,7 @@
         <v>45796</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17183,7 +17183,7 @@
         <v>45789</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17256,7 +17256,7 @@
         <v>45044</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17329,7 +17329,7 @@
         <v>45492</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17402,7 +17402,7 @@
         <v>45796</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17475,7 +17475,7 @@
         <v>45341</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17548,7 +17548,7 @@
         <v>45341</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17621,7 +17621,7 @@
         <v>45324</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17694,7 +17694,7 @@
         <v>45267</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17767,7 +17767,7 @@
         <v>44497</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17840,7 +17840,7 @@
         <v>45716</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17913,7 +17913,7 @@
         <v>45215</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>45334</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18059,7 +18059,7 @@
         <v>45607</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18132,7 +18132,7 @@
         <v>44782</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18205,7 +18205,7 @@
         <v>45075</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18278,7 +18278,7 @@
         <v>44855</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>45209</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18424,7 +18424,7 @@
         <v>45209</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18497,7 +18497,7 @@
         <v>45840</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18570,7 +18570,7 @@
         <v>46162</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18643,7 +18643,7 @@
         <v>46162</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18716,7 +18716,7 @@
         <v>46162</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18789,7 +18789,7 @@
         <v>45912</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18862,7 +18862,7 @@
         <v>45091</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18935,7 +18935,7 @@
         <v>45912</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19008,7 +19008,7 @@
         <v>45091</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19081,7 +19081,7 @@
         <v>45924</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19154,7 +19154,7 @@
         <v>45923</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19227,7 +19227,7 @@
         <v>45252</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19300,7 +19300,7 @@
         <v>45470</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19373,7 +19373,7 @@
         <v>45034</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19446,7 +19446,7 @@
         <v>45930</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19519,7 +19519,7 @@
         <v>45628</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19592,7 +19592,7 @@
         <v>45097</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>45932</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19738,7 +19738,7 @@
         <v>46099</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19811,7 +19811,7 @@
         <v>44895</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19884,7 +19884,7 @@
         <v>45540</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19957,7 +19957,7 @@
         <v>45418</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20030,7 +20030,7 @@
         <v>44971</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20103,7 +20103,7 @@
         <v>45090</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20176,7 +20176,7 @@
         <v>45939</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20249,7 +20249,7 @@
         <v>45243</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20322,7 +20322,7 @@
         <v>46177</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20395,7 +20395,7 @@
         <v>45915</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20468,7 +20468,7 @@
         <v>44529</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20541,7 +20541,7 @@
         <v>45378</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20614,7 +20614,7 @@
         <v>45250</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20687,7 +20687,7 @@
         <v>45156</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20760,7 +20760,7 @@
         <v>44993</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20833,7 +20833,7 @@
         <v>45625</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20906,7 +20906,7 @@
         <v>45212</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20979,7 +20979,7 @@
         <v>45564</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21052,7 +21052,7 @@
         <v>45411</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21125,7 +21125,7 @@
         <v>46185</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21198,7 +21198,7 @@
         <v>46188</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>45268</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21344,7 +21344,7 @@
         <v>45067</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21417,7 +21417,7 @@
         <v>44963</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21490,7 +21490,7 @@
         <v>45246</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21563,7 +21563,7 @@
         <v>45387</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21636,7 +21636,7 @@
         <v>45387</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21709,7 +21709,7 @@
         <v>46178</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21782,7 +21782,7 @@
         <v>44846</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21855,7 +21855,7 @@
         <v>46036</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21928,7 +21928,7 @@
         <v>46197</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22001,7 +22001,7 @@
         <v>45978</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22074,7 +22074,7 @@
         <v>45173</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22147,7 +22147,7 @@
         <v>45174</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22220,7 +22220,7 @@
         <v>45930</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22293,7 +22293,7 @@
         <v>46198</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22366,7 +22366,7 @@
         <v>46199</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22439,7 +22439,7 @@
         <v>46202</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>46203</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22585,7 +22585,7 @@
         <v>45097</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22658,7 +22658,7 @@
         <v>45219</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22731,7 +22731,7 @@
         <v>45628</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22804,7 +22804,7 @@
         <v>45272</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22877,7 +22877,7 @@
         <v>45113</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22950,7 +22950,7 @@
         <v>44914</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23023,7 +23023,7 @@
         <v>45173</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23096,7 +23096,7 @@
         <v>46139</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23169,7 +23169,7 @@
         <v>44971</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23242,7 +23242,7 @@
         <v>46154</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23315,7 +23315,7 @@
         <v>45735</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23388,7 +23388,7 @@
         <v>45175</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23461,7 +23461,7 @@
         <v>45097</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23534,7 +23534,7 @@
         <v>46111</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23607,7 +23607,7 @@
         <v>46063</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23680,7 +23680,7 @@
         <v>45188</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23753,7 +23753,7 @@
         <v>45181</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23826,7 +23826,7 @@
         <v>45439</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23899,7 +23899,7 @@
         <v>45246</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23972,7 +23972,7 @@
         <v>45551</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24045,7 +24045,7 @@
         <v>45558</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24123,7 +24123,7 @@
         <v>45775</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24196,7 +24196,7 @@
         <v>45443</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24269,7 +24269,7 @@
         <v>46223</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24342,7 +24342,7 @@
         <v>46008</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24415,7 +24415,7 @@
         <v>45566</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24488,7 +24488,7 @@
         <v>45664</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24561,7 +24561,7 @@
         <v>45363</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24634,7 +24634,7 @@
         <v>46010</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24707,7 +24707,7 @@
         <v>45785</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24780,7 +24780,7 @@
         <v>45664</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24853,7 +24853,7 @@
         <v>46013</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24926,7 +24926,7 @@
         <v>45730</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24999,7 +24999,7 @@
         <v>46281</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25072,7 +25072,7 @@
         <v>46281</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25145,7 +25145,7 @@
         <v>45306</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25218,7 +25218,7 @@
         <v>45792</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25296,7 +25296,7 @@
         <v>45791</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25369,7 +25369,7 @@
         <v>46063</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25442,7 +25442,7 @@
         <v>46281</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25515,7 +25515,7 @@
         <v>45096</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25588,7 +25588,7 @@
         <v>45141</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25661,7 +25661,7 @@
         <v>46048</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25734,7 +25734,7 @@
         <v>46049</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25807,7 +25807,7 @@
         <v>45720</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25880,7 +25880,7 @@
         <v>46247</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>46290</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26026,7 +26026,7 @@
         <v>45805</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26099,7 +26099,7 @@
         <v>46247</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26177,7 +26177,7 @@
         <v>46054</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26250,7 +26250,7 @@
         <v>46054</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26323,7 +26323,7 @@
         <v>45812</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26396,7 +26396,7 @@
         <v>46062</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26469,7 +26469,7 @@
         <v>46063</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26542,7 +26542,7 @@
         <v>46063</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26615,7 +26615,7 @@
         <v>45254</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26688,7 +26688,7 @@
         <v>46070</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26761,7 +26761,7 @@
         <v>46300</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26834,7 +26834,7 @@
         <v>46254</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26912,7 +26912,7 @@
         <v>46300</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26990,7 +26990,7 @@
         <v>46092</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27063,7 +27063,7 @@
         <v>46092</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27136,7 +27136,7 @@
         <v>46093</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27209,7 +27209,7 @@
         <v>46254</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27287,7 +27287,7 @@
         <v>46253</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27360,7 +27360,7 @@
         <v>46099</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27433,7 +27433,7 @@
         <v>45842</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27506,7 +27506,7 @@
         <v>45842</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27579,7 +27579,7 @@
         <v>45476</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27652,7 +27652,7 @@
         <v>46070</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27725,7 +27725,7 @@
         <v>46259</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27798,7 +27798,7 @@
         <v>46108</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27871,7 +27871,7 @@
         <v>45861</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27944,7 +27944,7 @@
         <v>45831</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28017,7 +28017,7 @@
         <v>46112</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28090,7 +28090,7 @@
         <v>46304</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28163,7 +28163,7 @@
         <v>45779</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28236,7 +28236,7 @@
         <v>45764</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28309,7 +28309,7 @@
         <v>45273</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28382,7 +28382,7 @@
         <v>46119</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28455,7 +28455,7 @@
         <v>45246</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28528,7 +28528,7 @@
         <v>45246</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28601,7 +28601,7 @@
         <v>46304</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28674,7 +28674,7 @@
         <v>44895</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28747,7 +28747,7 @@
         <v>46119</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28820,7 +28820,7 @@
         <v>44564</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28893,7 +28893,7 @@
         <v>45874</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28966,7 +28966,7 @@
         <v>45104</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29039,7 +29039,7 @@
         <v>44988</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29112,7 +29112,7 @@
         <v>45785</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29185,7 +29185,7 @@
         <v>44862</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29258,7 +29258,7 @@
         <v>46134</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29331,7 +29331,7 @@
         <v>45707</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29404,7 +29404,7 @@
         <v>46134</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29477,7 +29477,7 @@
         <v>46036</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29550,7 +29550,7 @@
         <v>46026</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29623,7 +29623,7 @@
         <v>45153</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29696,7 +29696,7 @@
         <v>45050</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29769,7 +29769,7 @@
         <v>44909</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29842,7 +29842,7 @@
         <v>46009</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29915,7 +29915,7 @@
         <v>44924</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29988,7 +29988,7 @@
         <v>45688</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30061,7 +30061,7 @@
         <v>45764</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30134,7 +30134,7 @@
         <v>45923</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30207,7 +30207,7 @@
         <v>45688</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30280,7 +30280,7 @@
         <v>45915</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30353,7 +30353,7 @@
         <v>46139</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30426,7 +30426,7 @@
         <v>45548</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30499,7 +30499,7 @@
         <v>45551</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30572,7 +30572,7 @@
         <v>44574</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30645,7 +30645,7 @@
         <v>45719</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30723,7 +30723,7 @@
         <v>44595</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30796,7 +30796,7 @@
         <v>44595</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30869,7 +30869,7 @@
         <v>45028</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30942,7 +30942,7 @@
         <v>46269</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31015,7 +31015,7 @@
         <v>44502</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31088,7 +31088,7 @@
         <v>45695</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31161,7 +31161,7 @@
         <v>45104</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31234,7 +31234,7 @@
         <v>46272</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31307,7 +31307,7 @@
         <v>46273</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31380,7 +31380,7 @@
         <v>46139</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31453,7 +31453,7 @@
         <v>46273</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31526,7 +31526,7 @@
         <v>44971</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31599,7 +31599,7 @@
         <v>45034</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31672,7 +31672,7 @@
         <v>44539</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31745,7 +31745,7 @@
         <v>45727</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31818,7 +31818,7 @@
         <v>46307</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31891,7 +31891,7 @@
         <v>45167</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31964,7 +31964,7 @@
         <v>46276</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32037,7 +32037,7 @@
         <v>45058</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32110,7 +32110,7 @@
         <v>45720</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32183,7 +32183,7 @@
         <v>46276</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32256,7 +32256,7 @@
         <v>44915</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32329,7 +32329,7 @@
         <v>46274</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32402,7 +32402,7 @@
         <v>46099</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32475,7 +32475,7 @@
         <v>45229</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32548,7 +32548,7 @@
         <v>46275</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32621,7 +32621,7 @@
         <v>45219</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32694,7 +32694,7 @@
         <v>45205</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32767,7 +32767,7 @@
         <v>45006</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32840,7 +32840,7 @@
         <v>44959</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32913,7 +32913,7 @@
         <v>45061</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32986,7 +32986,7 @@
         <v>45091</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33059,7 +33059,7 @@
         <v>45156</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33132,7 +33132,7 @@
         <v>44816</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33205,7 +33205,7 @@
         <v>45272</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33278,7 +33278,7 @@
         <v>44993</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33351,7 +33351,7 @@
         <v>46155</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33424,7 +33424,7 @@
         <v>46155</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33497,7 +33497,7 @@
         <v>46160</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33570,7 +33570,7 @@
         <v>44909</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33643,7 +33643,7 @@
         <v>45236</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33716,7 +33716,7 @@
         <v>46160</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33789,7 +33789,7 @@
         <v>45903</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33862,7 +33862,7 @@
         <v>45624</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33935,7 +33935,7 @@
         <v>44952</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34008,7 +34008,7 @@
         <v>44966</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34081,7 +34081,7 @@
         <v>44984</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34174,7 +34174,7 @@
         <v>44984</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34247,7 +34247,7 @@
         <v>44973</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34320,7 +34320,7 @@
         <v>45618</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34393,7 +34393,7 @@
         <v>45001</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34466,7 +34466,7 @@
         <v>45680</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34539,7 +34539,7 @@
         <v>44993</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34612,7 +34612,7 @@
         <v>44732</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34685,7 +34685,7 @@
         <v>44924</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34758,7 +34758,7 @@
         <v>45161</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34831,7 +34831,7 @@
         <v>45114</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34904,7 +34904,7 @@
         <v>45544</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34982,7 +34982,7 @@
         <v>44824</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35055,7 +35055,7 @@
         <v>44564</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35128,7 +35128,7 @@
         <v>45091</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35201,7 +35201,7 @@
         <v>44988</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35274,7 +35274,7 @@
         <v>45229</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35347,7 +35347,7 @@
         <v>45028</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35420,7 +35420,7 @@
         <v>44823</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35493,7 +35493,7 @@
         <v>44823</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35566,7 +35566,7 @@
         <v>44617</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35639,7 +35639,7 @@
         <v>44617</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35712,7 +35712,7 @@
         <v>45205</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35785,7 +35785,7 @@
         <v>45239</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35863,7 +35863,7 @@
         <v>44629</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35936,7 +35936,7 @@
         <v>45180</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36009,7 +36009,7 @@
         <v>45540</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36082,7 +36082,7 @@
         <v>44502</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36155,7 +36155,7 @@
         <v>44566</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36228,7 +36228,7 @@
         <v>45233</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36301,7 +36301,7 @@
         <v>44846</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36374,7 +36374,7 @@
         <v>44939</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36447,7 +36447,7 @@
         <v>44882</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36520,7 +36520,7 @@
         <v>45092</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36593,7 +36593,7 @@
         <v>44914</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36666,7 +36666,7 @@
         <v>45099</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36739,7 +36739,7 @@
         <v>45104</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36812,7 +36812,7 @@
         <v>45104</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36885,7 +36885,7 @@
         <v>44924</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36958,7 +36958,7 @@
         <v>45118</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37031,7 +37031,7 @@
         <v>45086</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37104,7 +37104,7 @@
         <v>45202</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37177,7 +37177,7 @@
         <v>45387</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37250,7 +37250,7 @@
         <v>45387</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37323,7 +37323,7 @@
         <v>45099</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37396,7 +37396,7 @@
         <v>44544</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37469,7 +37469,7 @@
         <v>45544</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37542,7 +37542,7 @@
         <v>45104</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37620,7 +37620,7 @@
         <v>44991</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37693,7 +37693,7 @@
         <v>45260</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37766,7 +37766,7 @@
         <v>45713</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37839,7 +37839,7 @@
         <v>45076</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37917,7 +37917,7 @@
         <v>45400</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37990,7 +37990,7 @@
         <v>45110</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38068,7 +38068,7 @@
         <v>45335</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38146,7 +38146,7 @@
         <v>44543</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38219,7 +38219,7 @@
         <v>45618</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38292,7 +38292,7 @@
         <v>45173</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38365,7 +38365,7 @@
         <v>45534</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38438,7 +38438,7 @@
         <v>45540</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38511,7 +38511,7 @@
         <v>44818</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38584,7 +38584,7 @@
         <v>45195</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38657,7 +38657,7 @@
         <v>45114</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38730,7 +38730,7 @@
         <v>45205</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>45531</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38876,7 +38876,7 @@
         <v>45090</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38949,7 +38949,7 @@
         <v>45090</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39022,7 +39022,7 @@
         <v>45618</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39095,7 +39095,7 @@
         <v>45189</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39168,7 +39168,7 @@
         <v>44645</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39241,7 +39241,7 @@
         <v>45327</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39314,7 +39314,7 @@
         <v>45345</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39387,7 +39387,7 @@
         <v>45027</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39460,7 +39460,7 @@
         <v>44819</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39533,7 +39533,7 @@
         <v>45070</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39611,7 +39611,7 @@
         <v>45182</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39684,7 +39684,7 @@
         <v>44656</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39757,7 +39757,7 @@
         <v>45402</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39835,7 +39835,7 @@
         <v>45406</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39908,7 +39908,7 @@
         <v>45182</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39981,7 +39981,7 @@
         <v>45363</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40054,7 +40054,7 @@
         <v>45629</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40127,7 +40127,7 @@
         <v>45149</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40200,7 +40200,7 @@
         <v>45149</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40273,7 +40273,7 @@
         <v>45703</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40346,7 +40346,7 @@
         <v>45125</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40419,7 +40419,7 @@
         <v>45154</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40492,7 +40492,7 @@
         <v>45574</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40570,7 +40570,7 @@
         <v>45233</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40643,7 +40643,7 @@
         <v>45233</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40716,7 +40716,7 @@
         <v>45198</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40789,7 +40789,7 @@
         <v>45189</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40862,7 +40862,7 @@
         <v>45685</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40935,7 +40935,7 @@
         <v>45169</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41008,7 +41008,7 @@
         <v>44861</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41081,7 +41081,7 @@
         <v>45119</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41154,7 +41154,7 @@
         <v>45153</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41227,7 +41227,7 @@
         <v>45233</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41300,7 +41300,7 @@
         <v>45173</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41373,7 +41373,7 @@
         <v>45173</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41446,7 +41446,7 @@
         <v>45246</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41519,7 +41519,7 @@
         <v>44782</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41592,7 +41592,7 @@
         <v>45252</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41665,7 +41665,7 @@
         <v>45170</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41738,7 +41738,7 @@
         <v>44973</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41811,7 +41811,7 @@
         <v>45356</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41884,7 +41884,7 @@
         <v>44847</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41957,7 +41957,7 @@
         <v>45454</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42030,7 +42030,7 @@
         <v>44690</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42103,7 +42103,7 @@
         <v>45349</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42176,7 +42176,7 @@
         <v>45212</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42249,7 +42249,7 @@
         <v>45007</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42322,7 +42322,7 @@
         <v>45007</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42395,7 +42395,7 @@
         <v>45266</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42468,7 +42468,7 @@
         <v>45323</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42541,7 +42541,7 @@
         <v>44963</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42614,7 +42614,7 @@
         <v>44963</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42687,7 +42687,7 @@
         <v>45093</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42760,7 +42760,7 @@
         <v>45229</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42833,7 +42833,7 @@
         <v>44864</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42906,7 +42906,7 @@
         <v>45308</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42979,7 +42979,7 @@
         <v>45595</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43052,7 +43052,7 @@
         <v>44658</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43125,7 +43125,7 @@
         <v>44858</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43198,7 +43198,7 @@
         <v>45524</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43271,7 +43271,7 @@
         <v>44712</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43344,7 +43344,7 @@
         <v>44803</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43417,7 +43417,7 @@
         <v>44978</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43490,7 +43490,7 @@
         <v>44939</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43563,7 +43563,7 @@
         <v>44607</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43636,7 +43636,7 @@
         <v>44587</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43709,7 +43709,7 @@
         <v>45387</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43782,7 +43782,7 @@
         <v>45373</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43855,7 +43855,7 @@
         <v>45345</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43928,7 +43928,7 @@
         <v>45440</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44001,7 +44001,7 @@
         <v>45595</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44074,7 +44074,7 @@
         <v>44806</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44147,7 +44147,7 @@
         <v>44965</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44220,7 +44220,7 @@
         <v>44531</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44293,7 +44293,7 @@
         <v>44957</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44366,7 +44366,7 @@
         <v>45345</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44439,7 +44439,7 @@
         <v>45345</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44512,7 +44512,7 @@
         <v>45685</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44585,7 +44585,7 @@
         <v>45358</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44658,7 +44658,7 @@
         <v>44957</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44731,7 +44731,7 @@
         <v>45824</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44804,7 +44804,7 @@
         <v>44071</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44877,7 +44877,7 @@
         <v>45890</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44950,7 +44950,7 @@
         <v>45902</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45023,7 +45023,7 @@
         <v>46058</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45096,7 +45096,7 @@
         <v>46062</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45169,7 +45169,7 @@
         <v>46062</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45242,7 +45242,7 @@
         <v>46063</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45315,7 +45315,7 @@
         <v>46062</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45388,7 +45388,7 @@
         <v>46062</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45461,7 +45461,7 @@
         <v>46065</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45534,7 +45534,7 @@
         <v>46110</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45607,7 +45607,7 @@
         <v>46300</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>

--- a/Översikt KALMAR.xlsx
+++ b/Översikt KALMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45209</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>44876</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45952</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>45345</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>46066</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>44876</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>46058</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>44979</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>44601</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>44876</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>45947</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>45915</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>44876</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>45324</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>45664</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>45561</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>46085</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         <v>46300</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2772,7 +2772,7 @@
         <v>44522</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
         <v>46303</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>44951</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>44984</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>45463</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>44970</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         <v>45953</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>45684</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>44853</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>44993</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>44979</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>45254</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>44595</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>44784</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>44951</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>45943</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>44785</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>45044</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>45363</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>46300</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>45118</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5094,7 +5094,7 @@
         <v>44970</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
         <v>44575</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>45114</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5423,7 +5423,7 @@
         <v>44785</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
         <v>44616</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
         <v>44595</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5766,7 +5766,7 @@
         <v>45903</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
         <v>45954</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
         <v>44517</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         <v>45190</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6200,7 +6200,7 @@
         <v>44802</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6306,7 +6306,7 @@
         <v>45924</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         <v>44517</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         <v>45243</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6628,7 +6628,7 @@
         <v>45966</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>46279</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>46245</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         <v>46253</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         <v>46119</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7166,7 +7166,7 @@
         <v>46119</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         <v>45874</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7378,7 +7378,7 @@
         <v>46055</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7484,7 +7484,7 @@
         <v>45105</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7590,7 +7590,7 @@
         <v>44994</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         <v>44994</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>46049</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>45722</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8027,7 +8027,7 @@
         <v>44796</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8133,7 +8133,7 @@
         <v>45275</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         <v>45575</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>45314</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         <v>44827</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8566,7 +8566,7 @@
         <v>45475</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         <v>45448</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
         <v>44623</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         <v>45007</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>44931</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         <v>44949</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         <v>44931</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
         <v>46177</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>45090</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         <v>46188</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>45063</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9741,7 +9741,7 @@
         <v>46199</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9846,7 +9846,7 @@
         <v>45083</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>45544</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>45775</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>45454</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10270,7 +10270,7 @@
         <v>45791</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>46247</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10480,7 +10480,7 @@
         <v>45574</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>46247</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>44855</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>46300</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10919,7 +10919,7 @@
         <v>46300</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>45782</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
         <v>45163</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>46300</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11362,7 +11362,7 @@
         <v>46258</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11467,7 +11467,7 @@
         <v>46304</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11572,7 +11572,7 @@
         <v>45868</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>46119</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
         <v>44915</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11887,7 +11887,7 @@
         <v>45086</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>45917</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12097,7 +12097,7 @@
         <v>44914</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12202,7 +12202,7 @@
         <v>45007</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12307,7 +12307,7 @@
         <v>44740</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12412,7 +12412,7 @@
         <v>44810</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12517,7 +12517,7 @@
         <v>44575</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
         <v>44991</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12731,7 +12731,7 @@
         <v>45069</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12836,7 +12836,7 @@
         <v>45007</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12945,7 +12945,7 @@
         <v>45264</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13054,7 +13054,7 @@
         <v>44895</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13159,7 +13159,7 @@
         <v>45117</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13264,7 +13264,7 @@
         <v>45180</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13373,7 +13373,7 @@
         <v>45167</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13478,7 +13478,7 @@
         <v>44586</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         <v>44810</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13693,7 +13693,7 @@
         <v>45611</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13798,7 +13798,7 @@
         <v>45373</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         <v>46063</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14012,7 +14012,7 @@
         <v>46087</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14117,7 +14117,7 @@
         <v>44629</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14190,7 +14190,7 @@
         <v>44643</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14263,7 +14263,7 @@
         <v>44823</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>44497</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14409,7 +14409,7 @@
         <v>44505</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14482,7 +14482,7 @@
         <v>44852</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14555,7 +14555,7 @@
         <v>44684</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14628,7 +14628,7 @@
         <v>44539</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>44498</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14774,7 +14774,7 @@
         <v>44498</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14847,7 +14847,7 @@
         <v>44525</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14920,7 +14920,7 @@
         <v>44823</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>44790</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>44531</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>44602</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15212,7 +15212,7 @@
         <v>44858</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>44522</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15358,7 +15358,7 @@
         <v>44823</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>44818</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15504,7 +15504,7 @@
         <v>44852</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15577,7 +15577,7 @@
         <v>44858</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15650,7 +15650,7 @@
         <v>44858</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15723,7 +15723,7 @@
         <v>44858</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15796,7 +15796,7 @@
         <v>44615</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15869,7 +15869,7 @@
         <v>44586</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>44502</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16015,7 +16015,7 @@
         <v>44552</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16088,7 +16088,7 @@
         <v>44620</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16161,7 +16161,7 @@
         <v>44625</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16234,7 +16234,7 @@
         <v>44784</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16307,7 +16307,7 @@
         <v>44654</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16380,7 +16380,7 @@
         <v>44855</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16453,7 +16453,7 @@
         <v>44858</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16526,7 +16526,7 @@
         <v>44732</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16599,7 +16599,7 @@
         <v>44810</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16672,7 +16672,7 @@
         <v>44858</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16745,7 +16745,7 @@
         <v>44529</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16818,7 +16818,7 @@
         <v>45630</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>44994</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16964,7 +16964,7 @@
         <v>44872</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17037,7 +17037,7 @@
         <v>44511</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17110,7 +17110,7 @@
         <v>45796</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17183,7 +17183,7 @@
         <v>45789</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17256,7 +17256,7 @@
         <v>45044</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17329,7 +17329,7 @@
         <v>45492</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17402,7 +17402,7 @@
         <v>45796</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17475,7 +17475,7 @@
         <v>45341</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17548,7 +17548,7 @@
         <v>45341</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17621,7 +17621,7 @@
         <v>45324</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17694,7 +17694,7 @@
         <v>45267</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17767,7 +17767,7 @@
         <v>44497</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17840,7 +17840,7 @@
         <v>45716</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17913,7 +17913,7 @@
         <v>45215</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>45334</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18059,7 +18059,7 @@
         <v>45607</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18132,7 +18132,7 @@
         <v>44782</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18205,7 +18205,7 @@
         <v>45075</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18278,7 +18278,7 @@
         <v>44855</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>45209</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18424,7 +18424,7 @@
         <v>45209</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18497,7 +18497,7 @@
         <v>45840</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18570,7 +18570,7 @@
         <v>46162</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18643,7 +18643,7 @@
         <v>46162</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18716,7 +18716,7 @@
         <v>46162</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18789,7 +18789,7 @@
         <v>45912</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18862,7 +18862,7 @@
         <v>45091</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18935,7 +18935,7 @@
         <v>45912</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19008,7 +19008,7 @@
         <v>45091</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19081,7 +19081,7 @@
         <v>45924</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19154,7 +19154,7 @@
         <v>45923</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19227,7 +19227,7 @@
         <v>45252</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19300,7 +19300,7 @@
         <v>45470</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19373,7 +19373,7 @@
         <v>45034</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19446,7 +19446,7 @@
         <v>45930</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19519,7 +19519,7 @@
         <v>45628</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19592,7 +19592,7 @@
         <v>45097</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>45932</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19738,7 +19738,7 @@
         <v>46099</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19811,7 +19811,7 @@
         <v>44895</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19884,7 +19884,7 @@
         <v>45540</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19957,7 +19957,7 @@
         <v>45418</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20030,7 +20030,7 @@
         <v>44971</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20103,7 +20103,7 @@
         <v>45090</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20176,7 +20176,7 @@
         <v>45939</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20249,7 +20249,7 @@
         <v>45243</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20322,7 +20322,7 @@
         <v>46177</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20395,7 +20395,7 @@
         <v>45915</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20468,7 +20468,7 @@
         <v>44529</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20541,7 +20541,7 @@
         <v>45378</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20614,7 +20614,7 @@
         <v>45250</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20687,7 +20687,7 @@
         <v>45156</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20760,7 +20760,7 @@
         <v>44993</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20833,7 +20833,7 @@
         <v>45625</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20906,7 +20906,7 @@
         <v>45212</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20979,7 +20979,7 @@
         <v>45564</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21052,7 +21052,7 @@
         <v>45411</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21125,7 +21125,7 @@
         <v>46185</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21198,7 +21198,7 @@
         <v>46188</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>45268</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21344,7 +21344,7 @@
         <v>45067</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21417,7 +21417,7 @@
         <v>44963</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21490,7 +21490,7 @@
         <v>45246</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21563,7 +21563,7 @@
         <v>45387</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21636,7 +21636,7 @@
         <v>45387</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21709,7 +21709,7 @@
         <v>46178</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21782,7 +21782,7 @@
         <v>44846</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21855,7 +21855,7 @@
         <v>46036</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21928,7 +21928,7 @@
         <v>46197</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22001,7 +22001,7 @@
         <v>45978</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22074,7 +22074,7 @@
         <v>45173</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22147,7 +22147,7 @@
         <v>45174</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22220,7 +22220,7 @@
         <v>45930</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22293,7 +22293,7 @@
         <v>46198</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22366,7 +22366,7 @@
         <v>46199</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22439,7 +22439,7 @@
         <v>46202</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>46203</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22585,7 +22585,7 @@
         <v>45097</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22658,7 +22658,7 @@
         <v>45219</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22731,7 +22731,7 @@
         <v>45628</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22804,7 +22804,7 @@
         <v>45272</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22877,7 +22877,7 @@
         <v>45113</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22950,7 +22950,7 @@
         <v>44914</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23023,7 +23023,7 @@
         <v>45173</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23096,7 +23096,7 @@
         <v>46139</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23169,7 +23169,7 @@
         <v>44971</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23242,7 +23242,7 @@
         <v>46154</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23315,7 +23315,7 @@
         <v>45735</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23388,7 +23388,7 @@
         <v>45175</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23461,7 +23461,7 @@
         <v>45097</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23534,7 +23534,7 @@
         <v>46111</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23607,7 +23607,7 @@
         <v>46063</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23680,7 +23680,7 @@
         <v>45188</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23753,7 +23753,7 @@
         <v>45181</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23826,7 +23826,7 @@
         <v>45439</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23899,7 +23899,7 @@
         <v>45246</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23972,7 +23972,7 @@
         <v>45551</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24045,7 +24045,7 @@
         <v>45558</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24123,7 +24123,7 @@
         <v>45775</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24196,7 +24196,7 @@
         <v>45443</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24269,7 +24269,7 @@
         <v>46223</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24342,7 +24342,7 @@
         <v>46008</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24415,7 +24415,7 @@
         <v>45566</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24488,7 +24488,7 @@
         <v>45664</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24561,7 +24561,7 @@
         <v>45363</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24634,7 +24634,7 @@
         <v>46010</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24707,7 +24707,7 @@
         <v>45785</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24780,7 +24780,7 @@
         <v>45664</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24853,7 +24853,7 @@
         <v>46013</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24926,7 +24926,7 @@
         <v>45730</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24999,7 +24999,7 @@
         <v>46281</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25072,7 +25072,7 @@
         <v>46281</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25145,7 +25145,7 @@
         <v>45306</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25218,7 +25218,7 @@
         <v>45792</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25296,7 +25296,7 @@
         <v>45791</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25369,7 +25369,7 @@
         <v>46063</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25442,7 +25442,7 @@
         <v>46281</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25515,7 +25515,7 @@
         <v>45096</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25588,7 +25588,7 @@
         <v>45141</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25661,7 +25661,7 @@
         <v>46048</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25734,7 +25734,7 @@
         <v>46049</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25807,7 +25807,7 @@
         <v>45720</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25880,7 +25880,7 @@
         <v>46247</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>46290</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26026,7 +26026,7 @@
         <v>45805</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26099,7 +26099,7 @@
         <v>46247</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26177,7 +26177,7 @@
         <v>46054</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26250,7 +26250,7 @@
         <v>46054</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26323,7 +26323,7 @@
         <v>45812</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26396,7 +26396,7 @@
         <v>46062</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26469,7 +26469,7 @@
         <v>46063</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26542,7 +26542,7 @@
         <v>46063</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26615,7 +26615,7 @@
         <v>45254</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26688,7 +26688,7 @@
         <v>46070</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26761,7 +26761,7 @@
         <v>46300</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26834,7 +26834,7 @@
         <v>46254</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26912,7 +26912,7 @@
         <v>46300</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26990,7 +26990,7 @@
         <v>46092</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27063,7 +27063,7 @@
         <v>46092</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27136,7 +27136,7 @@
         <v>46093</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27209,7 +27209,7 @@
         <v>46254</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27287,7 +27287,7 @@
         <v>46253</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27360,7 +27360,7 @@
         <v>46099</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27433,7 +27433,7 @@
         <v>45842</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27506,7 +27506,7 @@
         <v>45842</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27579,7 +27579,7 @@
         <v>45476</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27652,7 +27652,7 @@
         <v>46070</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27725,7 +27725,7 @@
         <v>46259</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27798,7 +27798,7 @@
         <v>46108</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27871,7 +27871,7 @@
         <v>45861</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27944,7 +27944,7 @@
         <v>45831</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28017,7 +28017,7 @@
         <v>46112</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28090,7 +28090,7 @@
         <v>46304</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28163,7 +28163,7 @@
         <v>45779</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28236,7 +28236,7 @@
         <v>45764</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28309,7 +28309,7 @@
         <v>45273</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28382,7 +28382,7 @@
         <v>46119</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28455,7 +28455,7 @@
         <v>45246</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28528,7 +28528,7 @@
         <v>45246</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28601,7 +28601,7 @@
         <v>46304</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28674,7 +28674,7 @@
         <v>44895</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28747,7 +28747,7 @@
         <v>46119</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28820,7 +28820,7 @@
         <v>44564</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28893,7 +28893,7 @@
         <v>45874</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28966,7 +28966,7 @@
         <v>45104</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29039,7 +29039,7 @@
         <v>44988</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29112,7 +29112,7 @@
         <v>45785</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29185,7 +29185,7 @@
         <v>44862</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29258,7 +29258,7 @@
         <v>46134</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29331,7 +29331,7 @@
         <v>45707</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29404,7 +29404,7 @@
         <v>46134</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29477,7 +29477,7 @@
         <v>46036</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29550,7 +29550,7 @@
         <v>46026</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29623,7 +29623,7 @@
         <v>45153</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29696,7 +29696,7 @@
         <v>45050</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29769,7 +29769,7 @@
         <v>44909</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29842,7 +29842,7 @@
         <v>46009</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29915,7 +29915,7 @@
         <v>44924</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29988,7 +29988,7 @@
         <v>45688</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30061,7 +30061,7 @@
         <v>45764</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30134,7 +30134,7 @@
         <v>45923</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30207,7 +30207,7 @@
         <v>45688</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30280,7 +30280,7 @@
         <v>45915</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30353,7 +30353,7 @@
         <v>46139</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30426,7 +30426,7 @@
         <v>45548</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30499,7 +30499,7 @@
         <v>45551</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30572,7 +30572,7 @@
         <v>44574</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30645,7 +30645,7 @@
         <v>45719</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30723,7 +30723,7 @@
         <v>44595</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30796,7 +30796,7 @@
         <v>44595</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30869,7 +30869,7 @@
         <v>45028</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30942,7 +30942,7 @@
         <v>46269</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31015,7 +31015,7 @@
         <v>44502</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31088,7 +31088,7 @@
         <v>45695</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31161,7 +31161,7 @@
         <v>45104</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31234,7 +31234,7 @@
         <v>46272</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31307,7 +31307,7 @@
         <v>46273</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31380,7 +31380,7 @@
         <v>46139</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31453,7 +31453,7 @@
         <v>46273</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31526,7 +31526,7 @@
         <v>44971</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31599,7 +31599,7 @@
         <v>45034</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31672,7 +31672,7 @@
         <v>44539</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31745,7 +31745,7 @@
         <v>45727</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31818,7 +31818,7 @@
         <v>46307</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31891,7 +31891,7 @@
         <v>45167</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31964,7 +31964,7 @@
         <v>46276</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32037,7 +32037,7 @@
         <v>45058</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32110,7 +32110,7 @@
         <v>45720</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32183,7 +32183,7 @@
         <v>46276</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32256,7 +32256,7 @@
         <v>44915</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32329,7 +32329,7 @@
         <v>46274</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32402,7 +32402,7 @@
         <v>46099</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32475,7 +32475,7 @@
         <v>45229</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32548,7 +32548,7 @@
         <v>46275</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32621,7 +32621,7 @@
         <v>45219</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32694,7 +32694,7 @@
         <v>45205</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32767,7 +32767,7 @@
         <v>45006</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32840,7 +32840,7 @@
         <v>44959</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32913,7 +32913,7 @@
         <v>45061</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32986,7 +32986,7 @@
         <v>45091</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33059,7 +33059,7 @@
         <v>45156</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33132,7 +33132,7 @@
         <v>44816</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33205,7 +33205,7 @@
         <v>45272</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33278,7 +33278,7 @@
         <v>44993</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33351,7 +33351,7 @@
         <v>46155</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33424,7 +33424,7 @@
         <v>46155</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33497,7 +33497,7 @@
         <v>46160</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33570,7 +33570,7 @@
         <v>44909</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33643,7 +33643,7 @@
         <v>45236</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33716,7 +33716,7 @@
         <v>46160</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33789,7 +33789,7 @@
         <v>45903</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33862,7 +33862,7 @@
         <v>45624</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33935,7 +33935,7 @@
         <v>44952</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34008,7 +34008,7 @@
         <v>44966</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34081,7 +34081,7 @@
         <v>44984</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34174,7 +34174,7 @@
         <v>44984</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34247,7 +34247,7 @@
         <v>44973</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34320,7 +34320,7 @@
         <v>45618</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34393,7 +34393,7 @@
         <v>45001</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34466,7 +34466,7 @@
         <v>45680</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34539,7 +34539,7 @@
         <v>44993</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34612,7 +34612,7 @@
         <v>44732</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34685,7 +34685,7 @@
         <v>44924</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34758,7 +34758,7 @@
         <v>45161</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34831,7 +34831,7 @@
         <v>45114</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34904,7 +34904,7 @@
         <v>45544</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34982,7 +34982,7 @@
         <v>44824</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35055,7 +35055,7 @@
         <v>44564</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35128,7 +35128,7 @@
         <v>45091</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35201,7 +35201,7 @@
         <v>44988</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35274,7 +35274,7 @@
         <v>45229</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35347,7 +35347,7 @@
         <v>45028</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35420,7 +35420,7 @@
         <v>44823</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35493,7 +35493,7 @@
         <v>44823</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35566,7 +35566,7 @@
         <v>44617</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35639,7 +35639,7 @@
         <v>44617</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35712,7 +35712,7 @@
         <v>45205</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35785,7 +35785,7 @@
         <v>45239</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35863,7 +35863,7 @@
         <v>44629</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35936,7 +35936,7 @@
         <v>45180</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36009,7 +36009,7 @@
         <v>45540</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36082,7 +36082,7 @@
         <v>44502</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36155,7 +36155,7 @@
         <v>44566</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36228,7 +36228,7 @@
         <v>45233</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36301,7 +36301,7 @@
         <v>44846</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36374,7 +36374,7 @@
         <v>44939</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36447,7 +36447,7 @@
         <v>44882</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36520,7 +36520,7 @@
         <v>45092</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36593,7 +36593,7 @@
         <v>44914</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36666,7 +36666,7 @@
         <v>45099</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36739,7 +36739,7 @@
         <v>45104</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36812,7 +36812,7 @@
         <v>45104</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36885,7 +36885,7 @@
         <v>44924</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36958,7 +36958,7 @@
         <v>45118</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37031,7 +37031,7 @@
         <v>45086</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37104,7 +37104,7 @@
         <v>45202</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37177,7 +37177,7 @@
         <v>45387</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37250,7 +37250,7 @@
         <v>45387</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37323,7 +37323,7 @@
         <v>45099</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37396,7 +37396,7 @@
         <v>44544</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37469,7 +37469,7 @@
         <v>45544</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37542,7 +37542,7 @@
         <v>45104</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37620,7 +37620,7 @@
         <v>44991</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37693,7 +37693,7 @@
         <v>45260</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37766,7 +37766,7 @@
         <v>45713</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37839,7 +37839,7 @@
         <v>45076</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37917,7 +37917,7 @@
         <v>45400</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37990,7 +37990,7 @@
         <v>45110</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38068,7 +38068,7 @@
         <v>45335</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38146,7 +38146,7 @@
         <v>44543</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38219,7 +38219,7 @@
         <v>45618</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38292,7 +38292,7 @@
         <v>45173</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38365,7 +38365,7 @@
         <v>45534</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38438,7 +38438,7 @@
         <v>45540</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38511,7 +38511,7 @@
         <v>44818</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38584,7 +38584,7 @@
         <v>45195</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38657,7 +38657,7 @@
         <v>45114</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38730,7 +38730,7 @@
         <v>45205</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>45531</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38876,7 +38876,7 @@
         <v>45090</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38949,7 +38949,7 @@
         <v>45090</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39022,7 +39022,7 @@
         <v>45618</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39095,7 +39095,7 @@
         <v>45189</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39168,7 +39168,7 @@
         <v>44645</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39241,7 +39241,7 @@
         <v>45327</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39314,7 +39314,7 @@
         <v>45345</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39387,7 +39387,7 @@
         <v>45027</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39460,7 +39460,7 @@
         <v>44819</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39533,7 +39533,7 @@
         <v>45070</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39611,7 +39611,7 @@
         <v>45182</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39684,7 +39684,7 @@
         <v>44656</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39757,7 +39757,7 @@
         <v>45402</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39835,7 +39835,7 @@
         <v>45406</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39908,7 +39908,7 @@
         <v>45182</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39981,7 +39981,7 @@
         <v>45363</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40054,7 +40054,7 @@
         <v>45629</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40127,7 +40127,7 @@
         <v>45149</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40200,7 +40200,7 @@
         <v>45149</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40273,7 +40273,7 @@
         <v>45703</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40346,7 +40346,7 @@
         <v>45125</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40419,7 +40419,7 @@
         <v>45154</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40492,7 +40492,7 @@
         <v>45574</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40570,7 +40570,7 @@
         <v>45233</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40643,7 +40643,7 @@
         <v>45233</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40716,7 +40716,7 @@
         <v>45198</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40789,7 +40789,7 @@
         <v>45189</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40862,7 +40862,7 @@
         <v>45685</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40935,7 +40935,7 @@
         <v>45169</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41008,7 +41008,7 @@
         <v>44861</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41081,7 +41081,7 @@
         <v>45119</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41154,7 +41154,7 @@
         <v>45153</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41227,7 +41227,7 @@
         <v>45233</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41300,7 +41300,7 @@
         <v>45173</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41373,7 +41373,7 @@
         <v>45173</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41446,7 +41446,7 @@
         <v>45246</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41519,7 +41519,7 @@
         <v>44782</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41592,7 +41592,7 @@
         <v>45252</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41665,7 +41665,7 @@
         <v>45170</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41738,7 +41738,7 @@
         <v>44973</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41811,7 +41811,7 @@
         <v>45356</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41884,7 +41884,7 @@
         <v>44847</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41957,7 +41957,7 @@
         <v>45454</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42030,7 +42030,7 @@
         <v>44690</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42103,7 +42103,7 @@
         <v>45349</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42176,7 +42176,7 @@
         <v>45212</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42249,7 +42249,7 @@
         <v>45007</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42322,7 +42322,7 @@
         <v>45007</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42395,7 +42395,7 @@
         <v>45266</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42468,7 +42468,7 @@
         <v>45323</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42541,7 +42541,7 @@
         <v>44963</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42614,7 +42614,7 @@
         <v>44963</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42687,7 +42687,7 @@
         <v>45093</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42760,7 +42760,7 @@
         <v>45229</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42833,7 +42833,7 @@
         <v>44864</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42906,7 +42906,7 @@
         <v>45308</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42979,7 +42979,7 @@
         <v>45595</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43052,7 +43052,7 @@
         <v>44658</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43125,7 +43125,7 @@
         <v>44858</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43198,7 +43198,7 @@
         <v>45524</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43271,7 +43271,7 @@
         <v>44712</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43344,7 +43344,7 @@
         <v>44803</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43417,7 +43417,7 @@
         <v>44978</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43490,7 +43490,7 @@
         <v>44939</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43563,7 +43563,7 @@
         <v>44607</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43636,7 +43636,7 @@
         <v>44587</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43709,7 +43709,7 @@
         <v>45387</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43782,7 +43782,7 @@
         <v>45373</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43855,7 +43855,7 @@
         <v>45345</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43928,7 +43928,7 @@
         <v>45440</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44001,7 +44001,7 @@
         <v>45595</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44074,7 +44074,7 @@
         <v>44806</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44147,7 +44147,7 @@
         <v>44965</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44220,7 +44220,7 @@
         <v>44531</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44293,7 +44293,7 @@
         <v>44957</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44366,7 +44366,7 @@
         <v>45345</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44439,7 +44439,7 @@
         <v>45345</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44512,7 +44512,7 @@
         <v>45685</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44585,7 +44585,7 @@
         <v>45358</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44658,7 +44658,7 @@
         <v>44957</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44731,7 +44731,7 @@
         <v>45824</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44804,7 +44804,7 @@
         <v>44071</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44877,7 +44877,7 @@
         <v>45890</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44950,7 +44950,7 @@
         <v>45902</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45023,7 +45023,7 @@
         <v>46058</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45096,7 +45096,7 @@
         <v>46062</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45169,7 +45169,7 @@
         <v>46062</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45242,7 +45242,7 @@
         <v>46063</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45315,7 +45315,7 @@
         <v>46062</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45388,7 +45388,7 @@
         <v>46062</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45461,7 +45461,7 @@
         <v>46065</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45534,7 +45534,7 @@
         <v>46110</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45607,7 +45607,7 @@
         <v>46300</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
